--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -4258,7 +4258,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130317679</v>
+        <v>130317681</v>
       </c>
       <c r="B30" t="n">
         <v>80285</v>
@@ -4288,11 +4288,7 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4300,10 +4296,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507027</v>
+        <v>506982</v>
       </c>
       <c r="R30" t="n">
-        <v>6958207</v>
+        <v>6958260</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4340,7 +4336,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4393,7 +4389,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130317681</v>
+        <v>130317679</v>
       </c>
       <c r="B31" t="n">
         <v>80285</v>
@@ -4423,7 +4419,11 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506982</v>
+        <v>507027</v>
       </c>
       <c r="R31" t="n">
-        <v>6958260</v>
+        <v>6958207</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317708</v>
+        <v>130317722</v>
       </c>
       <c r="B38" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507136</v>
+        <v>507004</v>
       </c>
       <c r="R38" t="n">
-        <v>6958243</v>
+        <v>6958523</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5375,11 +5375,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5393,26 +5388,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5430,10 +5405,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317674</v>
+        <v>130317723</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5441,31 +5416,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5473,10 +5443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506871</v>
+        <v>506907</v>
       </c>
       <c r="R39" t="n">
-        <v>6958417</v>
+        <v>6958328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5511,17 +5481,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5560,10 +5526,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317673</v>
+        <v>130317708</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>80285</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5571,31 +5537,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5603,10 +5564,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507049</v>
+        <v>507136</v>
       </c>
       <c r="R40" t="n">
-        <v>6958259</v>
+        <v>6958243</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5643,7 +5604,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>På liggande död sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5652,12 +5613,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5675,10 +5657,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317653</v>
+        <v>130317674</v>
       </c>
       <c r="B41" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5686,28 +5668,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5717,10 +5700,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507079</v>
+        <v>506871</v>
       </c>
       <c r="R41" t="n">
-        <v>6958339</v>
+        <v>6958417</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5755,13 +5738,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5780,14 +5767,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5805,10 +5787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317722</v>
+        <v>130317673</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5816,26 +5798,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5843,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507004</v>
+        <v>507049</v>
       </c>
       <c r="R42" t="n">
-        <v>6958523</v>
+        <v>6958259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5881,13 +5868,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5911,10 +5902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317723</v>
+        <v>130317653</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5922,26 +5913,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5949,10 +5944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506907</v>
+        <v>507079</v>
       </c>
       <c r="R43" t="n">
-        <v>6958328</v>
+        <v>6958339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6012,9 +6007,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B53" t="n">
-        <v>78937</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,26 +7165,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7192,10 +7197,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R53" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7230,19 +7235,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7260,10 +7284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>78937</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7271,31 +7295,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7303,10 +7322,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R54" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7341,38 +7360,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317676</v>
+        <v>130317650</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507117</v>
+        <v>506870</v>
       </c>
       <c r="R2" t="n">
-        <v>6958267</v>
+        <v>6958284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317712</v>
+        <v>130317676</v>
       </c>
       <c r="B3" t="n">
         <v>80285</v>
@@ -836,11 +826,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506953</v>
+        <v>507117</v>
       </c>
       <c r="R3" t="n">
-        <v>6958498</v>
+        <v>6958267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
+          <t>På en liggande död sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +904,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317650</v>
+        <v>130317682</v>
       </c>
       <c r="B4" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,26 +938,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506870</v>
+        <v>507013</v>
       </c>
       <c r="R4" t="n">
-        <v>6958284</v>
+        <v>6958267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +1007,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1034,17 +1029,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317682</v>
+        <v>130317712</v>
       </c>
       <c r="B5" t="n">
         <v>80285</v>
@@ -1094,7 +1094,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507013</v>
+        <v>506953</v>
       </c>
       <c r="R5" t="n">
-        <v>6958267</v>
+        <v>6958498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317698</v>
+        <v>130317659</v>
       </c>
       <c r="B16" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,26 +2503,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2530,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506953</v>
+        <v>506915</v>
       </c>
       <c r="R16" t="n">
-        <v>6958489</v>
+        <v>6958411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2584,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2594,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,10 +2622,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317659</v>
+        <v>130317709</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,31 +2633,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2666,10 +2660,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506915</v>
+        <v>507063</v>
       </c>
       <c r="R17" t="n">
-        <v>6958411</v>
+        <v>6958140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2706,7 +2700,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2715,6 +2709,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2725,17 +2720,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317709</v>
+        <v>130317710</v>
       </c>
       <c r="B18" t="n">
         <v>80285</v>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507063</v>
+        <v>506973</v>
       </c>
       <c r="R18" t="n">
-        <v>6958140</v>
+        <v>6958484</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317710</v>
+        <v>130317698</v>
       </c>
       <c r="B19" t="n">
         <v>80285</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506973</v>
+        <v>506953</v>
       </c>
       <c r="R19" t="n">
-        <v>6958484</v>
+        <v>6958489</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317649</v>
+        <v>130317714</v>
       </c>
       <c r="B21" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507053</v>
+        <v>506876</v>
       </c>
       <c r="R21" t="n">
-        <v>6958107</v>
+        <v>6958216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3239,17 +3239,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3267,10 +3272,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317695</v>
+        <v>130317721</v>
       </c>
       <c r="B22" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,37 +3283,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506917</v>
+        <v>507071</v>
       </c>
       <c r="R22" t="n">
-        <v>6958514</v>
+        <v>6958280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3343,45 +3345,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3398,10 +3369,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317714</v>
+        <v>130317649</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3409,21 +3380,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3436,10 +3407,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506876</v>
+        <v>507053</v>
       </c>
       <c r="R23" t="n">
-        <v>6958216</v>
+        <v>6958107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3491,22 +3462,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3524,10 +3490,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317721</v>
+        <v>130317695</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,34 +3501,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507071</v>
+        <v>506917</v>
       </c>
       <c r="R24" t="n">
-        <v>6958280</v>
+        <v>6958514</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3597,14 +3566,45 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4785,7 +4785,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317677</v>
+        <v>130317713</v>
       </c>
       <c r="B34" t="n">
         <v>80285</v>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507084</v>
+        <v>506868</v>
       </c>
       <c r="R34" t="n">
-        <v>6958173</v>
+        <v>6958334</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317713</v>
+        <v>130317677</v>
       </c>
       <c r="B35" t="n">
         <v>80285</v>
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506868</v>
+        <v>507084</v>
       </c>
       <c r="R35" t="n">
-        <v>6958334</v>
+        <v>6958173</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317722</v>
+        <v>130317708</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507004</v>
+        <v>507136</v>
       </c>
       <c r="R38" t="n">
-        <v>6958523</v>
+        <v>6958243</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5375,6 +5375,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5388,6 +5393,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5405,10 +5430,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317723</v>
+        <v>130317674</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5416,26 +5441,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5443,10 +5473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506907</v>
+        <v>506871</v>
       </c>
       <c r="R39" t="n">
-        <v>6958328</v>
+        <v>6958417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5481,13 +5511,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5526,10 +5560,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317708</v>
+        <v>130317673</v>
       </c>
       <c r="B40" t="n">
-        <v>80285</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5537,26 +5571,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5564,10 +5603,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507136</v>
+        <v>507049</v>
       </c>
       <c r="R40" t="n">
-        <v>6958243</v>
+        <v>6958259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5604,7 +5643,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På liggande död sälg.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5613,33 +5652,12 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5657,10 +5675,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317674</v>
+        <v>130317653</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>91728</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5668,29 +5686,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5700,10 +5717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506871</v>
+        <v>507079</v>
       </c>
       <c r="R41" t="n">
-        <v>6958417</v>
+        <v>6958339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5738,17 +5755,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5767,9 +5780,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5787,10 +5805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317673</v>
+        <v>130317722</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5798,31 +5816,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5830,10 +5843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507049</v>
+        <v>507004</v>
       </c>
       <c r="R42" t="n">
-        <v>6958259</v>
+        <v>6958523</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5868,17 +5881,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5902,10 +5911,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317653</v>
+        <v>130317723</v>
       </c>
       <c r="B43" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5913,30 +5922,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5944,10 +5949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507079</v>
+        <v>506907</v>
       </c>
       <c r="R43" t="n">
-        <v>6958339</v>
+        <v>6958328</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6007,14 +6012,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317650</v>
+        <v>130317676</v>
       </c>
       <c r="B2" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506870</v>
+        <v>507117</v>
       </c>
       <c r="R2" t="n">
-        <v>6958284</v>
+        <v>6958267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -768,17 +773,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317676</v>
+        <v>130317712</v>
       </c>
       <c r="B3" t="n">
         <v>80285</v>
@@ -826,7 +836,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507117</v>
+        <v>506953</v>
       </c>
       <c r="R3" t="n">
-        <v>6958267</v>
+        <v>6958498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en liggande död sälg.</t>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +918,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317682</v>
+        <v>130317650</v>
       </c>
       <c r="B4" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,30 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -969,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507013</v>
+        <v>506870</v>
       </c>
       <c r="R4" t="n">
-        <v>6958267</v>
+        <v>6958284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,11 +1017,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1029,22 +1034,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317712</v>
+        <v>130317682</v>
       </c>
       <c r="B5" t="n">
         <v>80285</v>
@@ -1094,7 +1094,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506953</v>
+        <v>507013</v>
       </c>
       <c r="R5" t="n">
-        <v>6958498</v>
+        <v>6958267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317659</v>
+        <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,31 +2503,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2535,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506915</v>
+        <v>506953</v>
       </c>
       <c r="R16" t="n">
-        <v>6958411</v>
+        <v>6958489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2575,7 +2570,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,6 +2579,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2594,17 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2622,10 +2623,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317709</v>
+        <v>130317659</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2633,26 +2634,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2660,10 +2666,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507063</v>
+        <v>506915</v>
       </c>
       <c r="R17" t="n">
-        <v>6958140</v>
+        <v>6958411</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2700,7 +2706,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2709,7 +2715,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2720,22 +2725,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317710</v>
+        <v>130317709</v>
       </c>
       <c r="B18" t="n">
         <v>80285</v>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506973</v>
+        <v>507063</v>
       </c>
       <c r="R18" t="n">
-        <v>6958484</v>
+        <v>6958140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317698</v>
+        <v>130317710</v>
       </c>
       <c r="B19" t="n">
         <v>80285</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506953</v>
+        <v>506973</v>
       </c>
       <c r="R19" t="n">
-        <v>6958489</v>
+        <v>6958484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317714</v>
+        <v>130317649</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506876</v>
+        <v>507053</v>
       </c>
       <c r="R21" t="n">
-        <v>6958216</v>
+        <v>6958107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3239,22 +3239,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3272,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317721</v>
+        <v>130317695</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3283,34 +3278,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507071</v>
+        <v>506917</v>
       </c>
       <c r="R22" t="n">
-        <v>6958280</v>
+        <v>6958514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3345,14 +3343,45 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3369,10 +3398,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317649</v>
+        <v>130317714</v>
       </c>
       <c r="B23" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3380,21 +3409,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3407,10 +3436,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507053</v>
+        <v>506876</v>
       </c>
       <c r="R23" t="n">
-        <v>6958107</v>
+        <v>6958216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3462,17 +3491,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3490,10 +3524,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317695</v>
+        <v>130317721</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3501,37 +3535,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506917</v>
+        <v>507071</v>
       </c>
       <c r="R24" t="n">
-        <v>6958514</v>
+        <v>6958280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3566,45 +3597,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4258,7 +4258,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130317681</v>
+        <v>130317679</v>
       </c>
       <c r="B30" t="n">
         <v>80285</v>
@@ -4288,7 +4288,11 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4296,10 +4300,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506982</v>
+        <v>507027</v>
       </c>
       <c r="R30" t="n">
-        <v>6958260</v>
+        <v>6958207</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4336,7 +4340,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4389,7 +4393,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130317679</v>
+        <v>130317681</v>
       </c>
       <c r="B31" t="n">
         <v>80285</v>
@@ -4419,11 +4423,7 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507027</v>
+        <v>506982</v>
       </c>
       <c r="R31" t="n">
-        <v>6958207</v>
+        <v>6958260</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317708</v>
+        <v>130317722</v>
       </c>
       <c r="B38" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507136</v>
+        <v>507004</v>
       </c>
       <c r="R38" t="n">
-        <v>6958243</v>
+        <v>6958523</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5375,11 +5375,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5393,26 +5388,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5430,10 +5405,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317674</v>
+        <v>130317723</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5441,31 +5416,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5473,10 +5443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506871</v>
+        <v>506907</v>
       </c>
       <c r="R39" t="n">
-        <v>6958417</v>
+        <v>6958328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5511,17 +5481,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5560,10 +5526,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317673</v>
+        <v>130317708</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>80285</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5571,31 +5537,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5603,10 +5564,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507049</v>
+        <v>507136</v>
       </c>
       <c r="R40" t="n">
-        <v>6958259</v>
+        <v>6958243</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5643,7 +5604,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>På liggande död sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5652,12 +5613,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5675,10 +5657,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317653</v>
+        <v>130317674</v>
       </c>
       <c r="B41" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5686,28 +5668,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5717,10 +5700,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507079</v>
+        <v>506871</v>
       </c>
       <c r="R41" t="n">
-        <v>6958339</v>
+        <v>6958417</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5755,13 +5738,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5780,14 +5767,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5805,10 +5787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317722</v>
+        <v>130317673</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5816,26 +5798,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5843,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507004</v>
+        <v>507049</v>
       </c>
       <c r="R42" t="n">
-        <v>6958523</v>
+        <v>6958259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5881,13 +5868,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5911,10 +5902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317723</v>
+        <v>130317653</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5922,26 +5913,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5949,10 +5944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506907</v>
+        <v>507079</v>
       </c>
       <c r="R43" t="n">
-        <v>6958328</v>
+        <v>6958339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6012,9 +6007,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>78937</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,31 +7165,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7197,10 +7192,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R53" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7235,38 +7230,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7284,10 +7260,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>78937</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7295,26 +7271,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7322,10 +7303,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R54" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7360,19 +7341,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317676</v>
+        <v>130317697</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507117</v>
+        <v>506897</v>
       </c>
       <c r="R2" t="n">
-        <v>6958267</v>
+        <v>6958467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en liggande död sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,12 +783,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317712</v>
+        <v>130317682</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506953</v>
+        <v>507013</v>
       </c>
       <c r="R3" t="n">
-        <v>6958498</v>
+        <v>6958267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317650</v>
+        <v>130317712</v>
       </c>
       <c r="B4" t="n">
-        <v>83158</v>
+        <v>80288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,26 +952,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506870</v>
+        <v>506953</v>
       </c>
       <c r="R4" t="n">
-        <v>6958284</v>
+        <v>6958498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +1021,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1034,17 +1043,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317682</v>
+        <v>130317650</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>83161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,30 +1087,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507013</v>
+        <v>506870</v>
       </c>
       <c r="R5" t="n">
-        <v>6958267</v>
+        <v>6958284</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,11 +1152,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1164,22 +1169,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317697</v>
+        <v>130317676</v>
       </c>
       <c r="B6" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506897</v>
+        <v>507117</v>
       </c>
       <c r="R6" t="n">
-        <v>6958467</v>
+        <v>6958267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På en liggande död sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317702</v>
+        <v>130317693</v>
       </c>
       <c r="B7" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506880</v>
+        <v>506874</v>
       </c>
       <c r="R7" t="n">
-        <v>6958248</v>
+        <v>6958543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317685</v>
+        <v>130317702</v>
       </c>
       <c r="B8" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507014</v>
+        <v>506880</v>
       </c>
       <c r="R8" t="n">
-        <v>6958455</v>
+        <v>6958248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317671</v>
+        <v>130317685</v>
       </c>
       <c r="B9" t="n">
-        <v>57985</v>
+        <v>80288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,50 +1601,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506956</v>
+        <v>507014</v>
       </c>
       <c r="R9" t="n">
-        <v>6958085</v>
+        <v>6958455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,18 +1666,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Lunglav på en död sälg.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1838,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317693</v>
+        <v>130317671</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,37 +1862,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506874</v>
+        <v>506956</v>
       </c>
       <c r="R11" t="n">
-        <v>6958543</v>
+        <v>6958085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1914,44 +1940,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317696</v>
+        <v>130317687</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506892</v>
+        <v>507040</v>
       </c>
       <c r="R12" t="n">
-        <v>6958496</v>
+        <v>6958467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2067,22 +2067,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +2095,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317691</v>
+        <v>130317684</v>
       </c>
       <c r="B13" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2130,11 +2125,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2142,10 +2133,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506877</v>
+        <v>507008</v>
       </c>
       <c r="R13" t="n">
-        <v>6958613</v>
+        <v>6958401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2182,7 +2173,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,10 +2226,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317684</v>
+        <v>130317691</v>
       </c>
       <c r="B14" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2256,11 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2273,10 +2268,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507008</v>
+        <v>506877</v>
       </c>
       <c r="R14" t="n">
-        <v>6958401</v>
+        <v>6958613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2313,7 +2308,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2366,10 +2361,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317687</v>
+        <v>130317696</v>
       </c>
       <c r="B15" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507040</v>
+        <v>506892</v>
       </c>
       <c r="R15" t="n">
-        <v>6958467</v>
+        <v>6958496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2439,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2464,17 +2459,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2495,7 +2495,7 @@
         <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317659</v>
+        <v>130317710</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2634,31 +2634,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506915</v>
+        <v>506973</v>
       </c>
       <c r="R17" t="n">
-        <v>6958411</v>
+        <v>6958484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2715,6 +2710,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2725,17 +2721,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2756,7 +2757,7 @@
         <v>130317709</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317710</v>
+        <v>130317659</v>
       </c>
       <c r="B19" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2895,26 +2896,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2922,10 +2928,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506973</v>
+        <v>506915</v>
       </c>
       <c r="R19" t="n">
-        <v>6958484</v>
+        <v>6958411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2962,7 +2968,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2971,7 +2977,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2982,22 +2987,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>130317678</v>
       </c>
       <c r="B20" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317649</v>
+        <v>130317695</v>
       </c>
       <c r="B21" t="n">
-        <v>83158</v>
+        <v>80288</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507053</v>
+        <v>506917</v>
       </c>
       <c r="R21" t="n">
-        <v>6958107</v>
+        <v>6958514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3222,6 +3222,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3239,17 +3244,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3267,10 +3277,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317695</v>
+        <v>130317714</v>
       </c>
       <c r="B22" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3305,10 +3315,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506917</v>
+        <v>506876</v>
       </c>
       <c r="R22" t="n">
-        <v>6958514</v>
+        <v>6958216</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3341,11 +3351,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3398,10 +3403,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317714</v>
+        <v>130317649</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>83161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3409,21 +3414,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3436,10 +3441,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506876</v>
+        <v>507053</v>
       </c>
       <c r="R23" t="n">
-        <v>6958216</v>
+        <v>6958107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3491,22 +3496,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
         <v>130317721</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>130317701</v>
       </c>
       <c r="B25" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317726</v>
+        <v>130317700</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4012,21 +4012,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507008</v>
+        <v>506928</v>
       </c>
       <c r="R28" t="n">
-        <v>6958564</v>
+        <v>6958456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4099,17 +4099,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4127,10 +4132,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130317700</v>
+        <v>130317726</v>
       </c>
       <c r="B29" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4138,21 +4143,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4165,10 +4170,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506928</v>
+        <v>507008</v>
       </c>
       <c r="R29" t="n">
-        <v>6958456</v>
+        <v>6958564</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4210,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4225,22 +4230,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4261,7 +4261,7 @@
         <v>130317679</v>
       </c>
       <c r="B30" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>130317681</v>
       </c>
       <c r="B31" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317688</v>
+        <v>130317713</v>
       </c>
       <c r="B33" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507005</v>
+        <v>506868</v>
       </c>
       <c r="R33" t="n">
-        <v>6958516</v>
+        <v>6958334</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317713</v>
+        <v>130317724</v>
       </c>
       <c r="B34" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506868</v>
+        <v>506880</v>
       </c>
       <c r="R34" t="n">
-        <v>6958334</v>
+        <v>6958273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4861,11 +4861,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Lunglav på död stående björk.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4883,22 +4878,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4916,10 +4906,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317677</v>
+        <v>130317680</v>
       </c>
       <c r="B35" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4954,10 +4944,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507084</v>
+        <v>506984</v>
       </c>
       <c r="R35" t="n">
-        <v>6958173</v>
+        <v>6958243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4984,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +5004,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5047,10 +5037,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317724</v>
+        <v>130317688</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5058,21 +5048,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506880</v>
+        <v>507005</v>
       </c>
       <c r="R36" t="n">
-        <v>6958273</v>
+        <v>6958516</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5123,6 +5113,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5140,17 +5135,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317680</v>
+        <v>130317677</v>
       </c>
       <c r="B37" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506984</v>
+        <v>507084</v>
       </c>
       <c r="R37" t="n">
-        <v>6958243</v>
+        <v>6958173</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5266,22 +5266,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317722</v>
+        <v>130317653</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>91731</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,26 +5310,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5337,10 +5341,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507004</v>
+        <v>507079</v>
       </c>
       <c r="R38" t="n">
-        <v>6958523</v>
+        <v>6958339</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5388,6 +5392,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5405,10 +5429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317723</v>
+        <v>130317722</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5443,10 +5467,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506907</v>
+        <v>507004</v>
       </c>
       <c r="R39" t="n">
-        <v>6958328</v>
+        <v>6958523</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5494,21 +5518,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5526,10 +5535,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317708</v>
+        <v>130317723</v>
       </c>
       <c r="B40" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5537,21 +5546,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5564,10 +5573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507136</v>
+        <v>506907</v>
       </c>
       <c r="R40" t="n">
-        <v>6958243</v>
+        <v>6958328</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5602,11 +5611,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5628,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5657,10 +5656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317674</v>
+        <v>130317708</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>80288</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5668,31 +5667,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5700,10 +5694,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506871</v>
+        <v>507136</v>
       </c>
       <c r="R41" t="n">
-        <v>6958417</v>
+        <v>6958243</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5740,7 +5734,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>På liggande död sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5749,6 +5743,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5759,17 +5754,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5787,7 +5787,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317673</v>
+        <v>130317674</v>
       </c>
       <c r="B42" t="n">
         <v>57823</v>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507049</v>
+        <v>506871</v>
       </c>
       <c r="R42" t="n">
-        <v>6958259</v>
+        <v>6958417</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5885,6 +5885,21 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5902,10 +5917,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317653</v>
+        <v>130317673</v>
       </c>
       <c r="B43" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5913,28 +5928,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5944,10 +5960,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507079</v>
+        <v>507049</v>
       </c>
       <c r="R43" t="n">
-        <v>6958339</v>
+        <v>6958259</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5982,39 +5998,23 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317657</v>
+        <v>130317683</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,31 +6043,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506890</v>
+        <v>507090</v>
       </c>
       <c r="R44" t="n">
-        <v>6958493</v>
+        <v>6958314</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6115,7 +6110,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6124,6 +6119,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6134,17 +6130,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6162,10 +6163,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317728</v>
+        <v>130317694</v>
       </c>
       <c r="B45" t="n">
-        <v>83024</v>
+        <v>80288</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6173,21 +6174,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6200,10 +6201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506918</v>
+        <v>506910</v>
       </c>
       <c r="R45" t="n">
-        <v>6958323</v>
+        <v>6958533</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6238,6 +6239,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6255,17 +6261,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6283,10 +6294,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317694</v>
+        <v>130317728</v>
       </c>
       <c r="B46" t="n">
-        <v>80285</v>
+        <v>83027</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6294,21 +6305,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6321,10 +6332,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506910</v>
+        <v>506918</v>
       </c>
       <c r="R46" t="n">
-        <v>6958533</v>
+        <v>6958323</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6359,11 +6370,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6381,22 +6387,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6417,7 +6418,7 @@
         <v>130317727</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6520,50 +6521,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317719</v>
+        <v>130317657</v>
       </c>
       <c r="B48" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6571,10 +6564,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506940</v>
+        <v>506890</v>
       </c>
       <c r="R48" t="n">
-        <v>6958101</v>
+        <v>6958493</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6611,7 +6604,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6620,13 +6613,27 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6644,37 +6651,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317683</v>
+        <v>130317719</v>
       </c>
       <c r="B49" t="n">
-        <v>80285</v>
+        <v>98923</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6682,10 +6702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507090</v>
+        <v>506940</v>
       </c>
       <c r="R49" t="n">
-        <v>6958314</v>
+        <v>6958101</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6722,7 +6742,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6738,26 +6758,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317675</v>
+        <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>56399</v>
+        <v>80288</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,50 +6786,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507115</v>
+        <v>506964</v>
       </c>
       <c r="R50" t="n">
-        <v>6958267</v>
+        <v>6958502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6870,12 +6857,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6893,10 +6901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317711</v>
+        <v>130317675</v>
       </c>
       <c r="B51" t="n">
-        <v>80285</v>
+        <v>56399</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6904,37 +6912,50 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506964</v>
+        <v>507115</v>
       </c>
       <c r="R51" t="n">
-        <v>6958502</v>
+        <v>6958267</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6975,33 +6996,12 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
         <v>130317699</v>
       </c>
       <c r="B52" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130317668</v>
+        <v>130317692</v>
       </c>
       <c r="B56" t="n">
-        <v>57985</v>
+        <v>80288</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7531,50 +7531,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506884</v>
+        <v>506870</v>
       </c>
       <c r="R56" t="n">
-        <v>6958644</v>
+        <v>6958615</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7609,18 +7596,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7638,10 +7651,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130317692</v>
+        <v>130317668</v>
       </c>
       <c r="B57" t="n">
-        <v>80285</v>
+        <v>57985</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,37 +7662,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506870</v>
+        <v>506884</v>
       </c>
       <c r="R57" t="n">
-        <v>6958615</v>
+        <v>6958644</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7714,44 +7740,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317697</v>
+        <v>130317676</v>
       </c>
       <c r="B2" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506897</v>
+        <v>507117</v>
       </c>
       <c r="R2" t="n">
-        <v>6958467</v>
+        <v>6958267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På en liggande död sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,12 +783,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317682</v>
+        <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507013</v>
+        <v>506953</v>
       </c>
       <c r="R3" t="n">
-        <v>6958267</v>
+        <v>6958498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317712</v>
+        <v>130317650</v>
       </c>
       <c r="B4" t="n">
-        <v>80288</v>
+        <v>83187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,30 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506953</v>
+        <v>506870</v>
       </c>
       <c r="R4" t="n">
-        <v>6958498</v>
+        <v>6958284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,11 +1017,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,22 +1034,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317650</v>
+        <v>130317682</v>
       </c>
       <c r="B5" t="n">
-        <v>83161</v>
+        <v>80314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,26 +1073,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1114,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506870</v>
+        <v>507013</v>
       </c>
       <c r="R5" t="n">
-        <v>6958284</v>
+        <v>6958267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,6 +1142,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1169,17 +1164,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317676</v>
+        <v>130317697</v>
       </c>
       <c r="B6" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507117</v>
+        <v>506897</v>
       </c>
       <c r="R6" t="n">
-        <v>6958267</v>
+        <v>6958467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en liggande död sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317693</v>
+        <v>130317671</v>
       </c>
       <c r="B7" t="n">
-        <v>80288</v>
+        <v>58011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,37 +1339,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506874</v>
+        <v>506956</v>
       </c>
       <c r="R7" t="n">
-        <v>6958543</v>
+        <v>6958085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,44 +1417,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,7 +1449,7 @@
         <v>130317702</v>
       </c>
       <c r="B8" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1593,7 +1580,7 @@
         <v>130317685</v>
       </c>
       <c r="B9" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1721,10 +1708,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317658</v>
+        <v>130317693</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,31 +1719,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1764,10 +1746,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506930</v>
+        <v>506874</v>
       </c>
       <c r="R10" t="n">
-        <v>6958447</v>
+        <v>6958543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1786,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1813,6 +1795,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1823,17 +1806,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,10 +1839,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317671</v>
+        <v>130317658</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,50 +1850,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506956</v>
+        <v>506930</v>
       </c>
       <c r="R11" t="n">
-        <v>6958085</v>
+        <v>6958447</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,6 +1920,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1952,6 +1937,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317687</v>
+        <v>130317696</v>
       </c>
       <c r="B12" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507040</v>
+        <v>506892</v>
       </c>
       <c r="R12" t="n">
-        <v>6958467</v>
+        <v>6958496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2067,17 +2067,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,7 +2103,7 @@
         <v>130317684</v>
       </c>
       <c r="B13" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2226,10 +2231,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317691</v>
+        <v>130317687</v>
       </c>
       <c r="B14" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2256,11 +2261,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2268,10 +2269,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506877</v>
+        <v>507040</v>
       </c>
       <c r="R14" t="n">
-        <v>6958613</v>
+        <v>6958467</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2308,7 +2309,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,22 +2329,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2361,10 +2357,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317696</v>
+        <v>130317691</v>
       </c>
       <c r="B15" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2387,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506892</v>
+        <v>506877</v>
       </c>
       <c r="R15" t="n">
-        <v>6958496</v>
+        <v>6958613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317698</v>
+        <v>130317659</v>
       </c>
       <c r="B16" t="n">
-        <v>80288</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,26 +2503,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2530,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506953</v>
+        <v>506915</v>
       </c>
       <c r="R16" t="n">
-        <v>6958489</v>
+        <v>6958411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2584,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2594,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,10 +2622,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317710</v>
+        <v>130317698</v>
       </c>
       <c r="B17" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,10 +2660,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506973</v>
+        <v>506953</v>
       </c>
       <c r="R17" t="n">
-        <v>6958484</v>
+        <v>6958489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2757,7 +2756,7 @@
         <v>130317709</v>
       </c>
       <c r="B18" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,10 +2884,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317659</v>
+        <v>130317710</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,31 +2895,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2928,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506915</v>
+        <v>506973</v>
       </c>
       <c r="R19" t="n">
-        <v>6958411</v>
+        <v>6958484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2968,7 +2962,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,6 +2971,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2987,17 +2982,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>130317678</v>
       </c>
       <c r="B20" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317695</v>
+        <v>130317721</v>
       </c>
       <c r="B21" t="n">
-        <v>80288</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,37 +3157,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506917</v>
+        <v>507071</v>
       </c>
       <c r="R21" t="n">
-        <v>6958514</v>
+        <v>6958280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3222,45 +3219,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3277,10 +3243,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317714</v>
+        <v>130317649</v>
       </c>
       <c r="B22" t="n">
-        <v>80288</v>
+        <v>83187</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3288,21 +3254,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3315,10 +3281,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506876</v>
+        <v>507053</v>
       </c>
       <c r="R22" t="n">
-        <v>6958216</v>
+        <v>6958107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3370,22 +3336,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3403,10 +3364,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317649</v>
+        <v>130317695</v>
       </c>
       <c r="B23" t="n">
-        <v>83161</v>
+        <v>80314</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3414,21 +3375,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3441,10 +3402,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507053</v>
+        <v>506917</v>
       </c>
       <c r="R23" t="n">
-        <v>6958107</v>
+        <v>6958514</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3479,6 +3440,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3496,17 +3462,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3524,10 +3495,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317721</v>
+        <v>130317714</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,34 +3506,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507071</v>
+        <v>506876</v>
       </c>
       <c r="R24" t="n">
-        <v>6958280</v>
+        <v>6958216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3603,8 +3577,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3624,7 +3624,7 @@
         <v>130317701</v>
       </c>
       <c r="B25" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>130317670</v>
       </c>
       <c r="B26" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B27" t="n">
-        <v>80288</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R27" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,22 +3968,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4001,10 +3996,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317700</v>
+        <v>130317689</v>
       </c>
       <c r="B28" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4039,10 +4034,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506928</v>
+        <v>506962</v>
       </c>
       <c r="R28" t="n">
-        <v>6958456</v>
+        <v>6958547</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +4074,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4132,10 +4127,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130317726</v>
+        <v>130317700</v>
       </c>
       <c r="B29" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4143,21 +4138,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4170,10 +4165,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507008</v>
+        <v>506928</v>
       </c>
       <c r="R29" t="n">
-        <v>6958564</v>
+        <v>6958456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4210,7 +4205,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4230,17 +4225,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4261,7 +4261,7 @@
         <v>130317679</v>
       </c>
       <c r="B30" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>130317681</v>
       </c>
       <c r="B31" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>130317661</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317713</v>
+        <v>130317688</v>
       </c>
       <c r="B33" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506868</v>
+        <v>507005</v>
       </c>
       <c r="R33" t="n">
-        <v>6958334</v>
+        <v>6958516</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317724</v>
+        <v>130317680</v>
       </c>
       <c r="B34" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506880</v>
+        <v>506984</v>
       </c>
       <c r="R34" t="n">
-        <v>6958273</v>
+        <v>6958243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4861,6 +4861,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4878,17 +4883,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4906,10 +4916,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317680</v>
+        <v>130317713</v>
       </c>
       <c r="B35" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4944,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506984</v>
+        <v>506868</v>
       </c>
       <c r="R35" t="n">
-        <v>6958243</v>
+        <v>6958334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4984,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5004,22 +5014,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5037,10 +5047,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317688</v>
+        <v>130317677</v>
       </c>
       <c r="B36" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507005</v>
+        <v>507084</v>
       </c>
       <c r="R36" t="n">
-        <v>6958516</v>
+        <v>6958173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5115,7 +5125,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5135,22 +5145,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317677</v>
+        <v>130317724</v>
       </c>
       <c r="B37" t="n">
-        <v>80288</v>
+        <v>79209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5179,21 +5189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5206,10 +5216,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507084</v>
+        <v>506880</v>
       </c>
       <c r="R37" t="n">
-        <v>6958173</v>
+        <v>6958273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5244,11 +5254,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På grenar av gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5274,14 +5279,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317653</v>
+        <v>130317722</v>
       </c>
       <c r="B38" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,30 +5310,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5341,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507079</v>
+        <v>507004</v>
       </c>
       <c r="R38" t="n">
-        <v>6958339</v>
+        <v>6958523</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5392,26 +5388,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5429,10 +5405,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317722</v>
+        <v>130317723</v>
       </c>
       <c r="B39" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5467,10 +5443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507004</v>
+        <v>506907</v>
       </c>
       <c r="R39" t="n">
-        <v>6958523</v>
+        <v>6958328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5518,6 +5494,21 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5535,10 +5526,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317723</v>
+        <v>130317708</v>
       </c>
       <c r="B40" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5546,21 +5537,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5573,10 +5564,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506907</v>
+        <v>507136</v>
       </c>
       <c r="R40" t="n">
-        <v>6958328</v>
+        <v>6958243</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5611,6 +5602,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5628,17 +5624,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5656,10 +5657,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317708</v>
+        <v>130317653</v>
       </c>
       <c r="B41" t="n">
-        <v>80288</v>
+        <v>91757</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5667,26 +5668,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5694,10 +5699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507136</v>
+        <v>507079</v>
       </c>
       <c r="R41" t="n">
-        <v>6958243</v>
+        <v>6958339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5732,11 +5737,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5754,22 +5754,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5790,7 +5790,7 @@
         <v>130317674</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>130317673</v>
       </c>
       <c r="B43" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317683</v>
+        <v>130317728</v>
       </c>
       <c r="B44" t="n">
-        <v>80288</v>
+        <v>83053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507090</v>
+        <v>506918</v>
       </c>
       <c r="R44" t="n">
-        <v>6958314</v>
+        <v>6958323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,11 +6108,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6130,22 +6125,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6163,10 +6153,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317694</v>
+        <v>130317657</v>
       </c>
       <c r="B45" t="n">
-        <v>80288</v>
+        <v>57852</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6174,26 +6164,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6201,10 +6196,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506910</v>
+        <v>506890</v>
       </c>
       <c r="R45" t="n">
-        <v>6958533</v>
+        <v>6958493</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6241,7 +6236,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6250,7 +6245,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6261,22 +6255,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6294,37 +6283,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317728</v>
+        <v>130317719</v>
       </c>
       <c r="B46" t="n">
-        <v>83027</v>
+        <v>98949</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6332,10 +6334,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506918</v>
+        <v>506940</v>
       </c>
       <c r="R46" t="n">
-        <v>6958323</v>
+        <v>6958101</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6370,6 +6372,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6383,21 +6390,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6415,10 +6407,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317727</v>
+        <v>130317694</v>
       </c>
       <c r="B47" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6426,21 +6418,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6453,10 +6445,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506867</v>
+        <v>506910</v>
       </c>
       <c r="R47" t="n">
-        <v>6958649</v>
+        <v>6958533</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6491,6 +6483,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6504,6 +6501,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6521,10 +6538,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317657</v>
+        <v>130317727</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6532,31 +6549,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6564,10 +6576,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506890</v>
+        <v>506867</v>
       </c>
       <c r="R48" t="n">
-        <v>6958493</v>
+        <v>6958649</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6602,38 +6614,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6651,50 +6644,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317719</v>
+        <v>130317683</v>
       </c>
       <c r="B49" t="n">
-        <v>98923</v>
+        <v>80314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6702,10 +6682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506940</v>
+        <v>507090</v>
       </c>
       <c r="R49" t="n">
-        <v>6958101</v>
+        <v>6958314</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6742,7 +6722,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6758,6 +6738,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6778,7 +6778,7 @@
         <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6901,10 +6901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317675</v>
+        <v>130317699</v>
       </c>
       <c r="B51" t="n">
-        <v>56399</v>
+        <v>80314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6912,50 +6912,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507115</v>
+        <v>506945</v>
       </c>
       <c r="R51" t="n">
-        <v>6958267</v>
+        <v>6958463</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6990,18 +6981,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7019,10 +7036,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317699</v>
+        <v>130317675</v>
       </c>
       <c r="B52" t="n">
-        <v>80288</v>
+        <v>56425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7030,41 +7047,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506945</v>
+        <v>507115</v>
       </c>
       <c r="R52" t="n">
-        <v>6958463</v>
+        <v>6958267</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7099,44 +7125,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7157,7 +7157,7 @@
         <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>130317660</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>130317692</v>
       </c>
       <c r="B56" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>130317668</v>
       </c>
       <c r="B57" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -1969,7 +1969,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317696</v>
+        <v>130317684</v>
       </c>
       <c r="B12" t="n">
         <v>80314</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506892</v>
+        <v>507008</v>
       </c>
       <c r="R12" t="n">
-        <v>6958496</v>
+        <v>6958401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317684</v>
+        <v>130317687</v>
       </c>
       <c r="B13" t="n">
         <v>80314</v>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507008</v>
+        <v>507040</v>
       </c>
       <c r="R13" t="n">
-        <v>6958401</v>
+        <v>6958467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2198,22 +2198,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2231,7 +2226,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317687</v>
+        <v>130317696</v>
       </c>
       <c r="B14" t="n">
         <v>80314</v>
@@ -2269,10 +2264,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507040</v>
+        <v>506892</v>
       </c>
       <c r="R14" t="n">
-        <v>6958467</v>
+        <v>6958496</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2309,7 +2304,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2329,17 +2324,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317711</v>
+        <v>130317675</v>
       </c>
       <c r="B50" t="n">
-        <v>80314</v>
+        <v>56425</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,37 +6786,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506964</v>
+        <v>507115</v>
       </c>
       <c r="R50" t="n">
-        <v>6958502</v>
+        <v>6958267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6857,33 +6870,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6901,7 +6893,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317699</v>
+        <v>130317711</v>
       </c>
       <c r="B51" t="n">
         <v>80314</v>
@@ -6931,11 +6923,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6943,10 +6931,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506945</v>
+        <v>506964</v>
       </c>
       <c r="R51" t="n">
-        <v>6958463</v>
+        <v>6958502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6979,11 +6967,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7036,10 +7019,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317675</v>
+        <v>130317699</v>
       </c>
       <c r="B52" t="n">
-        <v>56425</v>
+        <v>80314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7047,50 +7030,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507115</v>
+        <v>506945</v>
       </c>
       <c r="R52" t="n">
-        <v>6958267</v>
+        <v>6958463</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7125,18 +7099,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317676</v>
+        <v>130317650</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>83188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507117</v>
+        <v>506870</v>
       </c>
       <c r="R2" t="n">
-        <v>6958267</v>
+        <v>6958284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317712</v>
+        <v>130317676</v>
       </c>
       <c r="B3" t="n">
         <v>80314</v>
@@ -836,11 +826,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506953</v>
+        <v>507117</v>
       </c>
       <c r="R3" t="n">
-        <v>6958498</v>
+        <v>6958267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
+          <t>På en liggande död sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +904,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317650</v>
+        <v>130317712</v>
       </c>
       <c r="B4" t="n">
-        <v>83187</v>
+        <v>80314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,26 +938,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506870</v>
+        <v>506953</v>
       </c>
       <c r="R4" t="n">
-        <v>6958284</v>
+        <v>6958498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +1007,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1034,17 +1029,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317671</v>
+        <v>130317658</v>
       </c>
       <c r="B7" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,50 +1339,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506956</v>
+        <v>506930</v>
       </c>
       <c r="R7" t="n">
-        <v>6958085</v>
+        <v>6958447</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1417,6 +1409,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1429,6 +1426,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1458,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317702</v>
+        <v>130317671</v>
       </c>
       <c r="B8" t="n">
-        <v>80314</v>
+        <v>58011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,37 +1469,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506880</v>
+        <v>506956</v>
       </c>
       <c r="R8" t="n">
-        <v>6958248</v>
+        <v>6958085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,44 +1547,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1577,7 +1576,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317685</v>
+        <v>130317702</v>
       </c>
       <c r="B9" t="n">
         <v>80314</v>
@@ -1615,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507014</v>
+        <v>506880</v>
       </c>
       <c r="R9" t="n">
-        <v>6958455</v>
+        <v>6958248</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1655,7 +1654,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,12 +1684,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1708,7 +1707,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317693</v>
+        <v>130317685</v>
       </c>
       <c r="B10" t="n">
         <v>80314</v>
@@ -1746,10 +1745,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506874</v>
+        <v>507014</v>
       </c>
       <c r="R10" t="n">
-        <v>6958543</v>
+        <v>6958455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1786,7 +1785,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på en död sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,12 +1815,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1839,10 +1838,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317658</v>
+        <v>130317693</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,31 +1849,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1882,10 +1876,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506930</v>
+        <v>506874</v>
       </c>
       <c r="R11" t="n">
-        <v>6958447</v>
+        <v>6958543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1922,7 +1916,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,6 +1925,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1941,17 +1936,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317684</v>
+        <v>130317696</v>
       </c>
       <c r="B12" t="n">
         <v>80314</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507008</v>
+        <v>506892</v>
       </c>
       <c r="R12" t="n">
-        <v>6958401</v>
+        <v>6958496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317687</v>
+        <v>130317691</v>
       </c>
       <c r="B13" t="n">
         <v>80314</v>
@@ -2130,7 +2130,11 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2138,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507040</v>
+        <v>506877</v>
       </c>
       <c r="R13" t="n">
-        <v>6958467</v>
+        <v>6958613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2178,7 +2182,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2198,17 +2202,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2226,7 +2235,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317696</v>
+        <v>130317684</v>
       </c>
       <c r="B14" t="n">
         <v>80314</v>
@@ -2264,10 +2273,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506892</v>
+        <v>507008</v>
       </c>
       <c r="R14" t="n">
-        <v>6958496</v>
+        <v>6958401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2357,7 +2366,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317691</v>
+        <v>130317687</v>
       </c>
       <c r="B15" t="n">
         <v>80314</v>
@@ -2387,11 +2396,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2399,10 +2404,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506877</v>
+        <v>507040</v>
       </c>
       <c r="R15" t="n">
-        <v>6958613</v>
+        <v>6958467</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2439,7 +2444,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2459,22 +2464,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317659</v>
+        <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>80314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,31 +2503,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2535,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506915</v>
+        <v>506953</v>
       </c>
       <c r="R16" t="n">
-        <v>6958411</v>
+        <v>6958489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2575,7 +2570,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,6 +2579,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2594,17 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2622,7 +2623,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317698</v>
+        <v>130317709</v>
       </c>
       <c r="B17" t="n">
         <v>80314</v>
@@ -2660,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506953</v>
+        <v>507063</v>
       </c>
       <c r="R17" t="n">
-        <v>6958489</v>
+        <v>6958140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2753,7 +2754,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317709</v>
+        <v>130317710</v>
       </c>
       <c r="B18" t="n">
         <v>80314</v>
@@ -2791,10 +2792,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507063</v>
+        <v>506973</v>
       </c>
       <c r="R18" t="n">
-        <v>6958140</v>
+        <v>6958484</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317710</v>
+        <v>130317659</v>
       </c>
       <c r="B19" t="n">
-        <v>80314</v>
+        <v>57852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2895,26 +2896,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2922,10 +2928,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506973</v>
+        <v>506915</v>
       </c>
       <c r="R19" t="n">
-        <v>6958484</v>
+        <v>6958411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2962,7 +2968,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2971,7 +2977,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2982,22 +2987,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317721</v>
+        <v>130317649</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>83188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,34 +3157,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507071</v>
+        <v>507053</v>
       </c>
       <c r="R21" t="n">
-        <v>6958280</v>
+        <v>6958107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3225,8 +3228,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3243,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317649</v>
+        <v>130317721</v>
       </c>
       <c r="B22" t="n">
-        <v>83187</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3254,37 +3278,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507053</v>
+        <v>507071</v>
       </c>
       <c r="R22" t="n">
-        <v>6958107</v>
+        <v>6958280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3325,29 +3346,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317688</v>
+        <v>130317724</v>
       </c>
       <c r="B33" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507005</v>
+        <v>506880</v>
       </c>
       <c r="R33" t="n">
-        <v>6958516</v>
+        <v>6958273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4730,11 +4730,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4752,22 +4747,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4785,7 +4775,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317680</v>
+        <v>130317688</v>
       </c>
       <c r="B34" t="n">
         <v>80314</v>
@@ -4823,10 +4813,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506984</v>
+        <v>507005</v>
       </c>
       <c r="R34" t="n">
-        <v>6958243</v>
+        <v>6958516</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4863,7 +4853,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4916,7 +4906,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317713</v>
+        <v>130317680</v>
       </c>
       <c r="B35" t="n">
         <v>80314</v>
@@ -4954,10 +4944,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506868</v>
+        <v>506984</v>
       </c>
       <c r="R35" t="n">
-        <v>6958334</v>
+        <v>6958243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4984,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +5004,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5047,7 +5037,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317677</v>
+        <v>130317713</v>
       </c>
       <c r="B36" t="n">
         <v>80314</v>
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507084</v>
+        <v>506868</v>
       </c>
       <c r="R36" t="n">
-        <v>6958173</v>
+        <v>6958334</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5125,7 +5115,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5145,22 +5135,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5178,10 +5168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317724</v>
+        <v>130317677</v>
       </c>
       <c r="B37" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5189,21 +5179,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5216,10 +5206,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506880</v>
+        <v>507084</v>
       </c>
       <c r="R37" t="n">
-        <v>6958273</v>
+        <v>6958173</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5254,6 +5244,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På grenar av gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5279,9 +5274,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317722</v>
+        <v>130317653</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>91758</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,26 +5310,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5337,10 +5341,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507004</v>
+        <v>507079</v>
       </c>
       <c r="R38" t="n">
-        <v>6958523</v>
+        <v>6958339</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5388,6 +5392,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5526,10 +5550,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317708</v>
+        <v>130317722</v>
       </c>
       <c r="B40" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5537,21 +5561,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5564,10 +5588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507136</v>
+        <v>507004</v>
       </c>
       <c r="R40" t="n">
-        <v>6958243</v>
+        <v>6958523</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5602,11 +5626,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5620,26 +5639,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5657,10 +5656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317653</v>
+        <v>130317708</v>
       </c>
       <c r="B41" t="n">
-        <v>91757</v>
+        <v>80314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5668,30 +5667,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5699,10 +5694,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507079</v>
+        <v>507136</v>
       </c>
       <c r="R41" t="n">
-        <v>6958339</v>
+        <v>6958243</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5737,6 +5732,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5754,22 +5754,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317728</v>
+        <v>130317657</v>
       </c>
       <c r="B44" t="n">
-        <v>83053</v>
+        <v>57852</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,26 +6043,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506918</v>
+        <v>506890</v>
       </c>
       <c r="R44" t="n">
-        <v>6958323</v>
+        <v>6958493</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,13 +6113,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6153,42 +6162,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317657</v>
+        <v>130317719</v>
       </c>
       <c r="B45" t="n">
-        <v>57852</v>
+        <v>98950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6196,10 +6213,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506890</v>
+        <v>506940</v>
       </c>
       <c r="R45" t="n">
-        <v>6958493</v>
+        <v>6958101</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6236,7 +6253,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6245,27 +6262,13 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6283,50 +6286,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317719</v>
+        <v>130317728</v>
       </c>
       <c r="B46" t="n">
-        <v>98949</v>
+        <v>83054</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6334,10 +6324,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506940</v>
+        <v>506918</v>
       </c>
       <c r="R46" t="n">
-        <v>6958101</v>
+        <v>6958323</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6372,11 +6362,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6390,6 +6375,21 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317727</v>
+        <v>130317683</v>
       </c>
       <c r="B48" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6549,21 +6549,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506867</v>
+        <v>507090</v>
       </c>
       <c r="R48" t="n">
-        <v>6958649</v>
+        <v>6958314</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6614,6 +6614,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6627,6 +6632,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6644,10 +6669,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317683</v>
+        <v>130317727</v>
       </c>
       <c r="B49" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,21 +6680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6682,10 +6707,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507090</v>
+        <v>506867</v>
       </c>
       <c r="R49" t="n">
-        <v>6958314</v>
+        <v>6958649</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6720,11 +6745,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6738,26 +6758,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317675</v>
+        <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>56425</v>
+        <v>80314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,50 +6786,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507115</v>
+        <v>506964</v>
       </c>
       <c r="R50" t="n">
-        <v>6958267</v>
+        <v>6958502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6870,12 +6857,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6893,7 +6901,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317711</v>
+        <v>130317699</v>
       </c>
       <c r="B51" t="n">
         <v>80314</v>
@@ -6923,7 +6931,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6931,10 +6943,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506964</v>
+        <v>506945</v>
       </c>
       <c r="R51" t="n">
-        <v>6958502</v>
+        <v>6958463</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6967,6 +6979,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7019,10 +7036,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317699</v>
+        <v>130317675</v>
       </c>
       <c r="B52" t="n">
-        <v>80314</v>
+        <v>56425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7030,41 +7047,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506945</v>
+        <v>507115</v>
       </c>
       <c r="R52" t="n">
-        <v>6958463</v>
+        <v>6958267</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7099,44 +7125,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B53" t="n">
-        <v>78966</v>
+        <v>57852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,26 +7165,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7192,10 +7197,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R53" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7230,19 +7235,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7260,10 +7284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B54" t="n">
-        <v>57852</v>
+        <v>78966</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7271,31 +7295,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7303,10 +7322,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R54" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7341,38 +7360,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130317692</v>
+        <v>130317668</v>
       </c>
       <c r="B56" t="n">
-        <v>80314</v>
+        <v>58011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7531,37 +7531,50 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506870</v>
+        <v>506884</v>
       </c>
       <c r="R56" t="n">
-        <v>6958615</v>
+        <v>6958644</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7596,44 +7609,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7651,10 +7638,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130317668</v>
+        <v>130317692</v>
       </c>
       <c r="B57" t="n">
-        <v>58011</v>
+        <v>80314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7662,50 +7649,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506884</v>
+        <v>506870</v>
       </c>
       <c r="R57" t="n">
-        <v>6958644</v>
+        <v>6958615</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7740,18 +7714,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317650</v>
+        <v>130317676</v>
       </c>
       <c r="B2" t="n">
-        <v>83188</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506870</v>
+        <v>507117</v>
       </c>
       <c r="R2" t="n">
-        <v>6958284</v>
+        <v>6958267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -768,17 +773,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317676</v>
+        <v>130317712</v>
       </c>
       <c r="B3" t="n">
         <v>80314</v>
@@ -826,7 +836,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507117</v>
+        <v>506953</v>
       </c>
       <c r="R3" t="n">
-        <v>6958267</v>
+        <v>6958498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en liggande död sälg.</t>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,12 +918,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,7 +941,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317712</v>
+        <v>130317682</v>
       </c>
       <c r="B4" t="n">
         <v>80314</v>
@@ -959,7 +973,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -969,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506953</v>
+        <v>507013</v>
       </c>
       <c r="R4" t="n">
-        <v>6958498</v>
+        <v>6958267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1076,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317682</v>
+        <v>130317697</v>
       </c>
       <c r="B5" t="n">
         <v>80314</v>
@@ -1092,11 +1106,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507013</v>
+        <v>506897</v>
       </c>
       <c r="R5" t="n">
-        <v>6958267</v>
+        <v>6958467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1154,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317697</v>
+        <v>130317650</v>
       </c>
       <c r="B6" t="n">
-        <v>80314</v>
+        <v>83189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,21 +1218,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506897</v>
+        <v>506870</v>
       </c>
       <c r="R6" t="n">
-        <v>6958467</v>
+        <v>6958284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,11 +1283,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1295,22 +1300,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -3149,7 +3149,7 @@
         <v>130317649</v>
       </c>
       <c r="B21" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317721</v>
+        <v>130317695</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,34 +3278,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507071</v>
+        <v>506917</v>
       </c>
       <c r="R22" t="n">
-        <v>6958280</v>
+        <v>6958514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3340,14 +3343,45 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3364,7 +3398,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317695</v>
+        <v>130317714</v>
       </c>
       <c r="B23" t="n">
         <v>80314</v>
@@ -3402,10 +3436,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506917</v>
+        <v>506876</v>
       </c>
       <c r="R23" t="n">
-        <v>6958514</v>
+        <v>6958216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,11 +3472,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3495,10 +3524,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317714</v>
+        <v>130317721</v>
       </c>
       <c r="B24" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3506,37 +3535,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506876</v>
+        <v>507071</v>
       </c>
       <c r="R24" t="n">
-        <v>6958216</v>
+        <v>6958280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3577,34 +3603,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3621,10 +3621,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130317701</v>
+        <v>130317670</v>
       </c>
       <c r="B25" t="n">
-        <v>80314</v>
+        <v>58011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3632,37 +3632,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506872</v>
+        <v>506867</v>
       </c>
       <c r="R25" t="n">
-        <v>6958352</v>
+        <v>6958649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3697,44 +3710,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På en björkhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3752,10 +3739,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130317670</v>
+        <v>130317701</v>
       </c>
       <c r="B26" t="n">
-        <v>58011</v>
+        <v>80314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3763,50 +3750,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506867</v>
+        <v>506872</v>
       </c>
       <c r="R26" t="n">
-        <v>6958649</v>
+        <v>6958352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3841,18 +3815,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317726</v>
+        <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507008</v>
+        <v>506962</v>
       </c>
       <c r="R27" t="n">
-        <v>6958564</v>
+        <v>6958547</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,17 +3968,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3996,10 +4001,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B28" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4007,21 +4012,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4034,10 +4039,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R28" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4074,7 +4079,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4094,22 +4099,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317724</v>
+        <v>130317688</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506880</v>
+        <v>507005</v>
       </c>
       <c r="R33" t="n">
-        <v>6958273</v>
+        <v>6958516</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4730,6 +4730,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4747,17 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4775,7 +4785,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317688</v>
+        <v>130317680</v>
       </c>
       <c r="B34" t="n">
         <v>80314</v>
@@ -4813,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507005</v>
+        <v>506984</v>
       </c>
       <c r="R34" t="n">
-        <v>6958516</v>
+        <v>6958243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4853,7 +4863,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4906,7 +4916,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317680</v>
+        <v>130317713</v>
       </c>
       <c r="B35" t="n">
         <v>80314</v>
@@ -4944,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506984</v>
+        <v>506868</v>
       </c>
       <c r="R35" t="n">
-        <v>6958243</v>
+        <v>6958334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4984,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5004,22 +5014,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5037,7 +5047,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317713</v>
+        <v>130317677</v>
       </c>
       <c r="B36" t="n">
         <v>80314</v>
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506868</v>
+        <v>507084</v>
       </c>
       <c r="R36" t="n">
-        <v>6958334</v>
+        <v>6958173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5115,7 +5125,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5135,22 +5145,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317677</v>
+        <v>130317724</v>
       </c>
       <c r="B37" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5179,21 +5189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5206,10 +5216,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507084</v>
+        <v>506880</v>
       </c>
       <c r="R37" t="n">
-        <v>6958173</v>
+        <v>6958273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5244,11 +5254,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På grenar av gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5274,14 +5279,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317653</v>
+        <v>130317723</v>
       </c>
       <c r="B38" t="n">
-        <v>91758</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,30 +5310,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5341,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507079</v>
+        <v>506907</v>
       </c>
       <c r="R38" t="n">
-        <v>6958339</v>
+        <v>6958328</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5404,14 +5400,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5429,10 +5420,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317723</v>
+        <v>130317708</v>
       </c>
       <c r="B39" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5440,21 +5431,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5467,10 +5458,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506907</v>
+        <v>507136</v>
       </c>
       <c r="R39" t="n">
-        <v>6958328</v>
+        <v>6958243</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5505,6 +5496,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5522,17 +5518,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5550,10 +5551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317722</v>
+        <v>130317653</v>
       </c>
       <c r="B40" t="n">
-        <v>79209</v>
+        <v>91759</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5561,26 +5562,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5588,10 +5593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507004</v>
+        <v>507079</v>
       </c>
       <c r="R40" t="n">
-        <v>6958523</v>
+        <v>6958339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5639,6 +5644,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5656,10 +5681,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317708</v>
+        <v>130317722</v>
       </c>
       <c r="B41" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5667,21 +5692,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5694,10 +5719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507136</v>
+        <v>507004</v>
       </c>
       <c r="R41" t="n">
-        <v>6958243</v>
+        <v>6958523</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5732,11 +5757,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5770,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5787,7 +5787,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317674</v>
+        <v>130317673</v>
       </c>
       <c r="B42" t="n">
         <v>57849</v>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506871</v>
+        <v>507049</v>
       </c>
       <c r="R42" t="n">
-        <v>6958417</v>
+        <v>6958259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5885,21 +5885,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5917,7 +5902,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317673</v>
+        <v>130317674</v>
       </c>
       <c r="B43" t="n">
         <v>57849</v>
@@ -5960,10 +5945,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507049</v>
+        <v>506871</v>
       </c>
       <c r="R43" t="n">
-        <v>6958259</v>
+        <v>6958417</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6015,6 +6000,21 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317657</v>
+        <v>130317683</v>
       </c>
       <c r="B44" t="n">
-        <v>57852</v>
+        <v>80314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,31 +6043,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506890</v>
+        <v>507090</v>
       </c>
       <c r="R44" t="n">
-        <v>6958493</v>
+        <v>6958314</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6115,7 +6110,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6124,6 +6119,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6134,17 +6130,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6162,50 +6163,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317719</v>
+        <v>130317657</v>
       </c>
       <c r="B45" t="n">
-        <v>98950</v>
+        <v>57852</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6213,10 +6206,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506940</v>
+        <v>506890</v>
       </c>
       <c r="R45" t="n">
-        <v>6958101</v>
+        <v>6958493</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6253,7 +6246,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6262,13 +6255,27 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6289,7 +6296,7 @@
         <v>130317728</v>
       </c>
       <c r="B46" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6538,10 +6545,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317683</v>
+        <v>130317727</v>
       </c>
       <c r="B48" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6549,21 +6556,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6576,10 +6583,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507090</v>
+        <v>506867</v>
       </c>
       <c r="R48" t="n">
-        <v>6958314</v>
+        <v>6958649</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6614,11 +6621,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6632,26 +6634,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6669,37 +6651,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317727</v>
+        <v>130317719</v>
       </c>
       <c r="B49" t="n">
-        <v>79209</v>
+        <v>98951</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6707,10 +6702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506867</v>
+        <v>506940</v>
       </c>
       <c r="R49" t="n">
-        <v>6958649</v>
+        <v>6958101</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6743,6 +6738,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>57852</v>
+        <v>78966</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,31 +7165,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7197,10 +7192,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R53" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7235,38 +7230,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7284,10 +7260,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>78966</v>
+        <v>57852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7295,26 +7271,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7322,10 +7303,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R54" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7360,19 +7341,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130317668</v>
+        <v>130317692</v>
       </c>
       <c r="B56" t="n">
-        <v>58011</v>
+        <v>80314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7531,50 +7531,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506884</v>
+        <v>506870</v>
       </c>
       <c r="R56" t="n">
-        <v>6958644</v>
+        <v>6958615</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7609,18 +7596,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7638,10 +7651,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130317692</v>
+        <v>130317668</v>
       </c>
       <c r="B57" t="n">
-        <v>80314</v>
+        <v>58011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7649,37 +7662,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506870</v>
+        <v>506884</v>
       </c>
       <c r="R57" t="n">
-        <v>6958615</v>
+        <v>6958644</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7714,44 +7740,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317676</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>130317682</v>
       </c>
       <c r="B4" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>130317697</v>
       </c>
       <c r="B5" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>130317650</v>
       </c>
       <c r="B6" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317658</v>
+        <v>130317702</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,31 +1339,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506930</v>
+        <v>506880</v>
       </c>
       <c r="R7" t="n">
-        <v>6958447</v>
+        <v>6958248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,6 +1415,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1430,17 +1426,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1458,10 +1459,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317671</v>
+        <v>130317685</v>
       </c>
       <c r="B8" t="n">
-        <v>58011</v>
+        <v>80316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,50 +1470,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506956</v>
+        <v>507014</v>
       </c>
       <c r="R8" t="n">
-        <v>6958085</v>
+        <v>6958455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,18 +1535,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lunglav på en död sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1576,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317702</v>
+        <v>130317693</v>
       </c>
       <c r="B9" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,10 +1628,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506880</v>
+        <v>506874</v>
       </c>
       <c r="R9" t="n">
-        <v>6958248</v>
+        <v>6958543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,7 +1668,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1707,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317685</v>
+        <v>130317658</v>
       </c>
       <c r="B10" t="n">
-        <v>80314</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,26 +1732,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1745,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507014</v>
+        <v>506930</v>
       </c>
       <c r="R10" t="n">
-        <v>6958455</v>
+        <v>6958447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1785,7 +1804,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,7 +1813,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1805,22 +1823,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1838,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317693</v>
+        <v>130317671</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>58013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,37 +1862,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506874</v>
+        <v>506956</v>
       </c>
       <c r="R11" t="n">
-        <v>6958543</v>
+        <v>6958085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1914,44 +1940,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>130317696</v>
       </c>
       <c r="B12" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>130317691</v>
       </c>
       <c r="B13" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>130317684</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>130317687</v>
       </c>
       <c r="B15" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>130317709</v>
       </c>
       <c r="B17" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>130317710</v>
       </c>
       <c r="B18" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>130317659</v>
       </c>
       <c r="B19" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>130317678</v>
       </c>
       <c r="B20" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>130317649</v>
       </c>
       <c r="B21" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317695</v>
+        <v>130317721</v>
       </c>
       <c r="B22" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,37 +3278,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506917</v>
+        <v>507071</v>
       </c>
       <c r="R22" t="n">
-        <v>6958514</v>
+        <v>6958280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3343,45 +3340,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3398,10 +3364,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317714</v>
+        <v>130317695</v>
       </c>
       <c r="B23" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3436,10 +3402,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506876</v>
+        <v>506917</v>
       </c>
       <c r="R23" t="n">
-        <v>6958216</v>
+        <v>6958514</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3472,6 +3438,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3524,10 +3495,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317721</v>
+        <v>130317714</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>80316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,34 +3506,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507071</v>
+        <v>506876</v>
       </c>
       <c r="R24" t="n">
-        <v>6958280</v>
+        <v>6958216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3603,8 +3577,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3621,10 +3621,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130317670</v>
+        <v>130317701</v>
       </c>
       <c r="B25" t="n">
-        <v>58011</v>
+        <v>80316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3632,50 +3632,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506867</v>
+        <v>506872</v>
       </c>
       <c r="R25" t="n">
-        <v>6958649</v>
+        <v>6958352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3710,18 +3697,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3739,10 +3752,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130317701</v>
+        <v>130317670</v>
       </c>
       <c r="B26" t="n">
-        <v>80314</v>
+        <v>58013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3750,37 +3763,50 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506872</v>
+        <v>506867</v>
       </c>
       <c r="R26" t="n">
-        <v>6958352</v>
+        <v>6958649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3815,44 +3841,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På en björkhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B27" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R27" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,22 +3968,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4001,10 +3996,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317726</v>
+        <v>130317689</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>80316</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4012,21 +4007,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4039,10 +4034,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507008</v>
+        <v>506962</v>
       </c>
       <c r="R28" t="n">
-        <v>6958564</v>
+        <v>6958547</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +4074,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4099,17 +4094,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
         <v>130317700</v>
       </c>
       <c r="B29" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>130317679</v>
       </c>
       <c r="B30" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>130317681</v>
       </c>
       <c r="B31" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>130317661</v>
       </c>
       <c r="B32" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317688</v>
+        <v>130317724</v>
       </c>
       <c r="B33" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507005</v>
+        <v>506880</v>
       </c>
       <c r="R33" t="n">
-        <v>6958516</v>
+        <v>6958273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4730,11 +4730,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4752,22 +4747,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4785,10 +4775,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317680</v>
+        <v>130317688</v>
       </c>
       <c r="B34" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4823,10 +4813,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506984</v>
+        <v>507005</v>
       </c>
       <c r="R34" t="n">
-        <v>6958243</v>
+        <v>6958516</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4863,7 +4853,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4916,10 +4906,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317713</v>
+        <v>130317680</v>
       </c>
       <c r="B35" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4954,10 +4944,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506868</v>
+        <v>506984</v>
       </c>
       <c r="R35" t="n">
-        <v>6958334</v>
+        <v>6958243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4984,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +5004,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5047,10 +5037,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317677</v>
+        <v>130317713</v>
       </c>
       <c r="B36" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507084</v>
+        <v>506868</v>
       </c>
       <c r="R36" t="n">
-        <v>6958173</v>
+        <v>6958334</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5125,7 +5115,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5145,22 +5135,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5178,10 +5168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317724</v>
+        <v>130317677</v>
       </c>
       <c r="B37" t="n">
-        <v>79209</v>
+        <v>80316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5189,21 +5179,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5216,10 +5206,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506880</v>
+        <v>507084</v>
       </c>
       <c r="R37" t="n">
-        <v>6958273</v>
+        <v>6958173</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5254,6 +5244,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På grenar av gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5279,9 +5274,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317723</v>
+        <v>130317722</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506907</v>
+        <v>507004</v>
       </c>
       <c r="R38" t="n">
-        <v>6958328</v>
+        <v>6958523</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5388,21 +5388,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5420,10 +5405,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317708</v>
+        <v>130317723</v>
       </c>
       <c r="B39" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5431,21 +5416,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5458,10 +5443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507136</v>
+        <v>506907</v>
       </c>
       <c r="R39" t="n">
-        <v>6958243</v>
+        <v>6958328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5496,11 +5481,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5518,22 +5498,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5554,7 +5529,7 @@
         <v>130317653</v>
       </c>
       <c r="B40" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5681,10 +5656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317722</v>
+        <v>130317708</v>
       </c>
       <c r="B41" t="n">
-        <v>79209</v>
+        <v>80316</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5692,21 +5667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5719,10 +5694,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507004</v>
+        <v>507136</v>
       </c>
       <c r="R41" t="n">
-        <v>6958523</v>
+        <v>6958243</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5757,6 +5732,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5770,6 +5750,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5787,10 +5787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317673</v>
+        <v>130317674</v>
       </c>
       <c r="B42" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507049</v>
+        <v>506871</v>
       </c>
       <c r="R42" t="n">
-        <v>6958259</v>
+        <v>6958417</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5885,6 +5885,21 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5902,10 +5917,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317674</v>
+        <v>130317673</v>
       </c>
       <c r="B43" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5945,10 +5960,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506871</v>
+        <v>507049</v>
       </c>
       <c r="R43" t="n">
-        <v>6958417</v>
+        <v>6958259</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6000,21 +6015,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317683</v>
+        <v>130317728</v>
       </c>
       <c r="B44" t="n">
-        <v>80314</v>
+        <v>83057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507090</v>
+        <v>506918</v>
       </c>
       <c r="R44" t="n">
-        <v>6958314</v>
+        <v>6958323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,11 +6108,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6130,22 +6125,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6163,10 +6153,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317657</v>
+        <v>130317727</v>
       </c>
       <c r="B45" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6174,31 +6164,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6206,10 +6191,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506890</v>
+        <v>506867</v>
       </c>
       <c r="R45" t="n">
-        <v>6958493</v>
+        <v>6958649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6244,38 +6229,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6293,10 +6259,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317728</v>
+        <v>130317694</v>
       </c>
       <c r="B46" t="n">
-        <v>83055</v>
+        <v>80316</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6304,21 +6270,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6331,10 +6297,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506918</v>
+        <v>506910</v>
       </c>
       <c r="R46" t="n">
-        <v>6958323</v>
+        <v>6958533</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6369,6 +6335,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6386,17 +6357,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6414,10 +6390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317694</v>
+        <v>130317683</v>
       </c>
       <c r="B47" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6452,10 +6428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506910</v>
+        <v>507090</v>
       </c>
       <c r="R47" t="n">
-        <v>6958533</v>
+        <v>6958314</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6545,10 +6521,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317727</v>
+        <v>130317657</v>
       </c>
       <c r="B48" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6556,26 +6532,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6583,10 +6564,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506867</v>
+        <v>506890</v>
       </c>
       <c r="R48" t="n">
-        <v>6958649</v>
+        <v>6958493</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6621,19 +6602,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6654,7 +6654,7 @@
         <v>130317719</v>
       </c>
       <c r="B49" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>130317699</v>
       </c>
       <c r="B51" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>130317675</v>
       </c>
       <c r="B52" t="n">
-        <v>56425</v>
+        <v>56427</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>130317660</v>
       </c>
       <c r="B55" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>130317692</v>
       </c>
       <c r="B56" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>130317668</v>
       </c>
       <c r="B57" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317682</v>
+        <v>130317650</v>
       </c>
       <c r="B4" t="n">
-        <v>80316</v>
+        <v>83191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,30 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507013</v>
+        <v>506870</v>
       </c>
       <c r="R4" t="n">
-        <v>6958267</v>
+        <v>6958284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,11 +1017,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,22 +1034,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317697</v>
+        <v>130317682</v>
       </c>
       <c r="B5" t="n">
         <v>80316</v>
@@ -1106,7 +1092,11 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1114,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506897</v>
+        <v>507013</v>
       </c>
       <c r="R5" t="n">
-        <v>6958467</v>
+        <v>6958267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,10 +1197,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317650</v>
+        <v>130317697</v>
       </c>
       <c r="B6" t="n">
-        <v>83191</v>
+        <v>80316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,21 +1208,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506870</v>
+        <v>506897</v>
       </c>
       <c r="R6" t="n">
-        <v>6958284</v>
+        <v>6958467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1283,6 +1273,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1300,17 +1295,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317658</v>
+        <v>130317671</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>58013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,42 +1732,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506930</v>
+        <v>506956</v>
       </c>
       <c r="R10" t="n">
-        <v>6958447</v>
+        <v>6958085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,11 +1810,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1819,21 +1822,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,10 +1839,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317671</v>
+        <v>130317658</v>
       </c>
       <c r="B11" t="n">
-        <v>58013</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,50 +1850,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506956</v>
+        <v>506930</v>
       </c>
       <c r="R11" t="n">
-        <v>6958085</v>
+        <v>6958447</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,6 +1920,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1952,6 +1937,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317721</v>
+        <v>130317695</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,34 +3278,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507071</v>
+        <v>506917</v>
       </c>
       <c r="R22" t="n">
-        <v>6958280</v>
+        <v>6958514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3340,14 +3343,45 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3364,7 +3398,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317695</v>
+        <v>130317714</v>
       </c>
       <c r="B23" t="n">
         <v>80316</v>
@@ -3402,10 +3436,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506917</v>
+        <v>506876</v>
       </c>
       <c r="R23" t="n">
-        <v>6958514</v>
+        <v>6958216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,11 +3472,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3495,10 +3524,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317714</v>
+        <v>130317721</v>
       </c>
       <c r="B24" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3506,37 +3535,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506876</v>
+        <v>507071</v>
       </c>
       <c r="R24" t="n">
-        <v>6958216</v>
+        <v>6958280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3577,34 +3603,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317726</v>
+        <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507008</v>
+        <v>506962</v>
       </c>
       <c r="R27" t="n">
-        <v>6958564</v>
+        <v>6958547</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,17 +3968,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3996,10 +4001,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B28" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4007,21 +4012,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4034,10 +4039,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R28" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4074,7 +4079,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4094,22 +4099,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317724</v>
+        <v>130317688</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506880</v>
+        <v>507005</v>
       </c>
       <c r="R33" t="n">
-        <v>6958273</v>
+        <v>6958516</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4730,6 +4730,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4747,17 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4775,7 +4785,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317688</v>
+        <v>130317680</v>
       </c>
       <c r="B34" t="n">
         <v>80316</v>
@@ -4813,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507005</v>
+        <v>506984</v>
       </c>
       <c r="R34" t="n">
-        <v>6958516</v>
+        <v>6958243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4853,7 +4863,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4906,7 +4916,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317680</v>
+        <v>130317713</v>
       </c>
       <c r="B35" t="n">
         <v>80316</v>
@@ -4944,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506984</v>
+        <v>506868</v>
       </c>
       <c r="R35" t="n">
-        <v>6958243</v>
+        <v>6958334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4984,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5004,22 +5014,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5037,7 +5047,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317713</v>
+        <v>130317677</v>
       </c>
       <c r="B36" t="n">
         <v>80316</v>
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506868</v>
+        <v>507084</v>
       </c>
       <c r="R36" t="n">
-        <v>6958334</v>
+        <v>6958173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5115,7 +5125,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5135,22 +5145,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317677</v>
+        <v>130317724</v>
       </c>
       <c r="B37" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5179,21 +5189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5206,10 +5216,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507084</v>
+        <v>506880</v>
       </c>
       <c r="R37" t="n">
-        <v>6958173</v>
+        <v>6958273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5244,11 +5254,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På grenar av gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5274,14 +5279,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317722</v>
+        <v>130317673</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,26 +5310,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5337,10 +5342,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507004</v>
+        <v>507049</v>
       </c>
       <c r="R38" t="n">
-        <v>6958523</v>
+        <v>6958259</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5375,13 +5380,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5405,10 +5414,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317723</v>
+        <v>130317674</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5416,26 +5425,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5443,10 +5457,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506907</v>
+        <v>506871</v>
       </c>
       <c r="R39" t="n">
-        <v>6958328</v>
+        <v>6958417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5481,13 +5495,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5656,10 +5674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317708</v>
+        <v>130317722</v>
       </c>
       <c r="B41" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5667,21 +5685,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5694,10 +5712,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507136</v>
+        <v>507004</v>
       </c>
       <c r="R41" t="n">
-        <v>6958243</v>
+        <v>6958523</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5732,11 +5750,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5763,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5787,10 +5780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317674</v>
+        <v>130317723</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5798,31 +5791,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5830,10 +5818,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506871</v>
+        <v>506907</v>
       </c>
       <c r="R42" t="n">
-        <v>6958417</v>
+        <v>6958328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5868,17 +5856,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5917,10 +5901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317673</v>
+        <v>130317708</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>80316</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5928,31 +5912,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5960,10 +5939,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507049</v>
+        <v>507136</v>
       </c>
       <c r="R43" t="n">
-        <v>6958259</v>
+        <v>6958243</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6000,7 +5979,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>På liggande död sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6009,12 +5988,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,37 +6032,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317728</v>
+        <v>130317719</v>
       </c>
       <c r="B44" t="n">
-        <v>83057</v>
+        <v>98957</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6070,10 +6083,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506918</v>
+        <v>506940</v>
       </c>
       <c r="R44" t="n">
-        <v>6958323</v>
+        <v>6958101</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,6 +6121,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6121,21 +6139,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6153,10 +6156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317727</v>
+        <v>130317694</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,21 +6167,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6191,10 +6194,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506867</v>
+        <v>506910</v>
       </c>
       <c r="R45" t="n">
-        <v>6958649</v>
+        <v>6958533</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6229,6 +6232,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6242,6 +6250,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6259,10 +6287,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317694</v>
+        <v>130317727</v>
       </c>
       <c r="B46" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6270,21 +6298,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6297,10 +6325,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506910</v>
+        <v>506867</v>
       </c>
       <c r="R46" t="n">
-        <v>6958533</v>
+        <v>6958649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6335,11 +6363,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6353,26 +6376,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6651,50 +6654,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317719</v>
+        <v>130317728</v>
       </c>
       <c r="B49" t="n">
-        <v>98953</v>
+        <v>83057</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6702,10 +6692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506940</v>
+        <v>506918</v>
       </c>
       <c r="R49" t="n">
-        <v>6958101</v>
+        <v>6958323</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6740,11 +6730,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6758,6 +6743,21 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317711</v>
+        <v>130317675</v>
       </c>
       <c r="B50" t="n">
-        <v>80316</v>
+        <v>56427</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,37 +6786,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506964</v>
+        <v>507115</v>
       </c>
       <c r="R50" t="n">
-        <v>6958502</v>
+        <v>6958267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6857,33 +6870,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6901,7 +6893,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317699</v>
+        <v>130317711</v>
       </c>
       <c r="B51" t="n">
         <v>80316</v>
@@ -6931,11 +6923,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6943,10 +6931,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506945</v>
+        <v>506964</v>
       </c>
       <c r="R51" t="n">
-        <v>6958463</v>
+        <v>6958502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6979,11 +6967,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7036,10 +7019,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317675</v>
+        <v>130317699</v>
       </c>
       <c r="B52" t="n">
-        <v>56427</v>
+        <v>80316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7047,50 +7030,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507115</v>
+        <v>506945</v>
       </c>
       <c r="R52" t="n">
-        <v>6958267</v>
+        <v>6958463</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7125,18 +7099,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317650</v>
+        <v>130317682</v>
       </c>
       <c r="B4" t="n">
-        <v>83191</v>
+        <v>80316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,26 +952,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506870</v>
+        <v>507013</v>
       </c>
       <c r="R4" t="n">
-        <v>6958284</v>
+        <v>6958267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +1021,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1034,17 +1043,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317682</v>
+        <v>130317650</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>83191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,30 +1087,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507013</v>
+        <v>506870</v>
       </c>
       <c r="R5" t="n">
-        <v>6958267</v>
+        <v>6958284</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,11 +1152,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1164,22 +1169,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317671</v>
+        <v>130317658</v>
       </c>
       <c r="B10" t="n">
-        <v>58013</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,50 +1732,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506956</v>
+        <v>506930</v>
       </c>
       <c r="R10" t="n">
-        <v>6958085</v>
+        <v>6958447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1810,6 +1802,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1822,6 +1819,21 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1839,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317658</v>
+        <v>130317671</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>58013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,42 +1862,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506930</v>
+        <v>506956</v>
       </c>
       <c r="R11" t="n">
-        <v>6958447</v>
+        <v>6958085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1920,11 +1940,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1937,21 +1952,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317695</v>
+        <v>130317721</v>
       </c>
       <c r="B22" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,37 +3278,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506917</v>
+        <v>507071</v>
       </c>
       <c r="R22" t="n">
-        <v>6958514</v>
+        <v>6958280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3343,45 +3340,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3398,7 +3364,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317714</v>
+        <v>130317695</v>
       </c>
       <c r="B23" t="n">
         <v>80316</v>
@@ -3436,10 +3402,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506876</v>
+        <v>506917</v>
       </c>
       <c r="R23" t="n">
-        <v>6958216</v>
+        <v>6958514</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3472,6 +3438,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3524,10 +3495,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317721</v>
+        <v>130317714</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,34 +3506,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507071</v>
+        <v>506876</v>
       </c>
       <c r="R24" t="n">
-        <v>6958280</v>
+        <v>6958216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3603,8 +3577,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3621,10 +3621,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130317701</v>
+        <v>130317670</v>
       </c>
       <c r="B25" t="n">
-        <v>80316</v>
+        <v>58013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3632,37 +3632,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506872</v>
+        <v>506867</v>
       </c>
       <c r="R25" t="n">
-        <v>6958352</v>
+        <v>6958649</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3697,44 +3710,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På en björkhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3752,10 +3739,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130317670</v>
+        <v>130317701</v>
       </c>
       <c r="B26" t="n">
-        <v>58013</v>
+        <v>80316</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3763,50 +3750,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506867</v>
+        <v>506872</v>
       </c>
       <c r="R26" t="n">
-        <v>6958649</v>
+        <v>6958352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3841,18 +3815,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B27" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R27" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,22 +3968,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4001,10 +3996,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317726</v>
+        <v>130317700</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4012,21 +4007,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4039,10 +4034,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507008</v>
+        <v>506928</v>
       </c>
       <c r="R28" t="n">
-        <v>6958564</v>
+        <v>6958456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +4074,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4099,17 +4094,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130317700</v>
+        <v>130317689</v>
       </c>
       <c r="B29" t="n">
         <v>80316</v>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506928</v>
+        <v>506962</v>
       </c>
       <c r="R29" t="n">
-        <v>6958456</v>
+        <v>6958547</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317688</v>
+        <v>130317724</v>
       </c>
       <c r="B33" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507005</v>
+        <v>506880</v>
       </c>
       <c r="R33" t="n">
-        <v>6958516</v>
+        <v>6958273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4730,11 +4730,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4752,22 +4747,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4785,7 +4775,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317680</v>
+        <v>130317688</v>
       </c>
       <c r="B34" t="n">
         <v>80316</v>
@@ -4823,10 +4813,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506984</v>
+        <v>507005</v>
       </c>
       <c r="R34" t="n">
-        <v>6958243</v>
+        <v>6958516</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4863,7 +4853,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4916,7 +4906,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317713</v>
+        <v>130317680</v>
       </c>
       <c r="B35" t="n">
         <v>80316</v>
@@ -4954,10 +4944,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506868</v>
+        <v>506984</v>
       </c>
       <c r="R35" t="n">
-        <v>6958334</v>
+        <v>6958243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4984,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +5004,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5047,7 +5037,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317677</v>
+        <v>130317713</v>
       </c>
       <c r="B36" t="n">
         <v>80316</v>
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507084</v>
+        <v>506868</v>
       </c>
       <c r="R36" t="n">
-        <v>6958173</v>
+        <v>6958334</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5125,7 +5115,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5145,22 +5135,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5178,10 +5168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317724</v>
+        <v>130317677</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5189,21 +5179,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5216,10 +5206,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506880</v>
+        <v>507084</v>
       </c>
       <c r="R37" t="n">
-        <v>6958273</v>
+        <v>6958173</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5254,6 +5244,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På grenar av gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5279,9 +5274,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317673</v>
+        <v>130317653</v>
       </c>
       <c r="B38" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,29 +5310,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5342,10 +5341,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507049</v>
+        <v>507079</v>
       </c>
       <c r="R38" t="n">
-        <v>6958259</v>
+        <v>6958339</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5380,23 +5379,39 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5414,10 +5429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317674</v>
+        <v>130317722</v>
       </c>
       <c r="B39" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5425,31 +5440,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5457,10 +5467,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506871</v>
+        <v>507004</v>
       </c>
       <c r="R39" t="n">
-        <v>6958417</v>
+        <v>6958523</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5495,38 +5505,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5544,10 +5535,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317653</v>
+        <v>130317723</v>
       </c>
       <c r="B40" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5555,30 +5546,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5586,10 +5573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507079</v>
+        <v>506907</v>
       </c>
       <c r="R40" t="n">
-        <v>6958339</v>
+        <v>6958328</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5649,14 +5636,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5674,10 +5656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317722</v>
+        <v>130317708</v>
       </c>
       <c r="B41" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5685,21 +5667,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5712,10 +5694,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507004</v>
+        <v>507136</v>
       </c>
       <c r="R41" t="n">
-        <v>6958523</v>
+        <v>6958243</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5750,6 +5732,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5763,6 +5750,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5780,10 +5787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317723</v>
+        <v>130317674</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5791,26 +5798,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5818,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506907</v>
+        <v>506871</v>
       </c>
       <c r="R42" t="n">
-        <v>6958328</v>
+        <v>6958417</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5856,13 +5868,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5901,10 +5917,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317708</v>
+        <v>130317673</v>
       </c>
       <c r="B43" t="n">
-        <v>80316</v>
+        <v>57851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5912,26 +5928,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5939,10 +5960,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507136</v>
+        <v>507049</v>
       </c>
       <c r="R43" t="n">
-        <v>6958243</v>
+        <v>6958259</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5979,7 +6000,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På liggande död sälg.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5988,33 +6009,12 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,50 +6032,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317719</v>
+        <v>130317728</v>
       </c>
       <c r="B44" t="n">
-        <v>98957</v>
+        <v>83057</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6083,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506940</v>
+        <v>506918</v>
       </c>
       <c r="R44" t="n">
-        <v>6958101</v>
+        <v>6958323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6121,11 +6108,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6139,6 +6121,21 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6156,10 +6153,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317694</v>
+        <v>130317727</v>
       </c>
       <c r="B45" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6167,21 +6164,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6194,10 +6191,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506910</v>
+        <v>506867</v>
       </c>
       <c r="R45" t="n">
-        <v>6958533</v>
+        <v>6958649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6232,11 +6229,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6250,26 +6242,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6287,10 +6259,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317727</v>
+        <v>130317694</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6298,21 +6270,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6325,10 +6297,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506867</v>
+        <v>506910</v>
       </c>
       <c r="R46" t="n">
-        <v>6958649</v>
+        <v>6958533</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6363,6 +6335,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6376,6 +6353,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6654,37 +6651,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317728</v>
+        <v>130317719</v>
       </c>
       <c r="B49" t="n">
-        <v>83057</v>
+        <v>98957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6692,10 +6702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506918</v>
+        <v>506940</v>
       </c>
       <c r="R49" t="n">
-        <v>6958323</v>
+        <v>6958101</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6730,6 +6740,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6743,21 +6758,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317675</v>
+        <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>56427</v>
+        <v>80316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,50 +6786,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507115</v>
+        <v>506964</v>
       </c>
       <c r="R50" t="n">
-        <v>6958267</v>
+        <v>6958502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6870,12 +6857,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6893,7 +6901,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317711</v>
+        <v>130317699</v>
       </c>
       <c r="B51" t="n">
         <v>80316</v>
@@ -6923,7 +6931,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6931,10 +6943,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506964</v>
+        <v>506945</v>
       </c>
       <c r="R51" t="n">
-        <v>6958502</v>
+        <v>6958463</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6967,6 +6979,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7019,10 +7036,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317699</v>
+        <v>130317675</v>
       </c>
       <c r="B52" t="n">
-        <v>80316</v>
+        <v>56427</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7030,41 +7047,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506945</v>
+        <v>507115</v>
       </c>
       <c r="R52" t="n">
-        <v>6958463</v>
+        <v>6958267</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7099,44 +7125,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317676</v>
+        <v>130317697</v>
       </c>
       <c r="B2" t="n">
         <v>80316</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507117</v>
+        <v>506897</v>
       </c>
       <c r="R2" t="n">
-        <v>6958267</v>
+        <v>6958467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en liggande död sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,12 +783,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317712</v>
+        <v>130317682</v>
       </c>
       <c r="B3" t="n">
         <v>80316</v>
@@ -838,7 +838,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506953</v>
+        <v>507013</v>
       </c>
       <c r="R3" t="n">
-        <v>6958498</v>
+        <v>6958267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,7 +941,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317682</v>
+        <v>130317712</v>
       </c>
       <c r="B4" t="n">
         <v>80316</v>
@@ -973,7 +973,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507013</v>
+        <v>506953</v>
       </c>
       <c r="R4" t="n">
-        <v>6958267</v>
+        <v>6958498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1197,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317697</v>
+        <v>130317676</v>
       </c>
       <c r="B6" t="n">
         <v>80316</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506897</v>
+        <v>507117</v>
       </c>
       <c r="R6" t="n">
-        <v>6958467</v>
+        <v>6958267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På en liggande död sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317702</v>
+        <v>130317658</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,26 +1339,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506880</v>
+        <v>506930</v>
       </c>
       <c r="R7" t="n">
-        <v>6958248</v>
+        <v>6958447</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,7 +1420,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1426,22 +1430,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1459,7 +1458,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317685</v>
+        <v>130317693</v>
       </c>
       <c r="B8" t="n">
         <v>80316</v>
@@ -1497,10 +1496,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507014</v>
+        <v>506874</v>
       </c>
       <c r="R8" t="n">
-        <v>6958455</v>
+        <v>6958543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1537,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1567,12 +1566,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,7 +1589,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317693</v>
+        <v>130317702</v>
       </c>
       <c r="B9" t="n">
         <v>80316</v>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506874</v>
+        <v>506880</v>
       </c>
       <c r="R9" t="n">
-        <v>6958543</v>
+        <v>6958248</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317658</v>
+        <v>130317685</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,31 +1731,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1764,10 +1758,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506930</v>
+        <v>507014</v>
       </c>
       <c r="R10" t="n">
-        <v>6958447</v>
+        <v>6958455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1798,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Lunglav på en död sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1813,6 +1807,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1823,17 +1818,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317696</v>
+        <v>130317687</v>
       </c>
       <c r="B12" t="n">
         <v>80316</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506892</v>
+        <v>507040</v>
       </c>
       <c r="R12" t="n">
-        <v>6958496</v>
+        <v>6958467</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2067,22 +2067,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,7 +2095,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317691</v>
+        <v>130317684</v>
       </c>
       <c r="B13" t="n">
         <v>80316</v>
@@ -2130,11 +2125,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2142,10 +2133,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506877</v>
+        <v>507008</v>
       </c>
       <c r="R13" t="n">
-        <v>6958613</v>
+        <v>6958401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2182,7 +2173,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,7 +2226,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317684</v>
+        <v>130317691</v>
       </c>
       <c r="B14" t="n">
         <v>80316</v>
@@ -2265,7 +2256,11 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2273,10 +2268,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507008</v>
+        <v>506877</v>
       </c>
       <c r="R14" t="n">
-        <v>6958401</v>
+        <v>6958613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2313,7 +2308,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2366,7 +2361,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317687</v>
+        <v>130317696</v>
       </c>
       <c r="B15" t="n">
         <v>80316</v>
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507040</v>
+        <v>506892</v>
       </c>
       <c r="R15" t="n">
-        <v>6958467</v>
+        <v>6958496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2439,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2464,17 +2459,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317698</v>
+        <v>130317659</v>
       </c>
       <c r="B16" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,26 +2503,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2530,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506953</v>
+        <v>506915</v>
       </c>
       <c r="R16" t="n">
-        <v>6958489</v>
+        <v>6958411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2584,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2594,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,7 +2622,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317709</v>
+        <v>130317698</v>
       </c>
       <c r="B17" t="n">
         <v>80316</v>
@@ -2661,10 +2660,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507063</v>
+        <v>506953</v>
       </c>
       <c r="R17" t="n">
-        <v>6958140</v>
+        <v>6958489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2885,10 +2884,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317659</v>
+        <v>130317709</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,31 +2895,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2928,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506915</v>
+        <v>507063</v>
       </c>
       <c r="R19" t="n">
-        <v>6958411</v>
+        <v>6958140</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2968,7 +2962,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,6 +2971,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2987,17 +2982,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317649</v>
+        <v>130317721</v>
       </c>
       <c r="B21" t="n">
-        <v>83191</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,37 +3157,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507053</v>
+        <v>507071</v>
       </c>
       <c r="R21" t="n">
-        <v>6958107</v>
+        <v>6958280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3228,29 +3225,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3267,10 +3243,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317721</v>
+        <v>130317695</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,34 +3254,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507071</v>
+        <v>506917</v>
       </c>
       <c r="R22" t="n">
-        <v>6958280</v>
+        <v>6958514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3340,14 +3319,45 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3364,7 +3374,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317695</v>
+        <v>130317714</v>
       </c>
       <c r="B23" t="n">
         <v>80316</v>
@@ -3402,10 +3412,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506917</v>
+        <v>506876</v>
       </c>
       <c r="R23" t="n">
-        <v>6958514</v>
+        <v>6958216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,11 +3448,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3495,10 +3500,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317714</v>
+        <v>130317649</v>
       </c>
       <c r="B24" t="n">
-        <v>80316</v>
+        <v>83191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3506,21 +3511,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3533,10 +3538,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506876</v>
+        <v>507053</v>
       </c>
       <c r="R24" t="n">
-        <v>6958216</v>
+        <v>6958107</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3588,22 +3593,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317726</v>
+        <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507008</v>
+        <v>506962</v>
       </c>
       <c r="R27" t="n">
-        <v>6958564</v>
+        <v>6958547</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,17 +3968,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4127,10 +4132,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B29" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4138,21 +4143,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4165,10 +4170,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R29" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4210,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4225,22 +4230,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317724</v>
+        <v>130317713</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506880</v>
+        <v>506868</v>
       </c>
       <c r="R33" t="n">
-        <v>6958273</v>
+        <v>6958334</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4730,6 +4730,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Lunglav på död stående björk.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4747,17 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4775,10 +4785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317688</v>
+        <v>130317724</v>
       </c>
       <c r="B34" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4786,21 +4796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4813,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507005</v>
+        <v>506880</v>
       </c>
       <c r="R34" t="n">
-        <v>6958516</v>
+        <v>6958273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4851,11 +4861,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4873,22 +4878,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5037,7 +5037,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317713</v>
+        <v>130317688</v>
       </c>
       <c r="B36" t="n">
         <v>80316</v>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506868</v>
+        <v>507005</v>
       </c>
       <c r="R36" t="n">
-        <v>6958334</v>
+        <v>6958516</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317728</v>
+        <v>130317683</v>
       </c>
       <c r="B44" t="n">
-        <v>83057</v>
+        <v>80316</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506918</v>
+        <v>507090</v>
       </c>
       <c r="R44" t="n">
-        <v>6958323</v>
+        <v>6958314</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,6 +6108,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6125,17 +6130,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6153,10 +6163,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317727</v>
+        <v>130317694</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,21 +6174,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6191,10 +6201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506867</v>
+        <v>506910</v>
       </c>
       <c r="R45" t="n">
-        <v>6958649</v>
+        <v>6958533</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6229,6 +6239,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6242,6 +6257,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6259,10 +6294,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317694</v>
+        <v>130317727</v>
       </c>
       <c r="B46" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6270,21 +6305,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6297,10 +6332,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506910</v>
+        <v>506867</v>
       </c>
       <c r="R46" t="n">
-        <v>6958533</v>
+        <v>6958649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6335,11 +6370,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6353,26 +6383,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6390,10 +6400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317683</v>
+        <v>130317657</v>
       </c>
       <c r="B47" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6401,26 +6411,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6428,10 +6443,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507090</v>
+        <v>506890</v>
       </c>
       <c r="R47" t="n">
-        <v>6958314</v>
+        <v>6958493</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6468,7 +6483,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6477,7 +6492,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6488,22 +6502,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6521,42 +6530,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317657</v>
+        <v>130317719</v>
       </c>
       <c r="B48" t="n">
-        <v>57854</v>
+        <v>98957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6564,10 +6581,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506890</v>
+        <v>506940</v>
       </c>
       <c r="R48" t="n">
-        <v>6958493</v>
+        <v>6958101</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6604,7 +6621,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6613,27 +6630,13 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6651,50 +6654,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317719</v>
+        <v>130317728</v>
       </c>
       <c r="B49" t="n">
-        <v>98957</v>
+        <v>83057</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6702,10 +6692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506940</v>
+        <v>506918</v>
       </c>
       <c r="R49" t="n">
-        <v>6958101</v>
+        <v>6958323</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6740,11 +6730,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6758,6 +6743,21 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317711</v>
+        <v>130317675</v>
       </c>
       <c r="B50" t="n">
-        <v>80316</v>
+        <v>56427</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,37 +6786,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506964</v>
+        <v>507115</v>
       </c>
       <c r="R50" t="n">
-        <v>6958502</v>
+        <v>6958267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6857,33 +6870,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6901,7 +6893,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317699</v>
+        <v>130317711</v>
       </c>
       <c r="B51" t="n">
         <v>80316</v>
@@ -6931,11 +6923,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6943,10 +6931,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506945</v>
+        <v>506964</v>
       </c>
       <c r="R51" t="n">
-        <v>6958463</v>
+        <v>6958502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6979,11 +6967,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7036,10 +7019,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317675</v>
+        <v>130317699</v>
       </c>
       <c r="B52" t="n">
-        <v>56427</v>
+        <v>80316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7047,50 +7030,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507115</v>
+        <v>506945</v>
       </c>
       <c r="R52" t="n">
-        <v>6958267</v>
+        <v>6958463</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7125,18 +7099,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>57854</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,26 +7165,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7192,10 +7197,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R53" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7230,19 +7235,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7260,10 +7284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B54" t="n">
-        <v>57854</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7271,31 +7295,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7303,10 +7322,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R54" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7341,38 +7360,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317697</v>
+        <v>130317650</v>
       </c>
       <c r="B2" t="n">
-        <v>80316</v>
+        <v>83191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506897</v>
+        <v>506870</v>
       </c>
       <c r="R2" t="n">
-        <v>6958467</v>
+        <v>6958284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -1076,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317650</v>
+        <v>130317676</v>
       </c>
       <c r="B5" t="n">
-        <v>83191</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,21 +1077,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1114,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506870</v>
+        <v>507117</v>
       </c>
       <c r="R5" t="n">
-        <v>6958284</v>
+        <v>6958267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,6 +1142,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1169,17 +1164,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317676</v>
+        <v>130317697</v>
       </c>
       <c r="B6" t="n">
         <v>80316</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507117</v>
+        <v>506897</v>
       </c>
       <c r="R6" t="n">
-        <v>6958267</v>
+        <v>6958467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en liggande död sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317693</v>
+        <v>130317671</v>
       </c>
       <c r="B8" t="n">
-        <v>80316</v>
+        <v>58013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,37 +1469,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506874</v>
+        <v>506956</v>
       </c>
       <c r="R8" t="n">
-        <v>6958543</v>
+        <v>6958085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,44 +1547,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1589,7 +1576,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317702</v>
+        <v>130317693</v>
       </c>
       <c r="B9" t="n">
         <v>80316</v>
@@ -1627,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506880</v>
+        <v>506874</v>
       </c>
       <c r="R9" t="n">
-        <v>6958248</v>
+        <v>6958543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1667,7 +1654,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,7 +1707,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317685</v>
+        <v>130317702</v>
       </c>
       <c r="B10" t="n">
         <v>80316</v>
@@ -1758,10 +1745,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507014</v>
+        <v>506880</v>
       </c>
       <c r="R10" t="n">
-        <v>6958455</v>
+        <v>6958248</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1798,7 +1785,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1828,12 +1815,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,10 +1838,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317671</v>
+        <v>130317685</v>
       </c>
       <c r="B11" t="n">
-        <v>58013</v>
+        <v>80316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,50 +1849,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506956</v>
+        <v>507014</v>
       </c>
       <c r="R11" t="n">
-        <v>6958085</v>
+        <v>6958455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,18 +1914,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lunglav på en död sälg.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317659</v>
+        <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,31 +2503,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2535,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506915</v>
+        <v>506953</v>
       </c>
       <c r="R16" t="n">
-        <v>6958411</v>
+        <v>6958489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2575,7 +2570,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,6 +2579,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2594,17 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2622,7 +2623,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317698</v>
+        <v>130317710</v>
       </c>
       <c r="B17" t="n">
         <v>80316</v>
@@ -2660,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506953</v>
+        <v>506973</v>
       </c>
       <c r="R17" t="n">
-        <v>6958489</v>
+        <v>6958484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2753,7 +2754,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317710</v>
+        <v>130317709</v>
       </c>
       <c r="B18" t="n">
         <v>80316</v>
@@ -2791,10 +2792,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506973</v>
+        <v>507063</v>
       </c>
       <c r="R18" t="n">
-        <v>6958484</v>
+        <v>6958140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317709</v>
+        <v>130317659</v>
       </c>
       <c r="B19" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2895,26 +2896,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2922,10 +2928,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507063</v>
+        <v>506915</v>
       </c>
       <c r="R19" t="n">
-        <v>6958140</v>
+        <v>6958411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2962,7 +2968,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2971,7 +2977,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2982,22 +2987,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130317670</v>
+        <v>130317701</v>
       </c>
       <c r="B25" t="n">
-        <v>58013</v>
+        <v>80316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3632,50 +3632,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506867</v>
+        <v>506872</v>
       </c>
       <c r="R25" t="n">
-        <v>6958649</v>
+        <v>6958352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3710,18 +3697,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3739,10 +3752,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130317701</v>
+        <v>130317670</v>
       </c>
       <c r="B26" t="n">
-        <v>80316</v>
+        <v>58013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3750,37 +3763,50 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506872</v>
+        <v>506867</v>
       </c>
       <c r="R26" t="n">
-        <v>6958352</v>
+        <v>6958649</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3815,44 +3841,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På en björkhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B27" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R27" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,22 +3968,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4001,7 +3996,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317700</v>
+        <v>130317689</v>
       </c>
       <c r="B28" t="n">
         <v>80316</v>
@@ -4039,10 +4034,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506928</v>
+        <v>506962</v>
       </c>
       <c r="R28" t="n">
-        <v>6958456</v>
+        <v>6958547</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +4074,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4132,10 +4127,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130317726</v>
+        <v>130317700</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4143,21 +4138,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4170,10 +4165,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507008</v>
+        <v>506928</v>
       </c>
       <c r="R29" t="n">
-        <v>6958564</v>
+        <v>6958456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4210,7 +4205,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4230,17 +4225,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317724</v>
+        <v>130317680</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506880</v>
+        <v>506984</v>
       </c>
       <c r="R34" t="n">
-        <v>6958273</v>
+        <v>6958243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4861,6 +4861,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4878,17 +4883,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4906,7 +4916,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317680</v>
+        <v>130317688</v>
       </c>
       <c r="B35" t="n">
         <v>80316</v>
@@ -4944,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506984</v>
+        <v>507005</v>
       </c>
       <c r="R35" t="n">
-        <v>6958243</v>
+        <v>6958516</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4984,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5037,7 +5047,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317688</v>
+        <v>130317677</v>
       </c>
       <c r="B36" t="n">
         <v>80316</v>
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507005</v>
+        <v>507084</v>
       </c>
       <c r="R36" t="n">
-        <v>6958516</v>
+        <v>6958173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5115,7 +5125,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5135,22 +5145,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317677</v>
+        <v>130317724</v>
       </c>
       <c r="B37" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5179,21 +5189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5206,10 +5216,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507084</v>
+        <v>506880</v>
       </c>
       <c r="R37" t="n">
-        <v>6958173</v>
+        <v>6958273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5244,11 +5254,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På grenar av gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5274,14 +5279,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317653</v>
+        <v>130317674</v>
       </c>
       <c r="B38" t="n">
-        <v>91761</v>
+        <v>57851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,28 +5310,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5341,10 +5342,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507079</v>
+        <v>506871</v>
       </c>
       <c r="R38" t="n">
-        <v>6958339</v>
+        <v>6958417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5379,13 +5380,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5404,14 +5409,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317722</v>
+        <v>130317673</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5440,26 +5440,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5467,10 +5472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507004</v>
+        <v>507049</v>
       </c>
       <c r="R39" t="n">
-        <v>6958523</v>
+        <v>6958259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5505,13 +5510,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5535,10 +5544,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317723</v>
+        <v>130317653</v>
       </c>
       <c r="B40" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5546,26 +5555,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5573,10 +5586,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506907</v>
+        <v>507079</v>
       </c>
       <c r="R40" t="n">
-        <v>6958328</v>
+        <v>6958339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5636,9 +5649,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5656,10 +5674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317708</v>
+        <v>130317722</v>
       </c>
       <c r="B41" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5667,21 +5685,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5694,10 +5712,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507136</v>
+        <v>507004</v>
       </c>
       <c r="R41" t="n">
-        <v>6958243</v>
+        <v>6958523</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5732,11 +5750,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5750,26 +5763,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5787,10 +5780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317674</v>
+        <v>130317723</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5798,31 +5791,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5830,10 +5818,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506871</v>
+        <v>506907</v>
       </c>
       <c r="R42" t="n">
-        <v>6958417</v>
+        <v>6958328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5868,17 +5856,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5917,10 +5901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317673</v>
+        <v>130317708</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>80316</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5928,31 +5912,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5960,10 +5939,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507049</v>
+        <v>507136</v>
       </c>
       <c r="R43" t="n">
-        <v>6958259</v>
+        <v>6958243</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6000,7 +5979,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>På liggande död sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6009,12 +5988,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317683</v>
+        <v>130317657</v>
       </c>
       <c r="B44" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,26 +6043,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507090</v>
+        <v>506890</v>
       </c>
       <c r="R44" t="n">
-        <v>6958314</v>
+        <v>6958493</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6110,7 +6115,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6119,7 +6124,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6130,22 +6134,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6163,37 +6162,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317694</v>
+        <v>130317719</v>
       </c>
       <c r="B45" t="n">
-        <v>80316</v>
+        <v>98957</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6201,10 +6213,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506910</v>
+        <v>506940</v>
       </c>
       <c r="R45" t="n">
-        <v>6958533</v>
+        <v>6958101</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6241,7 +6253,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6257,26 +6269,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6400,10 +6392,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317657</v>
+        <v>130317728</v>
       </c>
       <c r="B47" t="n">
-        <v>57854</v>
+        <v>83057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6411,31 +6403,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6443,10 +6430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506890</v>
+        <v>506918</v>
       </c>
       <c r="R47" t="n">
-        <v>6958493</v>
+        <v>6958323</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6481,17 +6468,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6530,50 +6513,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317719</v>
+        <v>130317683</v>
       </c>
       <c r="B48" t="n">
-        <v>98957</v>
+        <v>80316</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6581,10 +6551,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506940</v>
+        <v>507090</v>
       </c>
       <c r="R48" t="n">
-        <v>6958101</v>
+        <v>6958314</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6621,7 +6591,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6637,6 +6607,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6654,10 +6644,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317728</v>
+        <v>130317694</v>
       </c>
       <c r="B49" t="n">
-        <v>83057</v>
+        <v>80316</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6665,21 +6655,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6692,10 +6682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506918</v>
+        <v>506910</v>
       </c>
       <c r="R49" t="n">
-        <v>6958323</v>
+        <v>6958533</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6730,6 +6720,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6747,17 +6742,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>57854</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,31 +7165,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7197,10 +7192,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R53" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7235,38 +7230,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7284,10 +7260,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>57854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7295,26 +7271,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7322,10 +7303,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R54" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7360,19 +7341,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317650</v>
+        <v>130317676</v>
       </c>
       <c r="B2" t="n">
-        <v>83191</v>
+        <v>80324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506870</v>
+        <v>507117</v>
       </c>
       <c r="R2" t="n">
-        <v>6958284</v>
+        <v>6958267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -768,17 +773,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317682</v>
+        <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,7 +838,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -838,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507013</v>
+        <v>506953</v>
       </c>
       <c r="R3" t="n">
-        <v>6958267</v>
+        <v>6958498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317712</v>
+        <v>130317650</v>
       </c>
       <c r="B4" t="n">
-        <v>80316</v>
+        <v>83199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,30 +952,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506953</v>
+        <v>506870</v>
       </c>
       <c r="R4" t="n">
-        <v>6958498</v>
+        <v>6958284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,11 +1017,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1033,22 +1034,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317676</v>
+        <v>130317682</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1092,11 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507117</v>
+        <v>507013</v>
       </c>
       <c r="R5" t="n">
         <v>6958267</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en liggande död sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
         <v>130317697</v>
       </c>
       <c r="B6" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>130317658</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317671</v>
+        <v>130317702</v>
       </c>
       <c r="B8" t="n">
-        <v>58013</v>
+        <v>80324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,50 +1469,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506956</v>
+        <v>506880</v>
       </c>
       <c r="R8" t="n">
-        <v>6958085</v>
+        <v>6958248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,18 +1534,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1576,10 +1589,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317693</v>
+        <v>130317685</v>
       </c>
       <c r="B9" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,10 +1627,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506874</v>
+        <v>507014</v>
       </c>
       <c r="R9" t="n">
-        <v>6958543</v>
+        <v>6958455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,7 +1667,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på en död sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1684,12 +1697,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1707,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317702</v>
+        <v>130317693</v>
       </c>
       <c r="B10" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1745,10 +1758,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506880</v>
+        <v>506874</v>
       </c>
       <c r="R10" t="n">
-        <v>6958248</v>
+        <v>6958543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1785,7 +1798,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1838,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317685</v>
+        <v>130317671</v>
       </c>
       <c r="B11" t="n">
-        <v>80316</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,37 +1862,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507014</v>
+        <v>506956</v>
       </c>
       <c r="R11" t="n">
-        <v>6958455</v>
+        <v>6958085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1914,44 +1940,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lunglav på en död sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317687</v>
+        <v>130317691</v>
       </c>
       <c r="B12" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,11 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2007,10 +2011,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507040</v>
+        <v>506877</v>
       </c>
       <c r="R12" t="n">
-        <v>6958467</v>
+        <v>6958613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2047,7 +2051,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2067,17 +2071,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2098,7 +2107,7 @@
         <v>130317684</v>
       </c>
       <c r="B13" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2226,10 +2235,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317691</v>
+        <v>130317687</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2256,11 +2265,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2268,10 +2273,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506877</v>
+        <v>507040</v>
       </c>
       <c r="R14" t="n">
-        <v>6958613</v>
+        <v>6958467</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2308,7 +2313,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,22 +2333,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
         <v>130317696</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317698</v>
+        <v>130317659</v>
       </c>
       <c r="B16" t="n">
-        <v>80316</v>
+        <v>57862</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,26 +2503,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2530,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506953</v>
+        <v>506915</v>
       </c>
       <c r="R16" t="n">
-        <v>6958489</v>
+        <v>6958411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2584,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2594,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,10 +2622,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317710</v>
+        <v>130317698</v>
       </c>
       <c r="B17" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,10 +2660,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506973</v>
+        <v>506953</v>
       </c>
       <c r="R17" t="n">
-        <v>6958484</v>
+        <v>6958489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2757,7 +2756,7 @@
         <v>130317709</v>
       </c>
       <c r="B18" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,10 +2884,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317659</v>
+        <v>130317710</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>80324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,31 +2895,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2928,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506915</v>
+        <v>506973</v>
       </c>
       <c r="R19" t="n">
-        <v>6958411</v>
+        <v>6958484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2968,7 +2962,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,6 +2971,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2987,17 +2982,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>130317678</v>
       </c>
       <c r="B20" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317721</v>
+        <v>130317649</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>83199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,34 +3157,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507071</v>
+        <v>507053</v>
       </c>
       <c r="R21" t="n">
-        <v>6958280</v>
+        <v>6958107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3225,8 +3228,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3246,7 +3270,7 @@
         <v>130317695</v>
       </c>
       <c r="B22" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3377,7 +3401,7 @@
         <v>130317714</v>
       </c>
       <c r="B23" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3500,10 +3524,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317649</v>
+        <v>130317721</v>
       </c>
       <c r="B24" t="n">
-        <v>83191</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3511,37 +3535,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507053</v>
+        <v>507071</v>
       </c>
       <c r="R24" t="n">
-        <v>6958107</v>
+        <v>6958280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3582,29 +3603,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3624,7 +3624,7 @@
         <v>130317701</v>
       </c>
       <c r="B25" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>130317670</v>
       </c>
       <c r="B26" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317726</v>
+        <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507008</v>
+        <v>506962</v>
       </c>
       <c r="R27" t="n">
-        <v>6958564</v>
+        <v>6958547</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,17 +3968,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3996,10 +4001,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B28" t="n">
-        <v>80316</v>
+        <v>79219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4007,21 +4012,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4034,10 +4039,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R28" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4074,7 +4079,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4094,22 +4099,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
         <v>130317700</v>
       </c>
       <c r="B29" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>130317679</v>
       </c>
       <c r="B30" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>130317681</v>
       </c>
       <c r="B31" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>130317661</v>
       </c>
       <c r="B32" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317713</v>
+        <v>130317677</v>
       </c>
       <c r="B33" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506868</v>
+        <v>507084</v>
       </c>
       <c r="R33" t="n">
-        <v>6958334</v>
+        <v>6958173</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317680</v>
+        <v>130317724</v>
       </c>
       <c r="B34" t="n">
-        <v>80316</v>
+        <v>79219</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506984</v>
+        <v>506880</v>
       </c>
       <c r="R34" t="n">
-        <v>6958243</v>
+        <v>6958273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4861,11 +4861,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4883,22 +4878,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4919,7 +4909,7 @@
         <v>130317688</v>
       </c>
       <c r="B35" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5047,10 +5037,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317677</v>
+        <v>130317680</v>
       </c>
       <c r="B36" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507084</v>
+        <v>506984</v>
       </c>
       <c r="R36" t="n">
-        <v>6958173</v>
+        <v>6958243</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5125,7 +5115,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5145,22 +5135,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5178,10 +5168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317724</v>
+        <v>130317713</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5189,21 +5179,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5216,10 +5206,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506880</v>
+        <v>506868</v>
       </c>
       <c r="R37" t="n">
-        <v>6958273</v>
+        <v>6958334</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5254,6 +5244,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lunglav på död stående björk.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5271,17 +5266,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317674</v>
+        <v>130317653</v>
       </c>
       <c r="B38" t="n">
-        <v>57851</v>
+        <v>91774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,29 +5310,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5342,10 +5341,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506871</v>
+        <v>507079</v>
       </c>
       <c r="R38" t="n">
-        <v>6958417</v>
+        <v>6958339</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5380,17 +5379,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5409,9 +5404,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317673</v>
+        <v>130317722</v>
       </c>
       <c r="B39" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5440,31 +5440,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5472,10 +5467,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507049</v>
+        <v>507004</v>
       </c>
       <c r="R39" t="n">
-        <v>6958259</v>
+        <v>6958523</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5510,17 +5505,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5544,10 +5535,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317653</v>
+        <v>130317673</v>
       </c>
       <c r="B40" t="n">
-        <v>91761</v>
+        <v>57859</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5555,28 +5546,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5586,10 +5578,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507079</v>
+        <v>507049</v>
       </c>
       <c r="R40" t="n">
-        <v>6958339</v>
+        <v>6958259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5624,39 +5616,23 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5674,10 +5650,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317722</v>
+        <v>130317708</v>
       </c>
       <c r="B41" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5685,21 +5661,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5712,10 +5688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507004</v>
+        <v>507136</v>
       </c>
       <c r="R41" t="n">
-        <v>6958523</v>
+        <v>6958243</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5750,6 +5726,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5763,6 +5744,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5783,7 +5784,7 @@
         <v>130317723</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5901,10 +5902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317708</v>
+        <v>130317674</v>
       </c>
       <c r="B43" t="n">
-        <v>80316</v>
+        <v>57859</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5912,26 +5913,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5939,10 +5945,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507136</v>
+        <v>506871</v>
       </c>
       <c r="R43" t="n">
-        <v>6958243</v>
+        <v>6958417</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5979,7 +5985,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På liggande död sälg.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5988,7 +5994,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5999,22 +6004,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317657</v>
+        <v>130317694</v>
       </c>
       <c r="B44" t="n">
-        <v>57854</v>
+        <v>80324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,31 +6043,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506890</v>
+        <v>506910</v>
       </c>
       <c r="R44" t="n">
-        <v>6958493</v>
+        <v>6958533</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6115,7 +6110,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6124,6 +6119,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6134,17 +6130,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6162,50 +6163,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317719</v>
+        <v>130317727</v>
       </c>
       <c r="B45" t="n">
-        <v>98957</v>
+        <v>79219</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6213,10 +6201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506940</v>
+        <v>506867</v>
       </c>
       <c r="R45" t="n">
-        <v>6958101</v>
+        <v>6958649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6249,11 +6237,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6286,10 +6269,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317727</v>
+        <v>130317683</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6297,21 +6280,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6324,10 +6307,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506867</v>
+        <v>507090</v>
       </c>
       <c r="R46" t="n">
-        <v>6958649</v>
+        <v>6958314</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6362,6 +6345,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6375,6 +6363,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6392,37 +6400,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317728</v>
+        <v>130317719</v>
       </c>
       <c r="B47" t="n">
-        <v>83057</v>
+        <v>98970</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6430,10 +6451,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506918</v>
+        <v>506940</v>
       </c>
       <c r="R47" t="n">
-        <v>6958323</v>
+        <v>6958101</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6468,6 +6489,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6481,21 +6507,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6513,10 +6524,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317683</v>
+        <v>130317728</v>
       </c>
       <c r="B48" t="n">
-        <v>80316</v>
+        <v>83065</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6524,21 +6535,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6551,10 +6562,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507090</v>
+        <v>506918</v>
       </c>
       <c r="R48" t="n">
-        <v>6958314</v>
+        <v>6958323</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6589,11 +6600,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6611,22 +6617,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6644,10 +6645,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317694</v>
+        <v>130317657</v>
       </c>
       <c r="B49" t="n">
-        <v>80316</v>
+        <v>57862</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6655,26 +6656,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6682,10 +6688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506910</v>
+        <v>506890</v>
       </c>
       <c r="R49" t="n">
-        <v>6958533</v>
+        <v>6958493</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6722,7 +6728,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6731,7 +6737,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6742,22 +6747,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317675</v>
+        <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>56427</v>
+        <v>80324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,50 +6786,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507115</v>
+        <v>506964</v>
       </c>
       <c r="R50" t="n">
-        <v>6958267</v>
+        <v>6958502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6870,12 +6857,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6893,10 +6901,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317711</v>
+        <v>130317699</v>
       </c>
       <c r="B51" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6923,7 +6931,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6931,10 +6943,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506964</v>
+        <v>506945</v>
       </c>
       <c r="R51" t="n">
-        <v>6958502</v>
+        <v>6958463</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6967,6 +6979,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7019,10 +7036,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317699</v>
+        <v>130317675</v>
       </c>
       <c r="B52" t="n">
-        <v>80316</v>
+        <v>56435</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7030,41 +7047,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506945</v>
+        <v>507115</v>
       </c>
       <c r="R52" t="n">
-        <v>6958463</v>
+        <v>6958267</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7099,44 +7125,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7157,7 +7157,7 @@
         <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>130317660</v>
       </c>
       <c r="B55" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>130317692</v>
       </c>
       <c r="B56" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>130317668</v>
       </c>
       <c r="B57" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317676</v>
       </c>
       <c r="B2" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>130317650</v>
       </c>
       <c r="B4" t="n">
-        <v>83199</v>
+        <v>83200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>130317682</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>130317697</v>
       </c>
       <c r="B6" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317658</v>
+        <v>130317702</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>80325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,31 +1339,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506930</v>
+        <v>506880</v>
       </c>
       <c r="R7" t="n">
-        <v>6958447</v>
+        <v>6958248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,6 +1415,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1430,17 +1426,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1458,10 +1459,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317702</v>
+        <v>130317685</v>
       </c>
       <c r="B8" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,10 +1497,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506880</v>
+        <v>507014</v>
       </c>
       <c r="R8" t="n">
-        <v>6958248</v>
+        <v>6958455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,7 +1537,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på en död sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,12 +1567,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1589,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317685</v>
+        <v>130317693</v>
       </c>
       <c r="B9" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,10 +1628,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507014</v>
+        <v>506874</v>
       </c>
       <c r="R9" t="n">
-        <v>6958455</v>
+        <v>6958543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1667,7 +1668,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,12 +1698,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1720,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317693</v>
+        <v>130317671</v>
       </c>
       <c r="B10" t="n">
-        <v>80324</v>
+        <v>58022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,37 +1732,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506874</v>
+        <v>506956</v>
       </c>
       <c r="R10" t="n">
-        <v>6958543</v>
+        <v>6958085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1796,44 +1810,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,10 +1839,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317671</v>
+        <v>130317658</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,50 +1850,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506956</v>
+        <v>506930</v>
       </c>
       <c r="R11" t="n">
-        <v>6958085</v>
+        <v>6958447</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,6 +1920,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1952,6 +1937,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317691</v>
+        <v>130317696</v>
       </c>
       <c r="B12" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,11 +1999,7 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2011,10 +2007,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506877</v>
+        <v>506892</v>
       </c>
       <c r="R12" t="n">
-        <v>6958613</v>
+        <v>6958496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2051,7 +2047,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2104,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317684</v>
+        <v>130317691</v>
       </c>
       <c r="B13" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2134,7 +2130,11 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507008</v>
+        <v>506877</v>
       </c>
       <c r="R13" t="n">
-        <v>6958401</v>
+        <v>6958613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,10 +2235,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317687</v>
+        <v>130317684</v>
       </c>
       <c r="B14" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507040</v>
+        <v>507008</v>
       </c>
       <c r="R14" t="n">
-        <v>6958467</v>
+        <v>6958401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2333,17 +2333,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2361,10 +2366,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317696</v>
+        <v>130317687</v>
       </c>
       <c r="B15" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2399,10 +2404,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506892</v>
+        <v>507040</v>
       </c>
       <c r="R15" t="n">
-        <v>6958496</v>
+        <v>6958467</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2439,7 +2444,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2459,22 +2464,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317659</v>
+        <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>57862</v>
+        <v>80325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,31 +2503,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2535,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506915</v>
+        <v>506953</v>
       </c>
       <c r="R16" t="n">
-        <v>6958411</v>
+        <v>6958489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2575,7 +2570,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,6 +2579,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2594,17 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2622,10 +2623,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317698</v>
+        <v>130317709</v>
       </c>
       <c r="B17" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2660,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506953</v>
+        <v>507063</v>
       </c>
       <c r="R17" t="n">
-        <v>6958489</v>
+        <v>6958140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2753,10 +2754,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317709</v>
+        <v>130317710</v>
       </c>
       <c r="B18" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2791,10 +2792,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507063</v>
+        <v>506973</v>
       </c>
       <c r="R18" t="n">
-        <v>6958140</v>
+        <v>6958484</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317710</v>
+        <v>130317659</v>
       </c>
       <c r="B19" t="n">
-        <v>80324</v>
+        <v>57863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2895,26 +2896,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2922,10 +2928,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506973</v>
+        <v>506915</v>
       </c>
       <c r="R19" t="n">
-        <v>6958484</v>
+        <v>6958411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2962,7 +2968,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2971,7 +2977,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2982,22 +2987,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>130317678</v>
       </c>
       <c r="B20" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317649</v>
+        <v>130317721</v>
       </c>
       <c r="B21" t="n">
-        <v>83199</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,37 +3157,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507053</v>
+        <v>507071</v>
       </c>
       <c r="R21" t="n">
-        <v>6958107</v>
+        <v>6958280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3228,29 +3225,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3267,10 +3243,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317695</v>
+        <v>130317649</v>
       </c>
       <c r="B22" t="n">
-        <v>80324</v>
+        <v>83200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,21 +3254,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3305,10 +3281,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506917</v>
+        <v>507053</v>
       </c>
       <c r="R22" t="n">
-        <v>6958514</v>
+        <v>6958107</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3343,11 +3319,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3365,22 +3336,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3398,10 +3364,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317714</v>
+        <v>130317695</v>
       </c>
       <c r="B23" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3436,10 +3402,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506876</v>
+        <v>506917</v>
       </c>
       <c r="R23" t="n">
-        <v>6958216</v>
+        <v>6958514</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3472,6 +3438,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3524,10 +3495,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317721</v>
+        <v>130317714</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3535,34 +3506,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507071</v>
+        <v>506876</v>
       </c>
       <c r="R24" t="n">
-        <v>6958280</v>
+        <v>6958216</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3603,8 +3577,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3624,7 +3624,7 @@
         <v>130317701</v>
       </c>
       <c r="B25" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>130317670</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>130317726</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>130317700</v>
       </c>
       <c r="B29" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>130317679</v>
       </c>
       <c r="B30" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>130317681</v>
       </c>
       <c r="B31" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>130317661</v>
       </c>
       <c r="B32" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317677</v>
+        <v>130317688</v>
       </c>
       <c r="B33" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507084</v>
+        <v>507005</v>
       </c>
       <c r="R33" t="n">
-        <v>6958173</v>
+        <v>6958516</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317724</v>
+        <v>130317713</v>
       </c>
       <c r="B34" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506880</v>
+        <v>506868</v>
       </c>
       <c r="R34" t="n">
-        <v>6958273</v>
+        <v>6958334</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4861,6 +4861,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Lunglav på död stående björk.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4878,17 +4883,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4906,10 +4916,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317688</v>
+        <v>130317677</v>
       </c>
       <c r="B35" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4944,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507005</v>
+        <v>507084</v>
       </c>
       <c r="R35" t="n">
-        <v>6958516</v>
+        <v>6958173</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4984,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5004,22 +5014,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5037,10 +5047,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317680</v>
+        <v>130317724</v>
       </c>
       <c r="B36" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5048,21 +5058,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506984</v>
+        <v>506880</v>
       </c>
       <c r="R36" t="n">
-        <v>6958243</v>
+        <v>6958273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5113,11 +5123,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5135,22 +5140,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317713</v>
+        <v>130317680</v>
       </c>
       <c r="B37" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506868</v>
+        <v>506984</v>
       </c>
       <c r="R37" t="n">
-        <v>6958334</v>
+        <v>6958243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5266,22 +5266,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5302,7 +5302,7 @@
         <v>130317653</v>
       </c>
       <c r="B38" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>130317722</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317673</v>
+        <v>130317723</v>
       </c>
       <c r="B40" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5546,31 +5546,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5578,10 +5573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507049</v>
+        <v>506907</v>
       </c>
       <c r="R40" t="n">
-        <v>6958259</v>
+        <v>6958328</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5616,23 +5611,34 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5653,7 +5659,7 @@
         <v>130317708</v>
       </c>
       <c r="B41" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5781,10 +5787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317723</v>
+        <v>130317674</v>
       </c>
       <c r="B42" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5792,26 +5798,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5819,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506907</v>
+        <v>506871</v>
       </c>
       <c r="R42" t="n">
-        <v>6958328</v>
+        <v>6958417</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5857,13 +5868,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5902,10 +5917,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317674</v>
+        <v>130317673</v>
       </c>
       <c r="B43" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5945,10 +5960,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506871</v>
+        <v>507049</v>
       </c>
       <c r="R43" t="n">
-        <v>6958417</v>
+        <v>6958259</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6000,21 +6015,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317694</v>
+        <v>130317728</v>
       </c>
       <c r="B44" t="n">
-        <v>80324</v>
+        <v>83066</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506910</v>
+        <v>506918</v>
       </c>
       <c r="R44" t="n">
-        <v>6958533</v>
+        <v>6958323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,11 +6108,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6130,22 +6125,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6166,7 +6156,7 @@
         <v>130317727</v>
       </c>
       <c r="B45" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6269,10 +6259,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317683</v>
+        <v>130317694</v>
       </c>
       <c r="B46" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6307,10 +6297,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507090</v>
+        <v>506910</v>
       </c>
       <c r="R46" t="n">
-        <v>6958314</v>
+        <v>6958533</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6400,50 +6390,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317719</v>
+        <v>130317683</v>
       </c>
       <c r="B47" t="n">
-        <v>98970</v>
+        <v>80325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6451,10 +6428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506940</v>
+        <v>507090</v>
       </c>
       <c r="R47" t="n">
-        <v>6958101</v>
+        <v>6958314</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6491,7 +6468,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6507,6 +6484,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6524,10 +6521,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317728</v>
+        <v>130317657</v>
       </c>
       <c r="B48" t="n">
-        <v>83065</v>
+        <v>57863</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6535,26 +6532,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6562,10 +6564,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506918</v>
+        <v>506890</v>
       </c>
       <c r="R48" t="n">
-        <v>6958323</v>
+        <v>6958493</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6600,13 +6602,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6645,42 +6651,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317657</v>
+        <v>130317719</v>
       </c>
       <c r="B49" t="n">
-        <v>57862</v>
+        <v>98971</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6688,10 +6702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506890</v>
+        <v>506940</v>
       </c>
       <c r="R49" t="n">
-        <v>6958493</v>
+        <v>6958101</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6728,7 +6742,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6737,27 +6751,13 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6778,7 +6778,7 @@
         <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>130317699</v>
       </c>
       <c r="B51" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>130317675</v>
       </c>
       <c r="B52" t="n">
-        <v>56435</v>
+        <v>56436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>130317660</v>
       </c>
       <c r="B55" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>130317692</v>
       </c>
       <c r="B56" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>130317668</v>
       </c>
       <c r="B57" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130317676</v>
       </c>
       <c r="B2" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130317712</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>130317650</v>
       </c>
       <c r="B4" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>130317682</v>
       </c>
       <c r="B5" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>130317697</v>
       </c>
       <c r="B6" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317702</v>
+        <v>130317658</v>
       </c>
       <c r="B7" t="n">
-        <v>80325</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,26 +1339,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506880</v>
+        <v>506930</v>
       </c>
       <c r="R7" t="n">
-        <v>6958248</v>
+        <v>6958447</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,7 +1420,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1426,22 +1430,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1459,10 +1458,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317685</v>
+        <v>130317671</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,37 +1469,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507014</v>
+        <v>506956</v>
       </c>
       <c r="R8" t="n">
-        <v>6958455</v>
+        <v>6958085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1535,44 +1547,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lunglav på en död sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,10 +1576,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317693</v>
+        <v>130317702</v>
       </c>
       <c r="B9" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1628,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506874</v>
+        <v>506880</v>
       </c>
       <c r="R9" t="n">
-        <v>6958543</v>
+        <v>6958248</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,7 +1654,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,10 +1707,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317671</v>
+        <v>130317685</v>
       </c>
       <c r="B10" t="n">
-        <v>58022</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,50 +1718,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506956</v>
+        <v>507014</v>
       </c>
       <c r="R10" t="n">
-        <v>6958085</v>
+        <v>6958455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1810,18 +1783,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lunglav på en död sälg.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1839,10 +1838,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317658</v>
+        <v>130317693</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>80326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,31 +1849,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1882,10 +1876,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506930</v>
+        <v>506874</v>
       </c>
       <c r="R11" t="n">
-        <v>6958447</v>
+        <v>6958543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1922,7 +1916,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,6 +1925,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1941,17 +1936,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>130317696</v>
       </c>
       <c r="B12" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>130317691</v>
       </c>
       <c r="B13" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>130317684</v>
       </c>
       <c r="B14" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>130317687</v>
       </c>
       <c r="B15" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>130317709</v>
       </c>
       <c r="B17" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>130317710</v>
       </c>
       <c r="B18" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>130317659</v>
       </c>
       <c r="B19" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>130317678</v>
       </c>
       <c r="B20" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>130317721</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>130317649</v>
       </c>
       <c r="B22" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>130317695</v>
       </c>
       <c r="B23" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>130317714</v>
       </c>
       <c r="B24" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>130317701</v>
       </c>
       <c r="B25" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>130317670</v>
       </c>
       <c r="B26" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B27" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R27" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,22 +3968,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4001,10 +3996,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317726</v>
+        <v>130317689</v>
       </c>
       <c r="B28" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4012,21 +4007,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4039,10 +4034,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507008</v>
+        <v>506962</v>
       </c>
       <c r="R28" t="n">
-        <v>6958564</v>
+        <v>6958547</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +4074,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4099,17 +4094,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
         <v>130317700</v>
       </c>
       <c r="B29" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130317679</v>
+        <v>130317681</v>
       </c>
       <c r="B30" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4288,11 +4288,7 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4300,10 +4296,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507027</v>
+        <v>506982</v>
       </c>
       <c r="R30" t="n">
-        <v>6958207</v>
+        <v>6958260</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4340,7 +4336,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4393,10 +4389,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130317681</v>
+        <v>130317679</v>
       </c>
       <c r="B31" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4423,7 +4419,11 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506982</v>
+        <v>507027</v>
       </c>
       <c r="R31" t="n">
-        <v>6958260</v>
+        <v>6958207</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4527,7 +4527,7 @@
         <v>130317661</v>
       </c>
       <c r="B32" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>130317688</v>
       </c>
       <c r="B33" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4785,10 +4785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317713</v>
+        <v>130317680</v>
       </c>
       <c r="B34" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506868</v>
+        <v>506984</v>
       </c>
       <c r="R34" t="n">
-        <v>6958334</v>
+        <v>6958243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317677</v>
+        <v>130317713</v>
       </c>
       <c r="B35" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507084</v>
+        <v>506868</v>
       </c>
       <c r="R35" t="n">
-        <v>6958173</v>
+        <v>6958334</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317724</v>
+        <v>130317677</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>80326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506880</v>
+        <v>507084</v>
       </c>
       <c r="R36" t="n">
-        <v>6958273</v>
+        <v>6958173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5123,6 +5123,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På grenar av gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5148,9 +5153,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5168,10 +5178,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317680</v>
+        <v>130317724</v>
       </c>
       <c r="B37" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5179,21 +5189,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5206,10 +5216,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506984</v>
+        <v>506880</v>
       </c>
       <c r="R37" t="n">
-        <v>6958243</v>
+        <v>6958273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5244,11 +5254,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5266,22 +5271,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317653</v>
+        <v>130317708</v>
       </c>
       <c r="B38" t="n">
-        <v>91775</v>
+        <v>80326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,30 +5310,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5341,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507079</v>
+        <v>507136</v>
       </c>
       <c r="R38" t="n">
-        <v>6958339</v>
+        <v>6958243</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5379,6 +5375,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5396,22 +5397,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5429,10 +5430,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317722</v>
+        <v>130317674</v>
       </c>
       <c r="B39" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5440,26 +5441,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5467,10 +5473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507004</v>
+        <v>506871</v>
       </c>
       <c r="R39" t="n">
-        <v>6958523</v>
+        <v>6958417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5505,19 +5511,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5535,10 +5560,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317723</v>
+        <v>130317673</v>
       </c>
       <c r="B40" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5546,26 +5571,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5573,10 +5603,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506907</v>
+        <v>507049</v>
       </c>
       <c r="R40" t="n">
-        <v>6958328</v>
+        <v>6958259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5611,34 +5641,23 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5656,10 +5675,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317708</v>
+        <v>130317653</v>
       </c>
       <c r="B41" t="n">
-        <v>80325</v>
+        <v>91776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5667,26 +5686,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5694,10 +5717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507136</v>
+        <v>507079</v>
       </c>
       <c r="R41" t="n">
-        <v>6958243</v>
+        <v>6958339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5732,11 +5755,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5754,22 +5772,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5787,10 +5805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317674</v>
+        <v>130317722</v>
       </c>
       <c r="B42" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5798,31 +5816,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5830,10 +5843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506871</v>
+        <v>507004</v>
       </c>
       <c r="R42" t="n">
-        <v>6958417</v>
+        <v>6958523</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5868,38 +5881,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5917,10 +5911,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317673</v>
+        <v>130317723</v>
       </c>
       <c r="B43" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5928,31 +5922,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5960,10 +5949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507049</v>
+        <v>506907</v>
       </c>
       <c r="R43" t="n">
-        <v>6958259</v>
+        <v>6958328</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5998,23 +5987,34 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,37 +6032,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317728</v>
+        <v>130317719</v>
       </c>
       <c r="B44" t="n">
-        <v>83066</v>
+        <v>98974</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6070,10 +6083,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506918</v>
+        <v>506940</v>
       </c>
       <c r="R44" t="n">
-        <v>6958323</v>
+        <v>6958101</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,6 +6121,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6121,21 +6139,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6153,10 +6156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317727</v>
+        <v>130317657</v>
       </c>
       <c r="B45" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,26 +6167,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6191,10 +6199,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506867</v>
+        <v>506890</v>
       </c>
       <c r="R45" t="n">
-        <v>6958649</v>
+        <v>6958493</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6229,19 +6237,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6259,10 +6286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317694</v>
+        <v>130317727</v>
       </c>
       <c r="B46" t="n">
-        <v>80325</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6270,21 +6297,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6297,10 +6324,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506910</v>
+        <v>506867</v>
       </c>
       <c r="R46" t="n">
-        <v>6958533</v>
+        <v>6958649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6335,11 +6362,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6353,26 +6375,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6390,10 +6392,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317683</v>
+        <v>130317694</v>
       </c>
       <c r="B47" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6428,10 +6430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507090</v>
+        <v>506910</v>
       </c>
       <c r="R47" t="n">
-        <v>6958314</v>
+        <v>6958533</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6521,10 +6523,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317657</v>
+        <v>130317683</v>
       </c>
       <c r="B48" t="n">
-        <v>57863</v>
+        <v>80326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6532,31 +6534,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6564,10 +6561,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506890</v>
+        <v>507090</v>
       </c>
       <c r="R48" t="n">
-        <v>6958493</v>
+        <v>6958314</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6604,7 +6601,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6613,6 +6610,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6623,17 +6621,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6651,50 +6654,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317719</v>
+        <v>130317728</v>
       </c>
       <c r="B49" t="n">
-        <v>98971</v>
+        <v>83067</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6702,10 +6692,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506940</v>
+        <v>506918</v>
       </c>
       <c r="R49" t="n">
-        <v>6958101</v>
+        <v>6958323</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6740,11 +6730,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6758,6 +6743,21 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317711</v>
+        <v>130317675</v>
       </c>
       <c r="B50" t="n">
-        <v>80325</v>
+        <v>56436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,37 +6786,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506964</v>
+        <v>507115</v>
       </c>
       <c r="R50" t="n">
-        <v>6958502</v>
+        <v>6958267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6857,33 +6870,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6901,10 +6893,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317699</v>
+        <v>130317711</v>
       </c>
       <c r="B51" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6931,11 +6923,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6943,10 +6931,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506945</v>
+        <v>506964</v>
       </c>
       <c r="R51" t="n">
-        <v>6958463</v>
+        <v>6958502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6979,11 +6967,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7036,10 +7019,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317675</v>
+        <v>130317699</v>
       </c>
       <c r="B52" t="n">
-        <v>56436</v>
+        <v>80326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7047,50 +7030,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507115</v>
+        <v>506945</v>
       </c>
       <c r="R52" t="n">
-        <v>6958267</v>
+        <v>6958463</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7125,18 +7099,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7157,7 +7157,7 @@
         <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>130317660</v>
       </c>
       <c r="B55" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>130317692</v>
       </c>
       <c r="B56" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>130317668</v>
       </c>
       <c r="B57" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317658</v>
+        <v>130317702</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,31 +1339,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506930</v>
+        <v>506880</v>
       </c>
       <c r="R7" t="n">
-        <v>6958447</v>
+        <v>6958248</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,6 +1415,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1430,17 +1426,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1458,10 +1459,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317671</v>
+        <v>130317685</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>80326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,50 +1470,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506956</v>
+        <v>507014</v>
       </c>
       <c r="R8" t="n">
-        <v>6958085</v>
+        <v>6958455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,18 +1535,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lunglav på en död sälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1576,7 +1590,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317702</v>
+        <v>130317693</v>
       </c>
       <c r="B9" t="n">
         <v>80326</v>
@@ -1614,10 +1628,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506880</v>
+        <v>506874</v>
       </c>
       <c r="R9" t="n">
-        <v>6958248</v>
+        <v>6958543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,7 +1668,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1707,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317685</v>
+        <v>130317658</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,26 +1732,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1745,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507014</v>
+        <v>506930</v>
       </c>
       <c r="R10" t="n">
-        <v>6958455</v>
+        <v>6958447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1785,7 +1804,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,7 +1813,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1805,22 +1823,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1838,10 +1851,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317693</v>
+        <v>130317671</v>
       </c>
       <c r="B11" t="n">
-        <v>80326</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,37 +1862,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506874</v>
+        <v>506956</v>
       </c>
       <c r="R11" t="n">
-        <v>6958543</v>
+        <v>6958085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1914,44 +1940,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317698</v>
+        <v>130317659</v>
       </c>
       <c r="B16" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,26 +2503,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2530,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506953</v>
+        <v>506915</v>
       </c>
       <c r="R16" t="n">
-        <v>6958489</v>
+        <v>6958411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2584,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2594,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,7 +2622,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317709</v>
+        <v>130317698</v>
       </c>
       <c r="B17" t="n">
         <v>80326</v>
@@ -2661,10 +2660,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507063</v>
+        <v>506953</v>
       </c>
       <c r="R17" t="n">
-        <v>6958140</v>
+        <v>6958489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2754,7 +2753,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317710</v>
+        <v>130317709</v>
       </c>
       <c r="B18" t="n">
         <v>80326</v>
@@ -2792,10 +2791,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506973</v>
+        <v>507063</v>
       </c>
       <c r="R18" t="n">
-        <v>6958484</v>
+        <v>6958140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2885,10 +2884,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317659</v>
+        <v>130317710</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,31 +2895,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2928,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506915</v>
+        <v>506973</v>
       </c>
       <c r="R19" t="n">
-        <v>6958411</v>
+        <v>6958484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2968,7 +2962,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,6 +2971,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2987,17 +2982,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317721</v>
+        <v>130317649</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>83201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,34 +3157,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507071</v>
+        <v>507053</v>
       </c>
       <c r="R21" t="n">
-        <v>6958280</v>
+        <v>6958107</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3225,8 +3228,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3243,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317649</v>
+        <v>130317695</v>
       </c>
       <c r="B22" t="n">
-        <v>83201</v>
+        <v>80326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3254,21 +3278,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3281,10 +3305,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507053</v>
+        <v>506917</v>
       </c>
       <c r="R22" t="n">
-        <v>6958107</v>
+        <v>6958514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3319,6 +3343,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3336,17 +3365,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3364,7 +3398,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317695</v>
+        <v>130317714</v>
       </c>
       <c r="B23" t="n">
         <v>80326</v>
@@ -3402,10 +3436,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506917</v>
+        <v>506876</v>
       </c>
       <c r="R23" t="n">
-        <v>6958514</v>
+        <v>6958216</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,11 +3472,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3495,10 +3524,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317714</v>
+        <v>130317721</v>
       </c>
       <c r="B24" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3506,37 +3535,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506876</v>
+        <v>507071</v>
       </c>
       <c r="R24" t="n">
-        <v>6958216</v>
+        <v>6958280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3577,34 +3603,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317726</v>
+        <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507008</v>
+        <v>506962</v>
       </c>
       <c r="R27" t="n">
-        <v>6958564</v>
+        <v>6958547</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,17 +3968,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3996,10 +4001,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B28" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4007,21 +4012,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4034,10 +4039,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R28" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4074,7 +4079,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4094,22 +4099,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130317681</v>
+        <v>130317679</v>
       </c>
       <c r="B30" t="n">
         <v>80326</v>
@@ -4288,7 +4288,11 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4296,10 +4300,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506982</v>
+        <v>507027</v>
       </c>
       <c r="R30" t="n">
-        <v>6958260</v>
+        <v>6958207</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4336,7 +4340,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4389,7 +4393,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130317679</v>
+        <v>130317681</v>
       </c>
       <c r="B31" t="n">
         <v>80326</v>
@@ -4419,11 +4423,7 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507027</v>
+        <v>506982</v>
       </c>
       <c r="R31" t="n">
-        <v>6958207</v>
+        <v>6958260</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317708</v>
+        <v>130317674</v>
       </c>
       <c r="B38" t="n">
-        <v>80326</v>
+        <v>57861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,26 +5310,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5337,10 +5342,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507136</v>
+        <v>506871</v>
       </c>
       <c r="R38" t="n">
-        <v>6958243</v>
+        <v>6958417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5377,7 +5382,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På liggande död sälg.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5386,7 +5391,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5397,22 +5401,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5430,7 +5429,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317674</v>
+        <v>130317673</v>
       </c>
       <c r="B39" t="n">
         <v>57861</v>
@@ -5473,10 +5472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506871</v>
+        <v>507049</v>
       </c>
       <c r="R39" t="n">
-        <v>6958417</v>
+        <v>6958259</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5528,21 +5527,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5560,10 +5544,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317673</v>
+        <v>130317653</v>
       </c>
       <c r="B40" t="n">
-        <v>57861</v>
+        <v>91776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5571,29 +5555,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5603,10 +5586,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507049</v>
+        <v>507079</v>
       </c>
       <c r="R40" t="n">
-        <v>6958259</v>
+        <v>6958339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5641,23 +5624,39 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5675,10 +5674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317653</v>
+        <v>130317722</v>
       </c>
       <c r="B41" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5686,30 +5685,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5717,10 +5712,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507079</v>
+        <v>507004</v>
       </c>
       <c r="R41" t="n">
-        <v>6958339</v>
+        <v>6958523</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5768,26 +5763,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5805,7 +5780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317722</v>
+        <v>130317723</v>
       </c>
       <c r="B42" t="n">
         <v>79221</v>
@@ -5843,10 +5818,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507004</v>
+        <v>506907</v>
       </c>
       <c r="R42" t="n">
-        <v>6958523</v>
+        <v>6958328</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5894,6 +5869,21 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5911,10 +5901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317723</v>
+        <v>130317708</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5922,21 +5912,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5949,10 +5939,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506907</v>
+        <v>507136</v>
       </c>
       <c r="R43" t="n">
-        <v>6958328</v>
+        <v>6958243</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5987,6 +5977,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6004,17 +5999,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,50 +6032,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317719</v>
+        <v>130317728</v>
       </c>
       <c r="B44" t="n">
-        <v>98974</v>
+        <v>83067</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6083,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506940</v>
+        <v>506918</v>
       </c>
       <c r="R44" t="n">
-        <v>6958101</v>
+        <v>6958323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6121,11 +6108,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6139,6 +6121,21 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6156,10 +6153,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317657</v>
+        <v>130317694</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6167,31 +6164,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6199,10 +6191,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506890</v>
+        <v>506910</v>
       </c>
       <c r="R45" t="n">
-        <v>6958493</v>
+        <v>6958533</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6239,7 +6231,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6248,6 +6240,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6258,17 +6251,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6392,7 +6390,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317694</v>
+        <v>130317683</v>
       </c>
       <c r="B47" t="n">
         <v>80326</v>
@@ -6430,10 +6428,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506910</v>
+        <v>507090</v>
       </c>
       <c r="R47" t="n">
-        <v>6958533</v>
+        <v>6958314</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6523,10 +6521,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317683</v>
+        <v>130317657</v>
       </c>
       <c r="B48" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6534,26 +6532,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6561,10 +6564,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>507090</v>
+        <v>506890</v>
       </c>
       <c r="R48" t="n">
-        <v>6958314</v>
+        <v>6958493</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6601,7 +6604,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6610,7 +6613,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6621,22 +6623,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6654,37 +6651,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317728</v>
+        <v>130317719</v>
       </c>
       <c r="B49" t="n">
-        <v>83067</v>
+        <v>98974</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6692,10 +6702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506918</v>
+        <v>506940</v>
       </c>
       <c r="R49" t="n">
-        <v>6958323</v>
+        <v>6958101</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6730,6 +6740,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6743,21 +6758,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317675</v>
+        <v>130317711</v>
       </c>
       <c r="B50" t="n">
-        <v>56436</v>
+        <v>80326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,50 +6786,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507115</v>
+        <v>506964</v>
       </c>
       <c r="R50" t="n">
-        <v>6958267</v>
+        <v>6958502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6870,12 +6857,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6893,7 +6901,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317711</v>
+        <v>130317699</v>
       </c>
       <c r="B51" t="n">
         <v>80326</v>
@@ -6923,7 +6931,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6931,10 +6943,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506964</v>
+        <v>506945</v>
       </c>
       <c r="R51" t="n">
-        <v>6958502</v>
+        <v>6958463</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6967,6 +6979,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7019,10 +7036,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317699</v>
+        <v>130317675</v>
       </c>
       <c r="B52" t="n">
-        <v>80326</v>
+        <v>56436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7030,41 +7047,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506945</v>
+        <v>507115</v>
       </c>
       <c r="R52" t="n">
-        <v>6958463</v>
+        <v>6958267</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7099,44 +7125,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317702</v>
+        <v>130317658</v>
       </c>
       <c r="B7" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,26 +1339,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1366,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506880</v>
+        <v>506930</v>
       </c>
       <c r="R7" t="n">
-        <v>6958248</v>
+        <v>6958447</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,7 +1411,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,7 +1420,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1426,22 +1430,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1459,7 +1458,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317685</v>
+        <v>130317702</v>
       </c>
       <c r="B8" t="n">
         <v>80326</v>
@@ -1497,10 +1496,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507014</v>
+        <v>506880</v>
       </c>
       <c r="R8" t="n">
-        <v>6958455</v>
+        <v>6958248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1537,7 +1536,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lunglav på en död sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1567,12 +1566,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,7 +1589,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317693</v>
+        <v>130317685</v>
       </c>
       <c r="B9" t="n">
         <v>80326</v>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506874</v>
+        <v>507014</v>
       </c>
       <c r="R9" t="n">
-        <v>6958543</v>
+        <v>6958455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på en död sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1698,12 +1697,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1721,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317658</v>
+        <v>130317693</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,31 +1731,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1764,10 +1758,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506930</v>
+        <v>506874</v>
       </c>
       <c r="R10" t="n">
-        <v>6958447</v>
+        <v>6958543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1798,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1813,6 +1807,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1823,17 +1818,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317659</v>
+        <v>130317698</v>
       </c>
       <c r="B16" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,31 +2503,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2535,10 +2530,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506915</v>
+        <v>506953</v>
       </c>
       <c r="R16" t="n">
-        <v>6958411</v>
+        <v>6958489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2575,7 +2570,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,6 +2579,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2594,17 +2590,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2622,7 +2623,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317698</v>
+        <v>130317709</v>
       </c>
       <c r="B17" t="n">
         <v>80326</v>
@@ -2660,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506953</v>
+        <v>507063</v>
       </c>
       <c r="R17" t="n">
-        <v>6958489</v>
+        <v>6958140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2753,7 +2754,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317709</v>
+        <v>130317710</v>
       </c>
       <c r="B18" t="n">
         <v>80326</v>
@@ -2791,10 +2792,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507063</v>
+        <v>506973</v>
       </c>
       <c r="R18" t="n">
-        <v>6958140</v>
+        <v>6958484</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317710</v>
+        <v>130317659</v>
       </c>
       <c r="B19" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2895,26 +2896,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2922,10 +2928,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506973</v>
+        <v>506915</v>
       </c>
       <c r="R19" t="n">
-        <v>6958484</v>
+        <v>6958411</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2962,7 +2968,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2971,7 +2977,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2982,22 +2987,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317674</v>
+        <v>130317673</v>
       </c>
       <c r="B38" t="n">
         <v>57861</v>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506871</v>
+        <v>507049</v>
       </c>
       <c r="R38" t="n">
-        <v>6958417</v>
+        <v>6958259</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5397,21 +5397,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5429,7 +5414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317673</v>
+        <v>130317674</v>
       </c>
       <c r="B39" t="n">
         <v>57861</v>
@@ -5472,10 +5457,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507049</v>
+        <v>506871</v>
       </c>
       <c r="R39" t="n">
-        <v>6958259</v>
+        <v>6958417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5527,6 +5512,21 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317653</v>
+        <v>130317722</v>
       </c>
       <c r="B40" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5555,30 +5555,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5586,10 +5582,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507079</v>
+        <v>507004</v>
       </c>
       <c r="R40" t="n">
-        <v>6958339</v>
+        <v>6958523</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5637,26 +5633,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5674,7 +5650,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317722</v>
+        <v>130317723</v>
       </c>
       <c r="B41" t="n">
         <v>79221</v>
@@ -5712,10 +5688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507004</v>
+        <v>506907</v>
       </c>
       <c r="R41" t="n">
-        <v>6958523</v>
+        <v>6958328</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5763,6 +5739,21 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5780,10 +5771,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317723</v>
+        <v>130317708</v>
       </c>
       <c r="B42" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5791,21 +5782,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5818,10 +5809,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>506907</v>
+        <v>507136</v>
       </c>
       <c r="R42" t="n">
-        <v>6958328</v>
+        <v>6958243</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5856,6 +5847,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5873,17 +5869,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5901,10 +5902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317708</v>
+        <v>130317653</v>
       </c>
       <c r="B43" t="n">
-        <v>80326</v>
+        <v>91776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5912,26 +5913,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5939,10 +5944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507136</v>
+        <v>507079</v>
       </c>
       <c r="R43" t="n">
-        <v>6958243</v>
+        <v>6958339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5977,11 +5982,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5999,22 +5999,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317694</v>
+        <v>130317657</v>
       </c>
       <c r="B45" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,26 +6164,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6191,10 +6196,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506910</v>
+        <v>506890</v>
       </c>
       <c r="R45" t="n">
-        <v>6958533</v>
+        <v>6958493</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6231,7 +6236,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6240,7 +6245,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6251,22 +6255,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6284,37 +6283,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317727</v>
+        <v>130317719</v>
       </c>
       <c r="B46" t="n">
-        <v>79221</v>
+        <v>98974</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6322,10 +6334,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506867</v>
+        <v>506940</v>
       </c>
       <c r="R46" t="n">
-        <v>6958649</v>
+        <v>6958101</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6358,6 +6370,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6390,7 +6407,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317683</v>
+        <v>130317694</v>
       </c>
       <c r="B47" t="n">
         <v>80326</v>
@@ -6428,10 +6445,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507090</v>
+        <v>506910</v>
       </c>
       <c r="R47" t="n">
-        <v>6958314</v>
+        <v>6958533</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6521,10 +6538,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317657</v>
+        <v>130317727</v>
       </c>
       <c r="B48" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6532,31 +6549,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6564,10 +6576,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506890</v>
+        <v>506867</v>
       </c>
       <c r="R48" t="n">
-        <v>6958493</v>
+        <v>6958649</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6602,38 +6614,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6651,50 +6644,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317719</v>
+        <v>130317683</v>
       </c>
       <c r="B49" t="n">
-        <v>98974</v>
+        <v>80326</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6702,10 +6682,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506940</v>
+        <v>507090</v>
       </c>
       <c r="R49" t="n">
-        <v>6958101</v>
+        <v>6958314</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6742,7 +6722,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6758,6 +6738,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317711</v>
+        <v>130317675</v>
       </c>
       <c r="B50" t="n">
-        <v>80326</v>
+        <v>56436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,37 +6786,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506964</v>
+        <v>507115</v>
       </c>
       <c r="R50" t="n">
-        <v>6958502</v>
+        <v>6958267</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6857,33 +6870,12 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6901,7 +6893,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317699</v>
+        <v>130317711</v>
       </c>
       <c r="B51" t="n">
         <v>80326</v>
@@ -6931,11 +6923,7 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6943,10 +6931,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506945</v>
+        <v>506964</v>
       </c>
       <c r="R51" t="n">
-        <v>6958463</v>
+        <v>6958502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6979,11 +6967,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7036,10 +7019,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317675</v>
+        <v>130317699</v>
       </c>
       <c r="B52" t="n">
-        <v>56436</v>
+        <v>80326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7047,50 +7030,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507115</v>
+        <v>506945</v>
       </c>
       <c r="R52" t="n">
-        <v>6958267</v>
+        <v>6958463</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7125,18 +7099,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B53" t="n">
-        <v>78978</v>
+        <v>57864</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,26 +7165,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7192,10 +7197,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R53" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7230,19 +7235,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7260,10 +7284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B54" t="n">
-        <v>57864</v>
+        <v>78978</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7271,31 +7295,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7303,10 +7322,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R54" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7341,38 +7360,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -2492,10 +2492,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317698</v>
+        <v>130317659</v>
       </c>
       <c r="B16" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2503,26 +2503,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2530,10 +2535,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506953</v>
+        <v>506915</v>
       </c>
       <c r="R16" t="n">
-        <v>6958489</v>
+        <v>6958411</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2575,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,7 +2584,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2590,22 +2594,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,7 +2622,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317709</v>
+        <v>130317698</v>
       </c>
       <c r="B17" t="n">
         <v>80326</v>
@@ -2661,10 +2660,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507063</v>
+        <v>506953</v>
       </c>
       <c r="R17" t="n">
-        <v>6958140</v>
+        <v>6958489</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2754,7 +2753,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317710</v>
+        <v>130317709</v>
       </c>
       <c r="B18" t="n">
         <v>80326</v>
@@ -2792,10 +2791,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506973</v>
+        <v>507063</v>
       </c>
       <c r="R18" t="n">
-        <v>6958484</v>
+        <v>6958140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2885,10 +2884,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317659</v>
+        <v>130317710</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,31 +2895,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2928,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506915</v>
+        <v>506973</v>
       </c>
       <c r="R19" t="n">
-        <v>6958411</v>
+        <v>6958484</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2968,7 +2962,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,6 +2971,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2987,17 +2982,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317673</v>
+        <v>130317722</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,31 +5310,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5342,10 +5337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507049</v>
+        <v>507004</v>
       </c>
       <c r="R38" t="n">
-        <v>6958259</v>
+        <v>6958523</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5380,17 +5375,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5405,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317674</v>
+        <v>130317723</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5425,31 +5416,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5457,10 +5443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506871</v>
+        <v>506907</v>
       </c>
       <c r="R39" t="n">
-        <v>6958417</v>
+        <v>6958328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5495,17 +5481,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5544,10 +5526,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317722</v>
+        <v>130317708</v>
       </c>
       <c r="B40" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5555,21 +5537,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5582,10 +5564,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507004</v>
+        <v>507136</v>
       </c>
       <c r="R40" t="n">
-        <v>6958523</v>
+        <v>6958243</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5620,6 +5602,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5633,6 +5620,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5650,10 +5657,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317723</v>
+        <v>130317653</v>
       </c>
       <c r="B41" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5661,26 +5668,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5688,10 +5699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>506907</v>
+        <v>507079</v>
       </c>
       <c r="R41" t="n">
-        <v>6958328</v>
+        <v>6958339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5751,9 +5762,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5771,10 +5787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317708</v>
+        <v>130317673</v>
       </c>
       <c r="B42" t="n">
-        <v>80326</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5782,26 +5798,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5809,10 +5830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507136</v>
+        <v>507049</v>
       </c>
       <c r="R42" t="n">
-        <v>6958243</v>
+        <v>6958259</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5849,7 +5870,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På liggande död sälg.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5858,33 +5879,12 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5902,10 +5902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317653</v>
+        <v>130317674</v>
       </c>
       <c r="B43" t="n">
-        <v>91776</v>
+        <v>57861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5913,28 +5913,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5944,10 +5945,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507079</v>
+        <v>506871</v>
       </c>
       <c r="R43" t="n">
-        <v>6958339</v>
+        <v>6958417</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5982,13 +5983,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6007,14 +6012,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317728</v>
+        <v>130317694</v>
       </c>
       <c r="B44" t="n">
-        <v>83067</v>
+        <v>80326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,21 +6043,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506918</v>
+        <v>506910</v>
       </c>
       <c r="R44" t="n">
-        <v>6958323</v>
+        <v>6958533</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,6 +6108,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6125,17 +6130,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6153,10 +6163,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317657</v>
+        <v>130317727</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6164,31 +6174,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6196,10 +6201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506890</v>
+        <v>506867</v>
       </c>
       <c r="R45" t="n">
-        <v>6958493</v>
+        <v>6958649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6234,38 +6239,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6283,50 +6269,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317719</v>
+        <v>130317683</v>
       </c>
       <c r="B46" t="n">
-        <v>98974</v>
+        <v>80326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6334,10 +6307,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506940</v>
+        <v>507090</v>
       </c>
       <c r="R46" t="n">
-        <v>6958101</v>
+        <v>6958314</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6374,7 +6347,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6390,6 +6363,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6407,10 +6400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317694</v>
+        <v>130317728</v>
       </c>
       <c r="B47" t="n">
-        <v>80326</v>
+        <v>83067</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6418,21 +6411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6445,10 +6438,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>506910</v>
+        <v>506918</v>
       </c>
       <c r="R47" t="n">
-        <v>6958533</v>
+        <v>6958323</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6483,11 +6476,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6505,22 +6493,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6538,10 +6521,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317727</v>
+        <v>130317657</v>
       </c>
       <c r="B48" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6549,26 +6532,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6576,10 +6564,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506867</v>
+        <v>506890</v>
       </c>
       <c r="R48" t="n">
-        <v>6958649</v>
+        <v>6958493</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6614,19 +6602,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6644,37 +6651,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317683</v>
+        <v>130317719</v>
       </c>
       <c r="B49" t="n">
-        <v>80326</v>
+        <v>98974</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6682,10 +6702,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507090</v>
+        <v>506940</v>
       </c>
       <c r="R49" t="n">
-        <v>6958314</v>
+        <v>6958101</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6722,7 +6742,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6738,26 +6758,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317655</v>
+        <v>130317717</v>
       </c>
       <c r="B53" t="n">
-        <v>57864</v>
+        <v>78978</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,31 +7165,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7197,10 +7192,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506974</v>
+        <v>506939</v>
       </c>
       <c r="R53" t="n">
-        <v>6958546</v>
+        <v>6958101</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7235,38 +7230,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7284,10 +7260,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317717</v>
+        <v>130317655</v>
       </c>
       <c r="B54" t="n">
-        <v>78978</v>
+        <v>57864</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7295,26 +7271,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7322,10 +7303,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506939</v>
+        <v>506974</v>
       </c>
       <c r="R54" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7360,19 +7341,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317676</v>
+        <v>130317650</v>
       </c>
       <c r="B2" t="n">
-        <v>80326</v>
+        <v>83201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507117</v>
+        <v>506870</v>
       </c>
       <c r="R2" t="n">
-        <v>6958267</v>
+        <v>6958284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +768,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317712</v>
+        <v>130317682</v>
       </c>
       <c r="B3" t="n">
         <v>80326</v>
@@ -838,7 +828,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506953</v>
+        <v>507013</v>
       </c>
       <c r="R3" t="n">
-        <v>6958498</v>
+        <v>6958267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +878,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,10 +931,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317650</v>
+        <v>130317697</v>
       </c>
       <c r="B4" t="n">
-        <v>83201</v>
+        <v>80326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,21 +942,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506870</v>
+        <v>506897</v>
       </c>
       <c r="R4" t="n">
-        <v>6958284</v>
+        <v>6958467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +1007,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1034,17 +1029,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317682</v>
+        <v>130317712</v>
       </c>
       <c r="B5" t="n">
         <v>80326</v>
@@ -1094,7 +1094,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507013</v>
+        <v>506953</v>
       </c>
       <c r="R5" t="n">
-        <v>6958267</v>
+        <v>6958498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1197,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317697</v>
+        <v>130317676</v>
       </c>
       <c r="B6" t="n">
         <v>80326</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506897</v>
+        <v>507117</v>
       </c>
       <c r="R6" t="n">
-        <v>6958467</v>
+        <v>6958267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På en liggande död sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317658</v>
+        <v>130317693</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,31 +1339,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506930</v>
+        <v>506874</v>
       </c>
       <c r="R7" t="n">
-        <v>6958447</v>
+        <v>6958543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,6 +1415,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1430,17 +1426,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1720,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317693</v>
+        <v>130317658</v>
       </c>
       <c r="B10" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,26 +1732,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1758,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506874</v>
+        <v>506930</v>
       </c>
       <c r="R10" t="n">
-        <v>6958543</v>
+        <v>6958447</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1798,7 +1804,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1807,7 +1813,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1818,22 +1823,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317691</v>
+        <v>130317684</v>
       </c>
       <c r="B13" t="n">
         <v>80326</v>
@@ -2130,11 +2130,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2142,10 +2138,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506877</v>
+        <v>507008</v>
       </c>
       <c r="R13" t="n">
-        <v>6958613</v>
+        <v>6958401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2182,7 +2178,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,7 +2231,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317684</v>
+        <v>130317687</v>
       </c>
       <c r="B14" t="n">
         <v>80326</v>
@@ -2273,10 +2269,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507008</v>
+        <v>507040</v>
       </c>
       <c r="R14" t="n">
-        <v>6958401</v>
+        <v>6958467</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2313,7 +2309,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2333,22 +2329,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2366,7 +2357,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317687</v>
+        <v>130317691</v>
       </c>
       <c r="B15" t="n">
         <v>80326</v>
@@ -2396,7 +2387,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507040</v>
+        <v>506877</v>
       </c>
       <c r="R15" t="n">
-        <v>6958467</v>
+        <v>6958613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2439,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2464,17 +2459,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2753,7 +2753,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317709</v>
+        <v>130317710</v>
       </c>
       <c r="B18" t="n">
         <v>80326</v>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507063</v>
+        <v>506973</v>
       </c>
       <c r="R18" t="n">
-        <v>6958140</v>
+        <v>6958484</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317710</v>
+        <v>130317709</v>
       </c>
       <c r="B19" t="n">
         <v>80326</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506973</v>
+        <v>507063</v>
       </c>
       <c r="R19" t="n">
-        <v>6958484</v>
+        <v>6958140</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317649</v>
+        <v>130317695</v>
       </c>
       <c r="B21" t="n">
-        <v>83201</v>
+        <v>80326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507053</v>
+        <v>506917</v>
       </c>
       <c r="R21" t="n">
-        <v>6958107</v>
+        <v>6958514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3222,6 +3222,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Lunglav på flera sälgar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3239,17 +3244,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3267,7 +3277,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317695</v>
+        <v>130317714</v>
       </c>
       <c r="B22" t="n">
         <v>80326</v>
@@ -3305,10 +3315,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506917</v>
+        <v>506876</v>
       </c>
       <c r="R22" t="n">
-        <v>6958514</v>
+        <v>6958216</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3341,11 +3351,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3398,10 +3403,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317714</v>
+        <v>130317649</v>
       </c>
       <c r="B23" t="n">
-        <v>80326</v>
+        <v>83201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3409,21 +3414,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3436,10 +3441,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506876</v>
+        <v>507053</v>
       </c>
       <c r="R23" t="n">
-        <v>6958216</v>
+        <v>6958107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3491,22 +3496,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130317689</v>
+        <v>130317726</v>
       </c>
       <c r="B27" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3881,21 +3881,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506962</v>
+        <v>507008</v>
       </c>
       <c r="R27" t="n">
-        <v>6958547</v>
+        <v>6958564</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3968,22 +3968,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4001,10 +3996,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317726</v>
+        <v>130317700</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4012,21 +4007,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4039,10 +4034,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507008</v>
+        <v>506928</v>
       </c>
       <c r="R28" t="n">
-        <v>6958564</v>
+        <v>6958456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +4074,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4099,17 +4094,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130317700</v>
+        <v>130317689</v>
       </c>
       <c r="B29" t="n">
         <v>80326</v>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506928</v>
+        <v>506962</v>
       </c>
       <c r="R29" t="n">
-        <v>6958456</v>
+        <v>6958547</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4258,7 +4258,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130317679</v>
+        <v>130317681</v>
       </c>
       <c r="B30" t="n">
         <v>80326</v>
@@ -4288,11 +4288,7 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4300,10 +4296,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507027</v>
+        <v>506982</v>
       </c>
       <c r="R30" t="n">
-        <v>6958207</v>
+        <v>6958260</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4340,7 +4336,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4393,7 +4389,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130317681</v>
+        <v>130317679</v>
       </c>
       <c r="B31" t="n">
         <v>80326</v>
@@ -4423,7 +4419,11 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506982</v>
+        <v>507027</v>
       </c>
       <c r="R31" t="n">
-        <v>6958260</v>
+        <v>6958207</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4654,7 +4654,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317688</v>
+        <v>130317713</v>
       </c>
       <c r="B33" t="n">
         <v>80326</v>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507005</v>
+        <v>506868</v>
       </c>
       <c r="R33" t="n">
-        <v>6958516</v>
+        <v>6958334</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4916,7 +4916,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317713</v>
+        <v>130317688</v>
       </c>
       <c r="B35" t="n">
         <v>80326</v>
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506868</v>
+        <v>507005</v>
       </c>
       <c r="R35" t="n">
-        <v>6958334</v>
+        <v>6958516</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317653</v>
+        <v>130317674</v>
       </c>
       <c r="B41" t="n">
-        <v>91776</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5668,28 +5668,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5699,10 +5700,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507079</v>
+        <v>506871</v>
       </c>
       <c r="R41" t="n">
-        <v>6958339</v>
+        <v>6958417</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5737,13 +5738,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5762,14 +5767,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5902,10 +5902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317674</v>
+        <v>130317653</v>
       </c>
       <c r="B43" t="n">
-        <v>57861</v>
+        <v>91776</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5913,29 +5913,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5945,10 +5944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506871</v>
+        <v>507079</v>
       </c>
       <c r="R43" t="n">
-        <v>6958417</v>
+        <v>6958339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5983,17 +5982,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre hackspår.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6012,9 +6007,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,37 +6032,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317694</v>
+        <v>130317719</v>
       </c>
       <c r="B44" t="n">
-        <v>80326</v>
+        <v>98974</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6070,10 +6083,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506910</v>
+        <v>506940</v>
       </c>
       <c r="R44" t="n">
-        <v>6958533</v>
+        <v>6958101</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6110,7 +6123,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6126,26 +6139,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6521,10 +6514,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317657</v>
+        <v>130317694</v>
       </c>
       <c r="B48" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6532,31 +6525,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6564,10 +6552,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506890</v>
+        <v>506910</v>
       </c>
       <c r="R48" t="n">
-        <v>6958493</v>
+        <v>6958533</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6604,7 +6592,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6613,6 +6601,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6623,17 +6612,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6651,50 +6645,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317719</v>
+        <v>130317657</v>
       </c>
       <c r="B49" t="n">
-        <v>98974</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6702,10 +6688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506940</v>
+        <v>506890</v>
       </c>
       <c r="R49" t="n">
-        <v>6958101</v>
+        <v>6958493</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6742,7 +6728,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6751,13 +6737,27 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317711</v>
+        <v>130317699</v>
       </c>
       <c r="B51" t="n">
         <v>80326</v>
@@ -6923,7 +6923,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6931,10 +6935,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506964</v>
+        <v>506945</v>
       </c>
       <c r="R51" t="n">
-        <v>6958502</v>
+        <v>6958463</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6967,6 +6971,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7019,7 +7028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317699</v>
+        <v>130317711</v>
       </c>
       <c r="B52" t="n">
         <v>80326</v>
@@ -7049,11 +7058,7 @@
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7061,10 +7066,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506945</v>
+        <v>506964</v>
       </c>
       <c r="R52" t="n">
-        <v>6958463</v>
+        <v>6958502</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7097,11 +7102,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130317676</v>
+        <v>130317653</v>
       </c>
       <c r="B2" t="n">
-        <v>80340</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507117</v>
+        <v>507079</v>
       </c>
       <c r="R2" t="n">
-        <v>6958267</v>
+        <v>6958339</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +755,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en liggande död sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +772,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död trädstam</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130317712</v>
+        <v>130317728</v>
       </c>
       <c r="B3" t="n">
-        <v>80340</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,30 +816,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506953</v>
+        <v>506918</v>
       </c>
       <c r="R3" t="n">
-        <v>6958498</v>
+        <v>6958323</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,11 +881,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar av lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -908,22 +898,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,41 +926,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130317682</v>
+        <v>130317720</v>
       </c>
       <c r="B4" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507013</v>
+        <v>507142</v>
       </c>
       <c r="R4" t="n">
-        <v>6958267</v>
+        <v>6958240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,11 +1002,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,26 +1015,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1076,48 +1032,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130317697</v>
+        <v>130317721</v>
       </c>
       <c r="B5" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506897</v>
+        <v>507071</v>
       </c>
       <c r="R5" t="n">
-        <v>6958467</v>
+        <v>6958280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,45 +1105,14 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1207,32 +1129,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130317650</v>
+        <v>130317722</v>
       </c>
       <c r="B6" t="n">
-        <v>83215</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1245,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506870</v>
+        <v>507004</v>
       </c>
       <c r="R6" t="n">
-        <v>6958284</v>
+        <v>6958523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1296,21 +1218,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130317702</v>
+        <v>130317723</v>
       </c>
       <c r="B7" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1366,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506880</v>
+        <v>506907</v>
       </c>
       <c r="R7" t="n">
-        <v>6958248</v>
+        <v>6958328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,11 +1311,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1426,22 +1328,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1459,32 +1356,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130317685</v>
+        <v>130317724</v>
       </c>
       <c r="B8" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1497,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507014</v>
+        <v>506880</v>
       </c>
       <c r="R8" t="n">
-        <v>6958455</v>
+        <v>6958273</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1535,11 +1432,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lunglav på en död sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1557,22 +1449,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1590,32 +1477,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130317693</v>
+        <v>130317726</v>
       </c>
       <c r="B9" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1628,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506874</v>
+        <v>507008</v>
       </c>
       <c r="R9" t="n">
-        <v>6958543</v>
+        <v>6958564</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1668,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Rikligt med garnlav här!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1688,22 +1575,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1721,42 +1603,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130317658</v>
+        <v>130317727</v>
       </c>
       <c r="B10" t="n">
-        <v>57878</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1764,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506930</v>
+        <v>506867</v>
       </c>
       <c r="R10" t="n">
-        <v>6958447</v>
+        <v>6958649</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,38 +1679,19 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1851,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130317671</v>
+        <v>130317649</v>
       </c>
       <c r="B11" t="n">
-        <v>58037</v>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,50 +1720,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506956</v>
+        <v>507053</v>
       </c>
       <c r="R11" t="n">
-        <v>6958085</v>
+        <v>6958107</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1946,12 +1791,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130317696</v>
+        <v>130317650</v>
       </c>
       <c r="B12" t="n">
-        <v>80340</v>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2007,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506892</v>
+        <v>506870</v>
       </c>
       <c r="R12" t="n">
-        <v>6958496</v>
+        <v>6958284</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2045,11 +1906,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2067,22 +1923,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2100,10 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130317691</v>
+        <v>130317717</v>
       </c>
       <c r="B13" t="n">
-        <v>80340</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2111,30 +1962,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2142,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506877</v>
+        <v>506939</v>
       </c>
       <c r="R13" t="n">
-        <v>6958613</v>
+        <v>6958101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2180,11 +2027,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2198,26 +2040,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2235,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130317684</v>
+        <v>130317718</v>
       </c>
       <c r="B14" t="n">
-        <v>80340</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2246,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2273,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507008</v>
+        <v>506963</v>
       </c>
       <c r="R14" t="n">
-        <v>6958401</v>
+        <v>6958046</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2311,11 +2133,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2329,26 +2146,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2366,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130317687</v>
+        <v>130317676</v>
       </c>
       <c r="B15" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2404,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507040</v>
+        <v>507117</v>
       </c>
       <c r="R15" t="n">
-        <v>6958467</v>
+        <v>6958267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2241,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lunglav på både björk och sälg.</t>
+          <t>På en liggande död sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2464,17 +2261,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2492,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130317698</v>
+        <v>130317677</v>
       </c>
       <c r="B16" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2530,10 +2332,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506953</v>
+        <v>507084</v>
       </c>
       <c r="R16" t="n">
-        <v>6958489</v>
+        <v>6958173</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2570,7 +2372,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På grenar av gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2590,22 +2392,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2623,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130317709</v>
+        <v>130317678</v>
       </c>
       <c r="B17" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2661,10 +2463,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507063</v>
+        <v>507047</v>
       </c>
       <c r="R17" t="n">
-        <v>6958140</v>
+        <v>6958189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2701,7 +2503,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2754,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130317710</v>
+        <v>130317679</v>
       </c>
       <c r="B18" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2784,7 +2586,11 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2792,10 +2598,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506973</v>
+        <v>507027</v>
       </c>
       <c r="R18" t="n">
-        <v>6958484</v>
+        <v>6958207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2832,7 +2638,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,10 +2691,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130317659</v>
+        <v>130317680</v>
       </c>
       <c r="B19" t="n">
-        <v>57878</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2896,31 +2702,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2928,10 +2729,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506915</v>
+        <v>506984</v>
       </c>
       <c r="R19" t="n">
-        <v>6958411</v>
+        <v>6958243</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2968,7 +2769,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2977,6 +2778,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2987,17 +2789,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3015,10 +2822,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130317678</v>
+        <v>130317681</v>
       </c>
       <c r="B20" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3053,10 +2860,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507047</v>
+        <v>506982</v>
       </c>
       <c r="R20" t="n">
-        <v>6958189</v>
+        <v>6958260</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3146,10 +2953,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130317695</v>
+        <v>130317682</v>
       </c>
       <c r="B21" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3176,7 +2983,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3184,10 +2995,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506917</v>
+        <v>507013</v>
       </c>
       <c r="R21" t="n">
-        <v>6958514</v>
+        <v>6958267</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3224,7 +3035,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Lunglav på flera sälgar.</t>
+          <t>Fertil lunglav med apothecier på sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3277,10 +3088,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130317714</v>
+        <v>130317683</v>
       </c>
       <c r="B22" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3315,10 +3126,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506876</v>
+        <v>507090</v>
       </c>
       <c r="R22" t="n">
-        <v>6958216</v>
+        <v>6958314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3351,6 +3162,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3403,10 +3219,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130317721</v>
+        <v>130317684</v>
       </c>
       <c r="B23" t="n">
-        <v>79235</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3414,34 +3230,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507071</v>
+        <v>507008</v>
       </c>
       <c r="R23" t="n">
-        <v>6958280</v>
+        <v>6958401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3476,14 +3295,45 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3500,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130317649</v>
+        <v>130317685</v>
       </c>
       <c r="B24" t="n">
-        <v>83215</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3511,21 +3361,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3538,10 +3388,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507053</v>
+        <v>507014</v>
       </c>
       <c r="R24" t="n">
-        <v>6958107</v>
+        <v>6958455</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3576,6 +3426,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lunglav på en död sälg.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3593,17 +3448,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3621,10 +3481,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130317701</v>
+        <v>130317687</v>
       </c>
       <c r="B25" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3659,10 +3519,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506872</v>
+        <v>507040</v>
       </c>
       <c r="R25" t="n">
-        <v>6958352</v>
+        <v>6958467</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3699,7 +3559,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På en björkhögstubbe.</t>
+          <t>Lunglav på både björk och sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3727,14 +3587,9 @@
           <t>Betula</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3752,10 +3607,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130317670</v>
+        <v>130317688</v>
       </c>
       <c r="B26" t="n">
-        <v>58037</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3763,50 +3618,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506867</v>
+        <v>507005</v>
       </c>
       <c r="R26" t="n">
-        <v>6958649</v>
+        <v>6958516</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3841,18 +3683,44 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3873,7 +3741,7 @@
         <v>130317689</v>
       </c>
       <c r="B27" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4001,10 +3869,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130317700</v>
+        <v>130317691</v>
       </c>
       <c r="B28" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4031,7 +3899,11 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4039,10 +3911,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506928</v>
+        <v>506877</v>
       </c>
       <c r="R28" t="n">
-        <v>6958456</v>
+        <v>6958613</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4079,7 +3951,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Rikligt med lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4132,10 +4004,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130317726</v>
+        <v>130317692</v>
       </c>
       <c r="B29" t="n">
-        <v>79235</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4143,21 +4015,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4170,10 +4042,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507008</v>
+        <v>506870</v>
       </c>
       <c r="R29" t="n">
-        <v>6958564</v>
+        <v>6958615</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4210,7 +4082,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav här!</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4230,17 +4102,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4258,10 +4135,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130317679</v>
+        <v>130317693</v>
       </c>
       <c r="B30" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4288,11 +4165,7 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4300,10 +4173,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507027</v>
+        <v>506874</v>
       </c>
       <c r="R30" t="n">
-        <v>6958207</v>
+        <v>6958543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4340,7 +4213,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apothecier på sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4393,10 +4266,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130317681</v>
+        <v>130317694</v>
       </c>
       <c r="B31" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4431,10 +4304,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506982</v>
+        <v>506910</v>
       </c>
       <c r="R31" t="n">
-        <v>6958260</v>
+        <v>6958533</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4524,10 +4397,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130317661</v>
+        <v>130317695</v>
       </c>
       <c r="B32" t="n">
-        <v>57878</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4535,31 +4408,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4567,10 +4435,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506892</v>
+        <v>506917</v>
       </c>
       <c r="R32" t="n">
-        <v>6958340</v>
+        <v>6958514</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4607,7 +4475,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på gran.</t>
+          <t>Lunglav på flera sälgar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4616,6 +4484,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4626,17 +4495,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4654,10 +4528,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130317688</v>
+        <v>130317696</v>
       </c>
       <c r="B33" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4692,10 +4566,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>507005</v>
+        <v>506892</v>
       </c>
       <c r="R33" t="n">
-        <v>6958516</v>
+        <v>6958496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4732,7 +4606,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4785,10 +4659,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130317680</v>
+        <v>130317697</v>
       </c>
       <c r="B34" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4823,10 +4697,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506984</v>
+        <v>506897</v>
       </c>
       <c r="R34" t="n">
-        <v>6958243</v>
+        <v>6958467</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4916,10 +4790,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130317713</v>
+        <v>130317698</v>
       </c>
       <c r="B35" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4954,10 +4828,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506868</v>
+        <v>506953</v>
       </c>
       <c r="R35" t="n">
-        <v>6958334</v>
+        <v>6958489</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4994,7 +4868,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Lunglav på död stående björk.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5014,22 +4888,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5047,10 +4921,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130317677</v>
+        <v>130317699</v>
       </c>
       <c r="B36" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5077,7 +4951,11 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5085,10 +4963,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507084</v>
+        <v>506945</v>
       </c>
       <c r="R36" t="n">
-        <v>6958173</v>
+        <v>6958463</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5125,7 +5003,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På grenar av gran.</t>
+          <t>Rikligt med lunglavsbålar på sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5145,22 +5023,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5178,10 +5056,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130317724</v>
+        <v>130317700</v>
       </c>
       <c r="B37" t="n">
-        <v>79235</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5189,21 +5067,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5216,10 +5094,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506880</v>
+        <v>506928</v>
       </c>
       <c r="R37" t="n">
-        <v>6958273</v>
+        <v>6958456</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5254,6 +5132,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5271,17 +5154,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5299,10 +5187,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130317653</v>
+        <v>130317701</v>
       </c>
       <c r="B38" t="n">
-        <v>91798</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5310,30 +5198,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5341,10 +5225,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507079</v>
+        <v>506872</v>
       </c>
       <c r="R38" t="n">
-        <v>6958339</v>
+        <v>6958352</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5379,6 +5263,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På en björkhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5396,22 +5285,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död trädstam</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead tree stem # Picea abies</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5429,10 +5318,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130317708</v>
+        <v>130317702</v>
       </c>
       <c r="B39" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5467,10 +5356,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507136</v>
+        <v>506880</v>
       </c>
       <c r="R39" t="n">
-        <v>6958243</v>
+        <v>6958248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5507,7 +5396,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På liggande död sälg.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5537,12 +5426,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5560,10 +5449,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130317674</v>
+        <v>130317708</v>
       </c>
       <c r="B40" t="n">
-        <v>57875</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5571,31 +5460,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5603,10 +5487,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506871</v>
+        <v>507136</v>
       </c>
       <c r="R40" t="n">
-        <v>6958417</v>
+        <v>6958243</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5643,7 +5527,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>På liggande död sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5652,6 +5536,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5662,17 +5547,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5690,10 +5580,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130317673</v>
+        <v>130317709</v>
       </c>
       <c r="B41" t="n">
-        <v>57875</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5701,31 +5591,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5733,10 +5618,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507049</v>
+        <v>507063</v>
       </c>
       <c r="R41" t="n">
-        <v>6958259</v>
+        <v>6958140</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5773,7 +5658,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre hackspår.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5782,12 +5667,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5805,10 +5711,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130317722</v>
+        <v>130317710</v>
       </c>
       <c r="B42" t="n">
-        <v>79235</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5816,21 +5722,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5843,10 +5749,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507004</v>
+        <v>506973</v>
       </c>
       <c r="R42" t="n">
-        <v>6958523</v>
+        <v>6958484</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5881,6 +5787,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5894,6 +5805,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5911,10 +5842,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130317723</v>
+        <v>130317711</v>
       </c>
       <c r="B43" t="n">
-        <v>79235</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5922,21 +5853,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5949,10 +5880,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506907</v>
+        <v>506964</v>
       </c>
       <c r="R43" t="n">
-        <v>6958328</v>
+        <v>6958502</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6004,17 +5935,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6032,10 +5968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130317727</v>
+        <v>130317712</v>
       </c>
       <c r="B44" t="n">
-        <v>79235</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,26 +5979,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6070,10 +6010,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>506867</v>
+        <v>506953</v>
       </c>
       <c r="R44" t="n">
-        <v>6958649</v>
+        <v>6958498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6108,6 +6048,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar av lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6121,6 +6066,26 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6138,10 +6103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130317657</v>
+        <v>130317713</v>
       </c>
       <c r="B45" t="n">
-        <v>57878</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6149,31 +6114,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6181,10 +6141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506890</v>
+        <v>506868</v>
       </c>
       <c r="R45" t="n">
-        <v>6958493</v>
+        <v>6958334</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6221,7 +6181,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>Lunglav på död stående björk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6230,6 +6190,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6240,17 +6201,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6268,10 +6234,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130317694</v>
+        <v>130317714</v>
       </c>
       <c r="B46" t="n">
-        <v>80340</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6306,10 +6272,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>506910</v>
+        <v>506876</v>
       </c>
       <c r="R46" t="n">
-        <v>6958533</v>
+        <v>6958216</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6342,11 +6308,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6399,37 +6360,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130317683</v>
+        <v>130317673</v>
       </c>
       <c r="B47" t="n">
-        <v>80340</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6437,10 +6403,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507090</v>
+        <v>507049</v>
       </c>
       <c r="R47" t="n">
-        <v>6958314</v>
+        <v>6958259</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6477,7 +6443,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Lunglav på sälg.</t>
+          <t>Äldre hackspår.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6486,33 +6452,12 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6530,37 +6475,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130317728</v>
+        <v>130317674</v>
       </c>
       <c r="B48" t="n">
-        <v>83081</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6568,10 +6518,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506918</v>
+        <v>506871</v>
       </c>
       <c r="R48" t="n">
-        <v>6958323</v>
+        <v>6958417</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6606,13 +6556,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6651,50 +6605,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130317719</v>
+        <v>130317655</v>
       </c>
       <c r="B49" t="n">
-        <v>99003</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6702,10 +6648,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506940</v>
+        <v>506974</v>
       </c>
       <c r="R49" t="n">
-        <v>6958101</v>
+        <v>6958546</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6742,7 +6688,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6751,13 +6697,27 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6775,10 +6735,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130317711</v>
+        <v>130317657</v>
       </c>
       <c r="B50" t="n">
-        <v>80340</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6786,26 +6746,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6813,10 +6778,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506964</v>
+        <v>506890</v>
       </c>
       <c r="R50" t="n">
-        <v>6958502</v>
+        <v>6958493</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6851,13 +6816,17 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6868,22 +6837,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6901,10 +6865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130317699</v>
+        <v>130317658</v>
       </c>
       <c r="B51" t="n">
-        <v>80340</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6912,28 +6876,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6943,10 +6908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506945</v>
+        <v>506930</v>
       </c>
       <c r="R51" t="n">
-        <v>6958463</v>
+        <v>6958447</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6983,7 +6948,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6992,7 +6957,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7003,22 +6967,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7036,10 +6995,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130317675</v>
+        <v>130317659</v>
       </c>
       <c r="B52" t="n">
-        <v>56450</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7047,50 +7006,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507115</v>
+        <v>506915</v>
       </c>
       <c r="R52" t="n">
-        <v>6958267</v>
+        <v>6958411</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7125,6 +7076,11 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -7137,6 +7093,21 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7154,10 +7125,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130317717</v>
+        <v>130317660</v>
       </c>
       <c r="B53" t="n">
-        <v>78992</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7165,26 +7136,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7192,10 +7168,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506939</v>
+        <v>506854</v>
       </c>
       <c r="R53" t="n">
-        <v>6958101</v>
+        <v>6958370</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7230,19 +7206,38 @@
           <t>2025-12-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7260,10 +7255,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130317655</v>
+        <v>130317661</v>
       </c>
       <c r="B54" t="n">
-        <v>57878</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7293,7 +7288,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7303,10 +7298,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>506974</v>
+        <v>506892</v>
       </c>
       <c r="R54" t="n">
-        <v>6958546</v>
+        <v>6958340</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7343,7 +7338,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska och äldre, på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7390,10 +7385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130317660</v>
+        <v>130317668</v>
       </c>
       <c r="B55" t="n">
-        <v>57878</v>
+        <v>58114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7401,42 +7396,50 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>506854</v>
+        <v>506884</v>
       </c>
       <c r="R55" t="n">
-        <v>6958370</v>
+        <v>6958644</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7471,11 +7474,6 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7488,21 +7486,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7520,10 +7503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130317692</v>
+        <v>130317670</v>
       </c>
       <c r="B56" t="n">
-        <v>80340</v>
+        <v>58114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7531,37 +7514,50 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>506870</v>
+        <v>506867</v>
       </c>
       <c r="R56" t="n">
-        <v>6958615</v>
+        <v>6958649</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7596,44 +7592,18 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7651,10 +7621,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130317668</v>
+        <v>130317671</v>
       </c>
       <c r="B57" t="n">
-        <v>58037</v>
+        <v>58114</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7702,10 +7672,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>506884</v>
+        <v>506956</v>
       </c>
       <c r="R57" t="n">
-        <v>6958644</v>
+        <v>6958085</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7766,6 +7736,248 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130317675</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>507115</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6958267</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130317719</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Björnsjön Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>506940</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6958101</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10771,7 +10771,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134841710</v>
+        <v>134957165</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -10799,32 +10799,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507106</v>
+        <v>507092</v>
       </c>
       <c r="R89" t="n">
-        <v>6958185</v>
+        <v>6958137</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10848,22 +10841,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10878,19 +10861,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134841711</v>
+        <v>134967586</v>
       </c>
       <c r="B90" t="n">
         <v>57975</v>
@@ -10918,32 +10901,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>507123</v>
+        <v>507045</v>
       </c>
       <c r="R90" t="n">
-        <v>6958243</v>
+        <v>6958452</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10967,22 +10943,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10997,19 +10963,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134957165</v>
+        <v>134968419</v>
       </c>
       <c r="B91" t="n">
         <v>57975</v>
@@ -11049,10 +11015,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>507092</v>
+        <v>507098</v>
       </c>
       <c r="R91" t="n">
-        <v>6958137</v>
+        <v>6958202</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11111,7 +11077,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134967586</v>
+        <v>134968835</v>
       </c>
       <c r="B92" t="n">
         <v>57975</v>
@@ -11151,10 +11117,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>507045</v>
+        <v>507100</v>
       </c>
       <c r="R92" t="n">
-        <v>6958452</v>
+        <v>6958200</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11213,10 +11179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134968419</v>
+        <v>130317668</v>
       </c>
       <c r="B93" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11224,39 +11190,50 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>507098</v>
+        <v>506884</v>
       </c>
       <c r="R93" t="n">
-        <v>6958202</v>
+        <v>6958644</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11283,12 +11260,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11299,26 +11276,31 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134968835</v>
+        <v>130317670</v>
       </c>
       <c r="B94" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11326,39 +11308,50 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>507100</v>
+        <v>506867</v>
       </c>
       <c r="R94" t="n">
-        <v>6958200</v>
+        <v>6958649</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11385,12 +11378,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11401,23 +11394,28 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130317668</v>
+        <v>130317671</v>
       </c>
       <c r="B95" t="n">
         <v>58114</v>
@@ -11468,10 +11466,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506884</v>
+        <v>506956</v>
       </c>
       <c r="R95" t="n">
-        <v>6958644</v>
+        <v>6958085</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11535,10 +11533,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130317670</v>
+        <v>130317675</v>
       </c>
       <c r="B96" t="n">
-        <v>58114</v>
+        <v>56522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11546,21 +11544,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11572,7 +11570,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -11586,10 +11584,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>506867</v>
+        <v>507115</v>
       </c>
       <c r="R96" t="n">
-        <v>6958649</v>
+        <v>6958267</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11653,61 +11651,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130317671</v>
+        <v>134959108</v>
       </c>
       <c r="B97" t="n">
-        <v>58114</v>
+        <v>99112</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>506956</v>
+        <v>507019</v>
       </c>
       <c r="R97" t="n">
-        <v>6958085</v>
+        <v>6958429</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11734,12 +11716,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11750,82 +11732,61 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130317675</v>
+        <v>134960863</v>
       </c>
       <c r="B98" t="n">
-        <v>56522</v>
+        <v>99112</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>206004</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>507115</v>
+        <v>507097</v>
       </c>
       <c r="R98" t="n">
-        <v>6958267</v>
+        <v>6958045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11852,12 +11813,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11868,28 +11829,23 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134959108</v>
+        <v>134966317</v>
       </c>
       <c r="B99" t="n">
         <v>99112</v>
@@ -11917,17 +11873,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>507019</v>
+        <v>507088</v>
       </c>
       <c r="R99" t="n">
-        <v>6958429</v>
+        <v>6958044</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11986,10 +11946,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134960863</v>
+        <v>134965260</v>
       </c>
       <c r="B100" t="n">
-        <v>99112</v>
+        <v>99533</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11997,34 +11957,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>507097</v>
+        <v>507028</v>
       </c>
       <c r="R100" t="n">
-        <v>6958045</v>
+        <v>6958424</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12083,10 +12043,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134966317</v>
+        <v>134966518</v>
       </c>
       <c r="B101" t="n">
-        <v>99112</v>
+        <v>99533</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12094,38 +12054,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>507088</v>
+        <v>507047</v>
       </c>
       <c r="R101" t="n">
-        <v>6958044</v>
+        <v>6958372</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12184,10 +12140,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134965260</v>
+        <v>134960440</v>
       </c>
       <c r="B102" t="n">
-        <v>99533</v>
+        <v>108205</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12195,21 +12151,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219880</v>
+        <v>220083</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12219,10 +12175,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>507028</v>
+        <v>507039</v>
       </c>
       <c r="R102" t="n">
-        <v>6958424</v>
+        <v>6958407</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12281,10 +12237,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134966518</v>
+        <v>134967588</v>
       </c>
       <c r="B103" t="n">
-        <v>99533</v>
+        <v>111153</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12292,21 +12248,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12316,10 +12272,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>507047</v>
+        <v>507108</v>
       </c>
       <c r="R103" t="n">
-        <v>6958372</v>
+        <v>6958208</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12378,45 +12334,61 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134960440</v>
+        <v>130317719</v>
       </c>
       <c r="B104" t="n">
-        <v>108205</v>
+        <v>99118</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>507039</v>
+        <v>506940</v>
       </c>
       <c r="R104" t="n">
-        <v>6958407</v>
+        <v>6958101</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12443,12 +12415,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12457,66 +12434,84 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134967588</v>
+        <v>134841767</v>
       </c>
       <c r="B105" t="n">
-        <v>111153</v>
+        <v>99195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>507108</v>
+        <v>507039</v>
       </c>
       <c r="R105" t="n">
-        <v>6958208</v>
+        <v>6958029</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12540,12 +12535,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12560,22 +12565,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130317719</v>
+        <v>134841768</v>
       </c>
       <c r="B106" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12602,7 +12607,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12610,26 +12615,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506940</v>
+        <v>506984</v>
       </c>
       <c r="R106" t="n">
-        <v>6958101</v>
+        <v>6958031</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12653,17 +12654,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12672,31 +12678,25 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134841767</v>
+        <v>134841769</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12739,14 +12739,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>507039</v>
+        <v>507066</v>
       </c>
       <c r="R107" t="n">
-        <v>6958029</v>
+        <v>6958073</v>
       </c>
       <c r="S107" t="n">
         <v>4</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12815,7 +12815,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134841768</v>
+        <v>134841770</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -12845,12 +12845,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -12858,14 +12858,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506984</v>
+        <v>506871</v>
       </c>
       <c r="R108" t="n">
-        <v>6958031</v>
+        <v>6958504</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12934,7 +12934,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134841769</v>
+        <v>134841771</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12977,14 +12977,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>507066</v>
+        <v>506917</v>
       </c>
       <c r="R109" t="n">
-        <v>6958073</v>
+        <v>6958119</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -13016,7 +13016,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13053,7 +13053,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134841770</v>
+        <v>134955275</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -13083,30 +13083,22 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506871</v>
+        <v>507086</v>
       </c>
       <c r="R110" t="n">
-        <v>6958504</v>
+        <v>6958292</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13130,22 +13122,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13160,19 +13142,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134841771</v>
+        <v>134956090</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -13202,30 +13184,22 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506917</v>
+        <v>507077</v>
       </c>
       <c r="R111" t="n">
-        <v>6958119</v>
+        <v>6958363</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13249,22 +13223,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13279,19 +13243,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134955275</v>
+        <v>134956544</v>
       </c>
       <c r="B112" t="n">
         <v>99195</v>
@@ -13330,10 +13294,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>507086</v>
+        <v>507071</v>
       </c>
       <c r="R112" t="n">
-        <v>6958292</v>
+        <v>6958357</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13392,7 +13356,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134956090</v>
+        <v>134958910</v>
       </c>
       <c r="B113" t="n">
         <v>99195</v>
@@ -13422,7 +13386,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13431,10 +13395,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>507077</v>
+        <v>507007</v>
       </c>
       <c r="R113" t="n">
-        <v>6958363</v>
+        <v>6958439</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13493,7 +13457,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134956544</v>
+        <v>134959316</v>
       </c>
       <c r="B114" t="n">
         <v>99195</v>
@@ -13532,10 +13496,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>507071</v>
+        <v>507064</v>
       </c>
       <c r="R114" t="n">
-        <v>6958357</v>
+        <v>6958456</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13594,7 +13558,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134958910</v>
+        <v>134959721</v>
       </c>
       <c r="B115" t="n">
         <v>99195</v>
@@ -13624,7 +13588,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13633,10 +13597,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>507007</v>
+        <v>507056</v>
       </c>
       <c r="R115" t="n">
-        <v>6958439</v>
+        <v>6958071</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13695,7 +13659,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134959316</v>
+        <v>134960866</v>
       </c>
       <c r="B116" t="n">
         <v>99195</v>
@@ -13723,21 +13687,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>507064</v>
+        <v>507090</v>
       </c>
       <c r="R116" t="n">
-        <v>6958456</v>
+        <v>6958137</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13796,7 +13756,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134959721</v>
+        <v>134961959</v>
       </c>
       <c r="B117" t="n">
         <v>99195</v>
@@ -13826,7 +13786,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13835,10 +13795,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>507056</v>
+        <v>507101</v>
       </c>
       <c r="R117" t="n">
-        <v>6958071</v>
+        <v>6958152</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13897,7 +13857,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134960866</v>
+        <v>134962672</v>
       </c>
       <c r="B118" t="n">
         <v>99195</v>
@@ -13925,17 +13885,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>507090</v>
+        <v>507106</v>
       </c>
       <c r="R118" t="n">
-        <v>6958137</v>
+        <v>6958171</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13994,7 +13958,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134961959</v>
+        <v>134965265</v>
       </c>
       <c r="B119" t="n">
         <v>99195</v>
@@ -14033,10 +13997,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>507101</v>
+        <v>507059</v>
       </c>
       <c r="R119" t="n">
-        <v>6958152</v>
+        <v>6958435</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14095,7 +14059,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134962672</v>
+        <v>134965893</v>
       </c>
       <c r="B120" t="n">
         <v>99195</v>
@@ -14125,7 +14089,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14134,10 +14098,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>507106</v>
+        <v>507091</v>
       </c>
       <c r="R120" t="n">
-        <v>6958171</v>
+        <v>6958333</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14196,7 +14160,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134965265</v>
+        <v>134966517</v>
       </c>
       <c r="B121" t="n">
         <v>99195</v>
@@ -14226,7 +14190,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14235,10 +14199,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>507059</v>
+        <v>507096</v>
       </c>
       <c r="R121" t="n">
-        <v>6958435</v>
+        <v>6958124</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14297,7 +14261,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134965893</v>
+        <v>134968005</v>
       </c>
       <c r="B122" t="n">
         <v>99195</v>
@@ -14327,7 +14291,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14336,10 +14300,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>507091</v>
+        <v>507082</v>
       </c>
       <c r="R122" t="n">
-        <v>6958333</v>
+        <v>6958354</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14398,7 +14362,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134966517</v>
+        <v>134968422</v>
       </c>
       <c r="B123" t="n">
         <v>99195</v>
@@ -14428,7 +14392,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14437,10 +14401,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>507096</v>
+        <v>507097</v>
       </c>
       <c r="R123" t="n">
-        <v>6958124</v>
+        <v>6958307</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14499,7 +14463,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134968005</v>
+        <v>134970031</v>
       </c>
       <c r="B124" t="n">
         <v>99195</v>
@@ -14529,7 +14493,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14538,10 +14502,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>507082</v>
+        <v>507099</v>
       </c>
       <c r="R124" t="n">
-        <v>6958354</v>
+        <v>6958231</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14600,7 +14564,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134968422</v>
+        <v>134970241</v>
       </c>
       <c r="B125" t="n">
         <v>99195</v>
@@ -14630,7 +14594,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14639,10 +14603,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>507097</v>
+        <v>507017</v>
       </c>
       <c r="R125" t="n">
-        <v>6958307</v>
+        <v>6958430</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14701,7 +14665,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134970031</v>
+        <v>134971309</v>
       </c>
       <c r="B126" t="n">
         <v>99195</v>
@@ -14731,19 +14695,19 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>507099</v>
+        <v>507068</v>
       </c>
       <c r="R126" t="n">
-        <v>6958231</v>
+        <v>6958037</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14802,49 +14766,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134970241</v>
+        <v>134960018</v>
       </c>
       <c r="B127" t="n">
-        <v>99195</v>
+        <v>106324</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>507017</v>
+        <v>507040</v>
       </c>
       <c r="R127" t="n">
-        <v>6958430</v>
+        <v>6958405</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14903,49 +14863,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134971309</v>
+        <v>134964821</v>
       </c>
       <c r="B128" t="n">
-        <v>99195</v>
+        <v>98060</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>507068</v>
+        <v>507084</v>
       </c>
       <c r="R128" t="n">
-        <v>6958037</v>
+        <v>6958378</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15004,10 +14960,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134960018</v>
+        <v>134965892</v>
       </c>
       <c r="B129" t="n">
-        <v>106324</v>
+        <v>103762</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15015,21 +14971,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221144</v>
+        <v>222002</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15039,10 +14995,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>507040</v>
+        <v>507106</v>
       </c>
       <c r="R129" t="n">
-        <v>6958405</v>
+        <v>6958112</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15098,200 +15054,6 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>134964821</v>
-      </c>
-      <c r="B130" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Björnsjöänget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q130" t="n">
-        <v>507084</v>
-      </c>
-      <c r="R130" t="n">
-        <v>6958378</v>
-      </c>
-      <c r="S130" t="n">
-        <v>10</v>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AD130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT130" t="inlineStr"/>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>Via Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>134965892</v>
-      </c>
-      <c r="B131" t="n">
-        <v>103762</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>222002</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Underviol</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Viola mirabilis</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Björnsjöänget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q131" t="n">
-        <v>507106</v>
-      </c>
-      <c r="R131" t="n">
-        <v>6958112</v>
-      </c>
-      <c r="S131" t="n">
-        <v>10</v>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AD131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT131" t="inlineStr"/>
-      <c r="AW131" t="inlineStr">
-        <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>Via Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10771,7 +10771,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134957165</v>
+        <v>134841710</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -10799,25 +10799,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507092</v>
+        <v>507106</v>
       </c>
       <c r="R89" t="n">
-        <v>6958137</v>
+        <v>6958185</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10841,12 +10848,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10861,19 +10878,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134967586</v>
+        <v>134841711</v>
       </c>
       <c r="B90" t="n">
         <v>57975</v>
@@ -10901,25 +10918,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>507045</v>
+        <v>507123</v>
       </c>
       <c r="R90" t="n">
-        <v>6958452</v>
+        <v>6958243</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10943,12 +10967,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10963,19 +10997,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134968419</v>
+        <v>134957165</v>
       </c>
       <c r="B91" t="n">
         <v>57975</v>
@@ -11015,10 +11049,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>507098</v>
+        <v>507092</v>
       </c>
       <c r="R91" t="n">
-        <v>6958202</v>
+        <v>6958137</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11077,7 +11111,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134968835</v>
+        <v>134967586</v>
       </c>
       <c r="B92" t="n">
         <v>57975</v>
@@ -11117,10 +11151,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>507100</v>
+        <v>507045</v>
       </c>
       <c r="R92" t="n">
-        <v>6958200</v>
+        <v>6958452</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11179,10 +11213,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130317668</v>
+        <v>134968419</v>
       </c>
       <c r="B93" t="n">
-        <v>58114</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11190,50 +11224,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>506884</v>
+        <v>507098</v>
       </c>
       <c r="R93" t="n">
-        <v>6958644</v>
+        <v>6958202</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11260,12 +11283,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11276,31 +11299,26 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130317670</v>
+        <v>134968835</v>
       </c>
       <c r="B94" t="n">
-        <v>58114</v>
+        <v>57975</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11308,50 +11326,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>506867</v>
+        <v>507100</v>
       </c>
       <c r="R94" t="n">
-        <v>6958649</v>
+        <v>6958200</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11378,12 +11385,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11394,28 +11401,23 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130317671</v>
+        <v>130317668</v>
       </c>
       <c r="B95" t="n">
         <v>58114</v>
@@ -11466,10 +11468,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506956</v>
+        <v>506884</v>
       </c>
       <c r="R95" t="n">
-        <v>6958085</v>
+        <v>6958644</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11533,10 +11535,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130317675</v>
+        <v>130317670</v>
       </c>
       <c r="B96" t="n">
-        <v>56522</v>
+        <v>58114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11544,21 +11546,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11570,7 +11572,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -11584,10 +11586,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>507115</v>
+        <v>506867</v>
       </c>
       <c r="R96" t="n">
-        <v>6958267</v>
+        <v>6958649</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11651,45 +11653,61 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134959108</v>
+        <v>130317671</v>
       </c>
       <c r="B97" t="n">
-        <v>99112</v>
+        <v>58114</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>507019</v>
+        <v>506956</v>
       </c>
       <c r="R97" t="n">
-        <v>6958429</v>
+        <v>6958085</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11716,12 +11734,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11732,61 +11750,82 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134960863</v>
+        <v>130317675</v>
       </c>
       <c r="B98" t="n">
-        <v>99112</v>
+        <v>56522</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>507097</v>
+        <v>507115</v>
       </c>
       <c r="R98" t="n">
-        <v>6958045</v>
+        <v>6958267</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11813,12 +11852,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11829,23 +11868,28 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134966317</v>
+        <v>134959108</v>
       </c>
       <c r="B99" t="n">
         <v>99112</v>
@@ -11873,21 +11917,17 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>507088</v>
+        <v>507019</v>
       </c>
       <c r="R99" t="n">
-        <v>6958044</v>
+        <v>6958429</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11946,10 +11986,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134965260</v>
+        <v>134960863</v>
       </c>
       <c r="B100" t="n">
-        <v>99533</v>
+        <v>99112</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11957,34 +11997,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>507028</v>
+        <v>507097</v>
       </c>
       <c r="R100" t="n">
-        <v>6958424</v>
+        <v>6958045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12043,10 +12083,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134966518</v>
+        <v>134966317</v>
       </c>
       <c r="B101" t="n">
-        <v>99533</v>
+        <v>99112</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12054,34 +12094,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>507047</v>
+        <v>507088</v>
       </c>
       <c r="R101" t="n">
-        <v>6958372</v>
+        <v>6958044</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12140,10 +12184,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134960440</v>
+        <v>134965260</v>
       </c>
       <c r="B102" t="n">
-        <v>108205</v>
+        <v>99533</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12151,21 +12195,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220083</v>
+        <v>219880</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12175,10 +12219,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>507039</v>
+        <v>507028</v>
       </c>
       <c r="R102" t="n">
-        <v>6958407</v>
+        <v>6958424</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12237,10 +12281,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134967588</v>
+        <v>134966518</v>
       </c>
       <c r="B103" t="n">
-        <v>111153</v>
+        <v>99533</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12248,21 +12292,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12272,10 +12316,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>507108</v>
+        <v>507047</v>
       </c>
       <c r="R103" t="n">
-        <v>6958208</v>
+        <v>6958372</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12334,61 +12378,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130317719</v>
+        <v>134960440</v>
       </c>
       <c r="B104" t="n">
-        <v>99118</v>
+        <v>108205</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>506940</v>
+        <v>507039</v>
       </c>
       <c r="R104" t="n">
-        <v>6958101</v>
+        <v>6958407</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12415,17 +12443,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12434,84 +12457,66 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134841767</v>
+        <v>134967588</v>
       </c>
       <c r="B105" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>507039</v>
+        <v>507108</v>
       </c>
       <c r="R105" t="n">
-        <v>6958029</v>
+        <v>6958208</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12535,22 +12540,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12565,22 +12560,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134841768</v>
+        <v>130317719</v>
       </c>
       <c r="B106" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12607,7 +12602,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12615,22 +12610,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506984</v>
+        <v>506940</v>
       </c>
       <c r="R106" t="n">
-        <v>6958031</v>
+        <v>6958101</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12654,22 +12653,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12678,25 +12672,31 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134841769</v>
+        <v>134841767</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12739,14 +12739,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>507066</v>
+        <v>507039</v>
       </c>
       <c r="R107" t="n">
-        <v>6958073</v>
+        <v>6958029</v>
       </c>
       <c r="S107" t="n">
         <v>4</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12815,7 +12815,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134841770</v>
+        <v>134841768</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -12845,12 +12845,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -12858,14 +12858,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506871</v>
+        <v>506984</v>
       </c>
       <c r="R108" t="n">
-        <v>6958504</v>
+        <v>6958031</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12934,7 +12934,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134841771</v>
+        <v>134841769</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12977,14 +12977,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506917</v>
+        <v>507066</v>
       </c>
       <c r="R109" t="n">
-        <v>6958119</v>
+        <v>6958073</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -13016,7 +13016,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13053,7 +13053,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134955275</v>
+        <v>134841770</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -13083,22 +13083,30 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>507086</v>
+        <v>506871</v>
       </c>
       <c r="R110" t="n">
-        <v>6958292</v>
+        <v>6958504</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13122,12 +13130,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13142,19 +13160,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134956090</v>
+        <v>134841771</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -13184,22 +13202,30 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>507077</v>
+        <v>506917</v>
       </c>
       <c r="R111" t="n">
-        <v>6958363</v>
+        <v>6958119</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13223,12 +13249,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13243,19 +13279,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134956544</v>
+        <v>134955275</v>
       </c>
       <c r="B112" t="n">
         <v>99195</v>
@@ -13294,10 +13330,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>507071</v>
+        <v>507086</v>
       </c>
       <c r="R112" t="n">
-        <v>6958357</v>
+        <v>6958292</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13356,7 +13392,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134958910</v>
+        <v>134956090</v>
       </c>
       <c r="B113" t="n">
         <v>99195</v>
@@ -13386,7 +13422,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13395,10 +13431,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>507007</v>
+        <v>507077</v>
       </c>
       <c r="R113" t="n">
-        <v>6958439</v>
+        <v>6958363</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13457,7 +13493,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134959316</v>
+        <v>134956544</v>
       </c>
       <c r="B114" t="n">
         <v>99195</v>
@@ -13496,10 +13532,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>507064</v>
+        <v>507071</v>
       </c>
       <c r="R114" t="n">
-        <v>6958456</v>
+        <v>6958357</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13558,7 +13594,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134959721</v>
+        <v>134958910</v>
       </c>
       <c r="B115" t="n">
         <v>99195</v>
@@ -13588,7 +13624,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13597,10 +13633,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>507056</v>
+        <v>507007</v>
       </c>
       <c r="R115" t="n">
-        <v>6958071</v>
+        <v>6958439</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13659,7 +13695,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134960866</v>
+        <v>134959316</v>
       </c>
       <c r="B116" t="n">
         <v>99195</v>
@@ -13687,17 +13723,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>507090</v>
+        <v>507064</v>
       </c>
       <c r="R116" t="n">
-        <v>6958137</v>
+        <v>6958456</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13756,7 +13796,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134961959</v>
+        <v>134959721</v>
       </c>
       <c r="B117" t="n">
         <v>99195</v>
@@ -13786,7 +13826,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13795,10 +13835,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>507101</v>
+        <v>507056</v>
       </c>
       <c r="R117" t="n">
-        <v>6958152</v>
+        <v>6958071</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13857,7 +13897,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134962672</v>
+        <v>134960866</v>
       </c>
       <c r="B118" t="n">
         <v>99195</v>
@@ -13885,21 +13925,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>507106</v>
+        <v>507090</v>
       </c>
       <c r="R118" t="n">
-        <v>6958171</v>
+        <v>6958137</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13958,7 +13994,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134965265</v>
+        <v>134961959</v>
       </c>
       <c r="B119" t="n">
         <v>99195</v>
@@ -13997,10 +14033,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>507059</v>
+        <v>507101</v>
       </c>
       <c r="R119" t="n">
-        <v>6958435</v>
+        <v>6958152</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14059,7 +14095,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134965893</v>
+        <v>134962672</v>
       </c>
       <c r="B120" t="n">
         <v>99195</v>
@@ -14089,7 +14125,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14098,10 +14134,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>507091</v>
+        <v>507106</v>
       </c>
       <c r="R120" t="n">
-        <v>6958333</v>
+        <v>6958171</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14160,7 +14196,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134966517</v>
+        <v>134965265</v>
       </c>
       <c r="B121" t="n">
         <v>99195</v>
@@ -14190,7 +14226,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14199,10 +14235,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>507096</v>
+        <v>507059</v>
       </c>
       <c r="R121" t="n">
-        <v>6958124</v>
+        <v>6958435</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14261,7 +14297,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134968005</v>
+        <v>134965893</v>
       </c>
       <c r="B122" t="n">
         <v>99195</v>
@@ -14291,7 +14327,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14300,10 +14336,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>507082</v>
+        <v>507091</v>
       </c>
       <c r="R122" t="n">
-        <v>6958354</v>
+        <v>6958333</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14362,7 +14398,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134968422</v>
+        <v>134966517</v>
       </c>
       <c r="B123" t="n">
         <v>99195</v>
@@ -14392,7 +14428,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14401,10 +14437,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>507097</v>
+        <v>507096</v>
       </c>
       <c r="R123" t="n">
-        <v>6958307</v>
+        <v>6958124</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14463,7 +14499,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134970031</v>
+        <v>134968005</v>
       </c>
       <c r="B124" t="n">
         <v>99195</v>
@@ -14493,7 +14529,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14502,10 +14538,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>507099</v>
+        <v>507082</v>
       </c>
       <c r="R124" t="n">
-        <v>6958231</v>
+        <v>6958354</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14564,7 +14600,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134970241</v>
+        <v>134968422</v>
       </c>
       <c r="B125" t="n">
         <v>99195</v>
@@ -14594,7 +14630,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14603,10 +14639,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>507017</v>
+        <v>507097</v>
       </c>
       <c r="R125" t="n">
-        <v>6958430</v>
+        <v>6958307</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14665,7 +14701,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134971309</v>
+        <v>134970031</v>
       </c>
       <c r="B126" t="n">
         <v>99195</v>
@@ -14695,19 +14731,19 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>507068</v>
+        <v>507099</v>
       </c>
       <c r="R126" t="n">
-        <v>6958037</v>
+        <v>6958231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14766,45 +14802,49 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134960018</v>
+        <v>134970241</v>
       </c>
       <c r="B127" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>507040</v>
+        <v>507017</v>
       </c>
       <c r="R127" t="n">
-        <v>6958405</v>
+        <v>6958430</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14863,45 +14903,49 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134964821</v>
+        <v>134971309</v>
       </c>
       <c r="B128" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>507084</v>
+        <v>507068</v>
       </c>
       <c r="R128" t="n">
-        <v>6958378</v>
+        <v>6958037</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14960,10 +15004,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134965892</v>
+        <v>134960018</v>
       </c>
       <c r="B129" t="n">
-        <v>103762</v>
+        <v>106324</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14971,21 +15015,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222002</v>
+        <v>221144</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14995,10 +15039,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>507106</v>
+        <v>507040</v>
       </c>
       <c r="R129" t="n">
-        <v>6958112</v>
+        <v>6958405</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15054,6 +15098,200 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>134964821</v>
+      </c>
+      <c r="B130" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Björnsjöänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>507084</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6958378</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>134965892</v>
+      </c>
+      <c r="B131" t="n">
+        <v>103762</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Björnsjöänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>507106</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6958112</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AZ131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956728</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317653</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966523</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317728</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970033</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964820</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961088</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963492</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966521</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963912</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963704</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956761</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,6 +2157,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963294</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970653</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317720</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2387,6 +2472,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317721</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317722</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2614,6 +2709,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317723</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2735,6 +2835,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317724</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2861,6 +2966,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317726</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2967,6 +3077,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317727</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3077,6 +3192,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841730</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3187,6 +3307,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841731</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3297,6 +3422,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841732</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3394,6 +3524,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959105</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3491,6 +3626,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959720</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3588,6 +3728,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962671</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3685,6 +3830,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963915</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3782,6 +3932,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970654</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3903,6 +4058,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317649</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4024,6 +4184,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317650</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4130,6 +4295,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317717</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4236,6 +4406,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317718</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4333,6 +4508,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961087</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4464,6 +4644,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317676</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4595,6 +4780,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317677</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4726,6 +4916,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317678</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4861,6 +5056,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317679</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4992,6 +5192,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317680</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5123,6 +5328,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317681</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5258,6 +5468,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317682</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5389,6 +5604,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317683</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5520,6 +5740,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317684</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5651,6 +5876,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317685</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5777,6 +6007,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317687</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5908,6 +6143,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317688</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6039,6 +6279,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317689</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6174,6 +6419,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317691</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6305,6 +6555,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317692</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6436,6 +6691,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317693</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6567,6 +6827,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317694</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6698,6 +6963,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317695</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6829,6 +7099,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317696</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6960,6 +7235,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317697</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7091,6 +7371,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317698</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7226,6 +7511,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317699</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7357,6 +7647,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317700</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7488,6 +7783,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317701</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7619,6 +7919,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317702</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7750,6 +8055,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317708</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7881,6 +8191,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317709</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8012,6 +8327,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317710</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8138,6 +8458,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317711</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8273,6 +8598,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317712</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8404,6 +8734,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317713</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8530,6 +8865,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317714</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8640,6 +8980,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841739</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8750,6 +9095,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841740</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8860,6 +9210,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841741</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8957,6 +9312,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957860</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9054,6 +9414,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959107</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9151,6 +9516,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963916</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9248,6 +9618,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964543</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9345,6 +9720,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967360</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9442,6 +9822,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968421</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9539,6 +9924,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970034</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9654,6 +10044,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317673</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9784,6 +10179,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317674</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9886,6 +10286,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960865</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9988,6 +10393,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965261</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10118,6 +10528,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317655</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10248,6 +10663,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317657</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10378,6 +10798,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317658</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10508,6 +10933,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317659</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10638,6 +11068,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317660</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10768,6 +11203,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317661</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10887,6 +11327,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841710</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11006,6 +11451,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841711</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11108,6 +11558,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957165</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11210,6 +11665,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967586</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11312,6 +11772,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968419</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11414,6 +11879,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968835</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11532,6 +12002,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317668</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11650,6 +12125,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317670</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11768,6 +12248,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317671</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11886,6 +12371,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317675</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11983,6 +12473,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959108</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12080,6 +12575,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960863</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12181,6 +12681,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966317</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12278,6 +12783,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965260</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12375,6 +12885,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966518</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12472,6 +12987,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960440</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12569,6 +13089,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967588</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12693,6 +13218,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130317719</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12812,6 +13342,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841767</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12931,6 +13466,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841768</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13050,6 +13590,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841769</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13169,6 +13714,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841770</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13288,6 +13838,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134841771</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13389,6 +13944,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955275</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13490,6 +14050,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956090</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13591,6 +14156,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956544</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13692,6 +14262,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958910</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13793,6 +14368,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959316</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13894,6 +14474,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959721</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13991,6 +14576,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960866</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14092,6 +14682,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961959</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14193,6 +14788,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962672</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14294,6 +14894,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965265</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14395,6 +15000,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965893</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14496,6 +15106,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966517</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14597,6 +15212,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968005</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14698,6 +15318,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968422</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14799,6 +15424,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970031</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14900,6 +15530,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970241</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15001,6 +15636,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971309</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15098,6 +15738,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960018</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15195,6 +15840,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964821</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15292,8 +15942,145 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965892</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ131"/>
+  <dimension ref="A1:AZ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11211,7 +11211,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134841710</v>
+        <v>134957165</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -11239,32 +11239,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507106</v>
+        <v>507092</v>
       </c>
       <c r="R89" t="n">
-        <v>6958185</v>
+        <v>6958137</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11288,22 +11281,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11318,24 +11301,24 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841710</t>
+          <t>https://artportalen.se/Sighting/134957165</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134841711</v>
+        <v>134967586</v>
       </c>
       <c r="B90" t="n">
         <v>57975</v>
@@ -11363,32 +11346,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>507123</v>
+        <v>507045</v>
       </c>
       <c r="R90" t="n">
-        <v>6958243</v>
+        <v>6958452</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11412,22 +11388,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11442,24 +11408,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841711</t>
+          <t>https://artportalen.se/Sighting/134967586</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134957165</v>
+        <v>134968419</v>
       </c>
       <c r="B91" t="n">
         <v>57975</v>
@@ -11499,10 +11465,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>507092</v>
+        <v>507098</v>
       </c>
       <c r="R91" t="n">
-        <v>6958137</v>
+        <v>6958202</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11560,13 +11526,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134957165</t>
+          <t>https://artportalen.se/Sighting/134968419</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134967586</v>
+        <v>134968835</v>
       </c>
       <c r="B92" t="n">
         <v>57975</v>
@@ -11606,10 +11572,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>507045</v>
+        <v>507100</v>
       </c>
       <c r="R92" t="n">
-        <v>6958452</v>
+        <v>6958200</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11667,16 +11633,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134967586</t>
+          <t>https://artportalen.se/Sighting/134968835</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134968419</v>
+        <v>130317668</v>
       </c>
       <c r="B93" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11684,39 +11650,50 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>507098</v>
+        <v>506884</v>
       </c>
       <c r="R93" t="n">
-        <v>6958202</v>
+        <v>6958644</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11743,12 +11720,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11759,31 +11736,36 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968419</t>
+          <t>https://artportalen.se/Sighting/130317668</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134968835</v>
+        <v>130317670</v>
       </c>
       <c r="B94" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11791,39 +11773,50 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>507100</v>
+        <v>506867</v>
       </c>
       <c r="R94" t="n">
-        <v>6958200</v>
+        <v>6958649</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11850,12 +11843,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11866,28 +11859,33 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968835</t>
+          <t>https://artportalen.se/Sighting/130317670</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130317668</v>
+        <v>130317671</v>
       </c>
       <c r="B95" t="n">
         <v>58114</v>
@@ -11938,10 +11936,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506884</v>
+        <v>506956</v>
       </c>
       <c r="R95" t="n">
-        <v>6958644</v>
+        <v>6958085</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12004,16 +12002,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317668</t>
+          <t>https://artportalen.se/Sighting/130317671</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130317670</v>
+        <v>130317675</v>
       </c>
       <c r="B96" t="n">
-        <v>58114</v>
+        <v>56522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12021,21 +12019,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12047,7 +12045,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -12061,10 +12059,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>506867</v>
+        <v>507115</v>
       </c>
       <c r="R96" t="n">
-        <v>6958649</v>
+        <v>6958267</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12127,67 +12125,51 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317670</t>
+          <t>https://artportalen.se/Sighting/130317675</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130317671</v>
+        <v>134959108</v>
       </c>
       <c r="B97" t="n">
-        <v>58114</v>
+        <v>99112</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>506956</v>
+        <v>507019</v>
       </c>
       <c r="R97" t="n">
-        <v>6958085</v>
+        <v>6958429</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12214,12 +12196,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12230,87 +12212,66 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317671</t>
+          <t>https://artportalen.se/Sighting/134959108</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130317675</v>
+        <v>134960863</v>
       </c>
       <c r="B98" t="n">
-        <v>56522</v>
+        <v>99112</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>206004</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>507115</v>
+        <v>507097</v>
       </c>
       <c r="R98" t="n">
-        <v>6958267</v>
+        <v>6958045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12337,12 +12298,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12353,33 +12314,28 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317675</t>
+          <t>https://artportalen.se/Sighting/134960863</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134959108</v>
+        <v>134966317</v>
       </c>
       <c r="B99" t="n">
         <v>99112</v>
@@ -12407,17 +12363,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>507019</v>
+        <v>507088</v>
       </c>
       <c r="R99" t="n">
-        <v>6958429</v>
+        <v>6958044</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12475,16 +12435,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959108</t>
+          <t>https://artportalen.se/Sighting/134966317</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134960863</v>
+        <v>134965260</v>
       </c>
       <c r="B100" t="n">
-        <v>99112</v>
+        <v>99533</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12492,34 +12452,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>507097</v>
+        <v>507028</v>
       </c>
       <c r="R100" t="n">
-        <v>6958045</v>
+        <v>6958424</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12577,16 +12537,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960863</t>
+          <t>https://artportalen.se/Sighting/134965260</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134966317</v>
+        <v>134966518</v>
       </c>
       <c r="B101" t="n">
-        <v>99112</v>
+        <v>99533</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12594,38 +12554,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>507088</v>
+        <v>507047</v>
       </c>
       <c r="R101" t="n">
-        <v>6958044</v>
+        <v>6958372</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12683,16 +12639,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966317</t>
+          <t>https://artportalen.se/Sighting/134966518</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134965260</v>
+        <v>134960440</v>
       </c>
       <c r="B102" t="n">
-        <v>99533</v>
+        <v>108205</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12700,21 +12656,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219880</v>
+        <v>220083</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12724,10 +12680,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>507028</v>
+        <v>507039</v>
       </c>
       <c r="R102" t="n">
-        <v>6958424</v>
+        <v>6958407</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12785,16 +12741,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965260</t>
+          <t>https://artportalen.se/Sighting/134960440</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134966518</v>
+        <v>134967588</v>
       </c>
       <c r="B103" t="n">
-        <v>99533</v>
+        <v>111153</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12802,21 +12758,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219880</v>
+        <v>220240</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12826,10 +12782,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>507047</v>
+        <v>507108</v>
       </c>
       <c r="R103" t="n">
-        <v>6958372</v>
+        <v>6958208</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12887,51 +12843,67 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966518</t>
+          <t>https://artportalen.se/Sighting/134967588</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134960440</v>
+        <v>130317719</v>
       </c>
       <c r="B104" t="n">
-        <v>108205</v>
+        <v>99118</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220083</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>507039</v>
+        <v>506940</v>
       </c>
       <c r="R104" t="n">
-        <v>6958407</v>
+        <v>6958101</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12958,12 +12930,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12972,71 +12949,89 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960440</t>
+          <t>https://artportalen.se/Sighting/130317719</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134967588</v>
+        <v>134841767</v>
       </c>
       <c r="B105" t="n">
-        <v>111153</v>
+        <v>99195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>507108</v>
+        <v>507039</v>
       </c>
       <c r="R105" t="n">
-        <v>6958208</v>
+        <v>6958029</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13060,12 +13055,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13080,27 +13085,27 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134967588</t>
+          <t>https://artportalen.se/Sighting/134841767</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130317719</v>
+        <v>134841768</v>
       </c>
       <c r="B106" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13127,7 +13132,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -13135,26 +13140,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506940</v>
+        <v>506984</v>
       </c>
       <c r="R106" t="n">
-        <v>6958101</v>
+        <v>6958031</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13178,17 +13179,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13197,36 +13203,30 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317719</t>
+          <t>https://artportalen.se/Sighting/134841768</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134841767</v>
+        <v>134841769</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -13269,14 +13269,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>507039</v>
+        <v>507066</v>
       </c>
       <c r="R107" t="n">
-        <v>6958029</v>
+        <v>6958073</v>
       </c>
       <c r="S107" t="n">
         <v>4</v>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13344,13 +13344,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841767</t>
+          <t>https://artportalen.se/Sighting/134841769</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134841768</v>
+        <v>134841770</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -13393,14 +13393,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506984</v>
+        <v>506871</v>
       </c>
       <c r="R108" t="n">
-        <v>6958031</v>
+        <v>6958504</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13468,13 +13468,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841768</t>
+          <t>https://artportalen.se/Sighting/134841770</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134841769</v>
+        <v>134841771</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13517,14 +13517,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>507066</v>
+        <v>506917</v>
       </c>
       <c r="R109" t="n">
-        <v>6958073</v>
+        <v>6958119</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13592,13 +13592,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841769</t>
+          <t>https://artportalen.se/Sighting/134841771</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134841770</v>
+        <v>134955275</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -13628,30 +13628,22 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>506871</v>
+        <v>507086</v>
       </c>
       <c r="R110" t="n">
-        <v>6958504</v>
+        <v>6958292</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13675,22 +13667,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13705,24 +13687,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841770</t>
+          <t>https://artportalen.se/Sighting/134955275</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134841771</v>
+        <v>134956090</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -13752,30 +13734,22 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>506917</v>
+        <v>507077</v>
       </c>
       <c r="R111" t="n">
-        <v>6958119</v>
+        <v>6958363</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13799,22 +13773,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13829,24 +13793,24 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841771</t>
+          <t>https://artportalen.se/Sighting/134956090</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134955275</v>
+        <v>134956544</v>
       </c>
       <c r="B112" t="n">
         <v>99195</v>
@@ -13885,10 +13849,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>507086</v>
+        <v>507071</v>
       </c>
       <c r="R112" t="n">
-        <v>6958292</v>
+        <v>6958357</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13946,13 +13910,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134955275</t>
+          <t>https://artportalen.se/Sighting/134956544</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134956090</v>
+        <v>134958910</v>
       </c>
       <c r="B113" t="n">
         <v>99195</v>
@@ -13982,7 +13946,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13991,10 +13955,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>507077</v>
+        <v>507007</v>
       </c>
       <c r="R113" t="n">
-        <v>6958363</v>
+        <v>6958439</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14052,13 +14016,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134956090</t>
+          <t>https://artportalen.se/Sighting/134958910</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134956544</v>
+        <v>134959316</v>
       </c>
       <c r="B114" t="n">
         <v>99195</v>
@@ -14097,10 +14061,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>507071</v>
+        <v>507064</v>
       </c>
       <c r="R114" t="n">
-        <v>6958357</v>
+        <v>6958456</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14158,13 +14122,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134956544</t>
+          <t>https://artportalen.se/Sighting/134959316</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134958910</v>
+        <v>134959721</v>
       </c>
       <c r="B115" t="n">
         <v>99195</v>
@@ -14194,7 +14158,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14203,10 +14167,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>507007</v>
+        <v>507056</v>
       </c>
       <c r="R115" t="n">
-        <v>6958439</v>
+        <v>6958071</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14264,13 +14228,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134958910</t>
+          <t>https://artportalen.se/Sighting/134959721</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134959316</v>
+        <v>134960866</v>
       </c>
       <c r="B116" t="n">
         <v>99195</v>
@@ -14298,21 +14262,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>507064</v>
+        <v>507090</v>
       </c>
       <c r="R116" t="n">
-        <v>6958456</v>
+        <v>6958137</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14370,13 +14330,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959316</t>
+          <t>https://artportalen.se/Sighting/134960866</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134959721</v>
+        <v>134961959</v>
       </c>
       <c r="B117" t="n">
         <v>99195</v>
@@ -14406,7 +14366,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14415,10 +14375,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>507056</v>
+        <v>507101</v>
       </c>
       <c r="R117" t="n">
-        <v>6958071</v>
+        <v>6958152</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14476,13 +14436,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959721</t>
+          <t>https://artportalen.se/Sighting/134961959</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134960866</v>
+        <v>134962672</v>
       </c>
       <c r="B118" t="n">
         <v>99195</v>
@@ -14510,17 +14470,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>507090</v>
+        <v>507106</v>
       </c>
       <c r="R118" t="n">
-        <v>6958137</v>
+        <v>6958171</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14578,13 +14542,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960866</t>
+          <t>https://artportalen.se/Sighting/134962672</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134961959</v>
+        <v>134965265</v>
       </c>
       <c r="B119" t="n">
         <v>99195</v>
@@ -14623,10 +14587,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>507101</v>
+        <v>507059</v>
       </c>
       <c r="R119" t="n">
-        <v>6958152</v>
+        <v>6958435</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14684,13 +14648,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134961959</t>
+          <t>https://artportalen.se/Sighting/134965265</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134962672</v>
+        <v>134965893</v>
       </c>
       <c r="B120" t="n">
         <v>99195</v>
@@ -14720,7 +14684,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14729,10 +14693,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>507106</v>
+        <v>507091</v>
       </c>
       <c r="R120" t="n">
-        <v>6958171</v>
+        <v>6958333</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14790,13 +14754,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134962672</t>
+          <t>https://artportalen.se/Sighting/134965893</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134965265</v>
+        <v>134966517</v>
       </c>
       <c r="B121" t="n">
         <v>99195</v>
@@ -14826,7 +14790,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14835,10 +14799,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>507059</v>
+        <v>507096</v>
       </c>
       <c r="R121" t="n">
-        <v>6958435</v>
+        <v>6958124</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14896,13 +14860,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965265</t>
+          <t>https://artportalen.se/Sighting/134966517</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134965893</v>
+        <v>134968005</v>
       </c>
       <c r="B122" t="n">
         <v>99195</v>
@@ -14932,7 +14896,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14941,10 +14905,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>507091</v>
+        <v>507082</v>
       </c>
       <c r="R122" t="n">
-        <v>6958333</v>
+        <v>6958354</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15002,13 +14966,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965893</t>
+          <t>https://artportalen.se/Sighting/134968005</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134966517</v>
+        <v>134968422</v>
       </c>
       <c r="B123" t="n">
         <v>99195</v>
@@ -15038,7 +15002,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -15047,10 +15011,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>507096</v>
+        <v>507097</v>
       </c>
       <c r="R123" t="n">
-        <v>6958124</v>
+        <v>6958307</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15108,13 +15072,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966517</t>
+          <t>https://artportalen.se/Sighting/134968422</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134968005</v>
+        <v>134970031</v>
       </c>
       <c r="B124" t="n">
         <v>99195</v>
@@ -15144,7 +15108,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15153,10 +15117,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>507082</v>
+        <v>507099</v>
       </c>
       <c r="R124" t="n">
-        <v>6958354</v>
+        <v>6958231</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15214,13 +15178,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968005</t>
+          <t>https://artportalen.se/Sighting/134970031</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134968422</v>
+        <v>134970241</v>
       </c>
       <c r="B125" t="n">
         <v>99195</v>
@@ -15250,7 +15214,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -15259,10 +15223,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>507097</v>
+        <v>507017</v>
       </c>
       <c r="R125" t="n">
-        <v>6958307</v>
+        <v>6958430</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15320,13 +15284,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968422</t>
+          <t>https://artportalen.se/Sighting/134970241</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134970031</v>
+        <v>134971309</v>
       </c>
       <c r="B126" t="n">
         <v>99195</v>
@@ -15356,19 +15320,19 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>507099</v>
+        <v>507068</v>
       </c>
       <c r="R126" t="n">
-        <v>6958231</v>
+        <v>6958037</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15426,55 +15390,51 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134970031</t>
+          <t>https://artportalen.se/Sighting/134971309</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134970241</v>
+        <v>134960018</v>
       </c>
       <c r="B127" t="n">
-        <v>99195</v>
+        <v>106324</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>507017</v>
+        <v>507040</v>
       </c>
       <c r="R127" t="n">
-        <v>6958430</v>
+        <v>6958405</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15532,55 +15492,51 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134970241</t>
+          <t>https://artportalen.se/Sighting/134960018</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134971309</v>
+        <v>134964821</v>
       </c>
       <c r="B128" t="n">
-        <v>99195</v>
+        <v>98060</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>507068</v>
+        <v>507084</v>
       </c>
       <c r="R128" t="n">
-        <v>6958037</v>
+        <v>6958378</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15638,16 +15594,16 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134971309</t>
+          <t>https://artportalen.se/Sighting/134964821</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134960018</v>
+        <v>134965892</v>
       </c>
       <c r="B129" t="n">
-        <v>106324</v>
+        <v>103762</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,21 +15611,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221144</v>
+        <v>222002</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15679,10 +15635,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>507040</v>
+        <v>507106</v>
       </c>
       <c r="R129" t="n">
-        <v>6958405</v>
+        <v>6958112</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15739,210 +15695,6 @@
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134960018</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>134964821</v>
-      </c>
-      <c r="B130" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Björnsjöänget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q130" t="n">
-        <v>507084</v>
-      </c>
-      <c r="R130" t="n">
-        <v>6958378</v>
-      </c>
-      <c r="S130" t="n">
-        <v>10</v>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AD130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT130" t="inlineStr"/>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>Via Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/134964821</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>134965892</v>
-      </c>
-      <c r="B131" t="n">
-        <v>103762</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>222002</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Underviol</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Viola mirabilis</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Björnsjöänget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q131" t="n">
-        <v>507106</v>
-      </c>
-      <c r="R131" t="n">
-        <v>6958112</v>
-      </c>
-      <c r="S131" t="n">
-        <v>10</v>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>Bodsjö</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="AD131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT131" t="inlineStr"/>
-      <c r="AW131" t="inlineStr">
-        <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>Via Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
-      <c r="AZ131" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134965892</t>
         </is>
@@ -16078,8 +15830,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61483-2024 artfynd.xlsx
+++ b/artfynd/A 61483-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ129"/>
+  <dimension ref="A1:AZ131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>134956728</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134967164</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>134966523</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>134970033</v>
       </c>
       <c r="B7" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>134964820</v>
       </c>
       <c r="B8" t="n">
-        <v>96413</v>
+        <v>96457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>134961088</v>
       </c>
       <c r="B9" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>134963492</v>
       </c>
       <c r="B10" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>134966521</v>
       </c>
       <c r="B11" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>134963912</v>
       </c>
       <c r="B12" t="n">
-        <v>91745</v>
+        <v>91786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>134963704</v>
       </c>
       <c r="B13" t="n">
-        <v>92199</v>
+        <v>92241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>134956761</v>
       </c>
       <c r="B14" t="n">
-        <v>92943</v>
+        <v>92985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>134963294</v>
       </c>
       <c r="B15" t="n">
-        <v>92943</v>
+        <v>92985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>134970653</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>134959105</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>134959720</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>134962671</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>134963915</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>134970654</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>134961087</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>134957860</v>
       </c>
       <c r="B72" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>134959107</v>
       </c>
       <c r="B73" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>134963916</v>
       </c>
       <c r="B74" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>134964543</v>
       </c>
       <c r="B75" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>134967360</v>
       </c>
       <c r="B76" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>134968421</v>
       </c>
       <c r="B77" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>134970034</v>
       </c>
       <c r="B78" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>134960865</v>
       </c>
       <c r="B81" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>134965261</v>
       </c>
       <c r="B82" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11211,10 +11211,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134957165</v>
+        <v>134841710</v>
       </c>
       <c r="B89" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11239,25 +11239,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>507092</v>
+        <v>507106</v>
       </c>
       <c r="R89" t="n">
-        <v>6958137</v>
+        <v>6958185</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11281,12 +11288,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11301,27 +11318,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134957165</t>
+          <t>https://artportalen.se/Sighting/134841710</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134967586</v>
+        <v>134841711</v>
       </c>
       <c r="B90" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11346,25 +11363,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>507045</v>
+        <v>507123</v>
       </c>
       <c r="R90" t="n">
-        <v>6958452</v>
+        <v>6958243</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11388,12 +11412,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11408,27 +11442,27 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134967586</t>
+          <t>https://artportalen.se/Sighting/134841711</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134968419</v>
+        <v>134957165</v>
       </c>
       <c r="B91" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11465,10 +11499,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>507098</v>
+        <v>507092</v>
       </c>
       <c r="R91" t="n">
-        <v>6958202</v>
+        <v>6958137</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11526,16 +11560,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968419</t>
+          <t>https://artportalen.se/Sighting/134957165</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134968835</v>
+        <v>134967586</v>
       </c>
       <c r="B92" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11572,10 +11606,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>507100</v>
+        <v>507045</v>
       </c>
       <c r="R92" t="n">
-        <v>6958200</v>
+        <v>6958452</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11633,16 +11667,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968835</t>
+          <t>https://artportalen.se/Sighting/134967586</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130317668</v>
+        <v>134968419</v>
       </c>
       <c r="B93" t="n">
-        <v>58114</v>
+        <v>57980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11650,50 +11684,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>506884</v>
+        <v>507098</v>
       </c>
       <c r="R93" t="n">
-        <v>6958644</v>
+        <v>6958202</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11720,12 +11743,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11736,36 +11759,31 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317668</t>
+          <t>https://artportalen.se/Sighting/134968419</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130317670</v>
+        <v>134968835</v>
       </c>
       <c r="B94" t="n">
-        <v>58114</v>
+        <v>57980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11773,50 +11791,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>506867</v>
+        <v>507100</v>
       </c>
       <c r="R94" t="n">
-        <v>6958649</v>
+        <v>6958200</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11843,12 +11850,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11859,33 +11866,28 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317670</t>
+          <t>https://artportalen.se/Sighting/134968835</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130317671</v>
+        <v>130317668</v>
       </c>
       <c r="B95" t="n">
         <v>58114</v>
@@ -11936,10 +11938,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>506956</v>
+        <v>506884</v>
       </c>
       <c r="R95" t="n">
-        <v>6958085</v>
+        <v>6958644</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12002,16 +12004,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317671</t>
+          <t>https://artportalen.se/Sighting/130317668</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130317675</v>
+        <v>130317670</v>
       </c>
       <c r="B96" t="n">
-        <v>56522</v>
+        <v>58114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12019,21 +12021,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12045,7 +12047,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -12059,10 +12061,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>507115</v>
+        <v>506867</v>
       </c>
       <c r="R96" t="n">
-        <v>6958267</v>
+        <v>6958649</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12125,51 +12127,67 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317675</t>
+          <t>https://artportalen.se/Sighting/130317670</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134959108</v>
+        <v>130317671</v>
       </c>
       <c r="B97" t="n">
-        <v>99112</v>
+        <v>58114</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>507019</v>
+        <v>506956</v>
       </c>
       <c r="R97" t="n">
-        <v>6958429</v>
+        <v>6958085</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12196,12 +12214,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12212,66 +12230,87 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959108</t>
+          <t>https://artportalen.se/Sighting/130317671</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134960863</v>
+        <v>130317675</v>
       </c>
       <c r="B98" t="n">
-        <v>99112</v>
+        <v>56522</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>507097</v>
+        <v>507115</v>
       </c>
       <c r="R98" t="n">
-        <v>6958045</v>
+        <v>6958267</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12298,12 +12337,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12314,31 +12353,36 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960863</t>
+          <t>https://artportalen.se/Sighting/130317675</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134966317</v>
+        <v>134959108</v>
       </c>
       <c r="B99" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12363,21 +12407,17 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>507088</v>
+        <v>507019</v>
       </c>
       <c r="R99" t="n">
-        <v>6958044</v>
+        <v>6958429</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12435,16 +12475,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966317</t>
+          <t>https://artportalen.se/Sighting/134959108</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134965260</v>
+        <v>134960863</v>
       </c>
       <c r="B100" t="n">
-        <v>99533</v>
+        <v>99159</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12452,34 +12492,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>507028</v>
+        <v>507097</v>
       </c>
       <c r="R100" t="n">
-        <v>6958424</v>
+        <v>6958045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12537,16 +12577,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965260</t>
+          <t>https://artportalen.se/Sighting/134960863</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134966518</v>
+        <v>134966317</v>
       </c>
       <c r="B101" t="n">
-        <v>99533</v>
+        <v>99159</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12554,34 +12594,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>507047</v>
+        <v>507088</v>
       </c>
       <c r="R101" t="n">
-        <v>6958372</v>
+        <v>6958044</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12639,16 +12683,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966518</t>
+          <t>https://artportalen.se/Sighting/134966317</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134960440</v>
+        <v>134965260</v>
       </c>
       <c r="B102" t="n">
-        <v>108205</v>
+        <v>99580</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12656,21 +12700,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220083</v>
+        <v>219880</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12680,10 +12724,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>507039</v>
+        <v>507028</v>
       </c>
       <c r="R102" t="n">
-        <v>6958407</v>
+        <v>6958424</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12741,16 +12785,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960440</t>
+          <t>https://artportalen.se/Sighting/134965260</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134967588</v>
+        <v>134966518</v>
       </c>
       <c r="B103" t="n">
-        <v>111153</v>
+        <v>99580</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12758,21 +12802,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220240</v>
+        <v>219880</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12782,10 +12826,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>507108</v>
+        <v>507047</v>
       </c>
       <c r="R103" t="n">
-        <v>6958208</v>
+        <v>6958372</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12843,67 +12887,51 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134967588</t>
+          <t>https://artportalen.se/Sighting/134966518</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130317719</v>
+        <v>134960440</v>
       </c>
       <c r="B104" t="n">
-        <v>99118</v>
+        <v>108260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Björnsjön Öst, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>506940</v>
+        <v>507039</v>
       </c>
       <c r="R104" t="n">
-        <v>6958101</v>
+        <v>6958407</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12930,17 +12958,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12949,89 +12972,71 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130317719</t>
+          <t>https://artportalen.se/Sighting/134960440</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134841767</v>
+        <v>134967588</v>
       </c>
       <c r="B105" t="n">
-        <v>99195</v>
+        <v>111210</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>507039</v>
+        <v>507108</v>
       </c>
       <c r="R105" t="n">
-        <v>6958029</v>
+        <v>6958208</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13055,22 +13060,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13085,27 +13080,27 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Via Caspar Ström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841767</t>
+          <t>https://artportalen.se/Sighting/134967588</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134841768</v>
+        <v>130317719</v>
       </c>
       <c r="B106" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13132,7 +13127,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -13140,22 +13135,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>506984</v>
+        <v>506940</v>
       </c>
       <c r="R106" t="n">
-        <v>6958031</v>
+        <v>6958101</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13179,22 +13178,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Minst 4 st synliga plantor på fyndplatsen. Dessa observerades på delvis snötäckt mark. Under barmarksperioden kan här mest sannolikt observeras betydligt fler plantor av knärot.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13203,30 +13197,36 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841768</t>
+          <t>https://artportalen.se/Sighting/130317719</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134841769</v>
+        <v>134841767</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -13269,14 +13269,14 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>507066</v>
+        <v>507039</v>
       </c>
       <c r="R107" t="n">
-        <v>6958073</v>
+        <v>6958029</v>
       </c>
       <c r="S107" t="n">
         <v>4</v>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13344,13 +13344,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841769</t>
+          <t>https://artportalen.se/Sighting/134841767</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134841770</v>
+        <v>134841768</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -13393,14 +13393,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>506871</v>
+        <v>506984</v>
       </c>
       <c r="R108" t="n">
-        <v>6958504</v>
+        <v>6958031</v>
       </c>
       <c r="S108" t="n">
         <v>4</v>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13468,13 +13468,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841770</t>
+          <t>https://artportalen.se/Sighting/134841768</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134841771</v>
+        <v>134841769</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13517,14 +13517,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Korsgräsnäset, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>506917</v>
+        <v>507066</v>
       </c>
       <c r="R109" t="n">
-        <v>6958119</v>
+        <v>6958073</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13592,13 +13592,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134841771</t>
+          <t>https://artportalen.se/Sighting/134841769</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134955275</v>
+        <v>134841770</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -13628,22 +13628,30 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>507086</v>
+        <v>506871</v>
       </c>
       <c r="R110" t="n">
-        <v>6958292</v>
+        <v>6958504</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13667,12 +13675,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13687,24 +13705,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134955275</t>
+          <t>https://artportalen.se/Sighting/134841770</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134956090</v>
+        <v>134841771</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -13734,22 +13752,30 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Korsgräsnäset, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>507077</v>
+        <v>506917</v>
       </c>
       <c r="R111" t="n">
-        <v>6958363</v>
+        <v>6958119</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13773,12 +13799,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13793,27 +13829,27 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Via Caspar Ström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134956090</t>
+          <t>https://artportalen.se/Sighting/134841771</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134956544</v>
+        <v>134955275</v>
       </c>
       <c r="B112" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13849,10 +13885,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>507071</v>
+        <v>507086</v>
       </c>
       <c r="R112" t="n">
-        <v>6958357</v>
+        <v>6958292</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13910,16 +13946,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134956544</t>
+          <t>https://artportalen.se/Sighting/134955275</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134958910</v>
+        <v>134956090</v>
       </c>
       <c r="B113" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13946,7 +13982,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13955,10 +13991,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>507007</v>
+        <v>507077</v>
       </c>
       <c r="R113" t="n">
-        <v>6958439</v>
+        <v>6958363</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14016,16 +14052,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134958910</t>
+          <t>https://artportalen.se/Sighting/134956090</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134959316</v>
+        <v>134956544</v>
       </c>
       <c r="B114" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14061,10 +14097,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>507064</v>
+        <v>507071</v>
       </c>
       <c r="R114" t="n">
-        <v>6958456</v>
+        <v>6958357</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14122,16 +14158,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959316</t>
+          <t>https://artportalen.se/Sighting/134956544</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134959721</v>
+        <v>134958910</v>
       </c>
       <c r="B115" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14158,7 +14194,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -14167,10 +14203,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>507056</v>
+        <v>507007</v>
       </c>
       <c r="R115" t="n">
-        <v>6958071</v>
+        <v>6958439</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14228,16 +14264,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134959721</t>
+          <t>https://artportalen.se/Sighting/134958910</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134960866</v>
+        <v>134959316</v>
       </c>
       <c r="B116" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14262,17 +14298,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>507090</v>
+        <v>507064</v>
       </c>
       <c r="R116" t="n">
-        <v>6958137</v>
+        <v>6958456</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14330,16 +14370,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960866</t>
+          <t>https://artportalen.se/Sighting/134959316</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134961959</v>
+        <v>134959721</v>
       </c>
       <c r="B117" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14366,7 +14406,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14375,10 +14415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>507101</v>
+        <v>507056</v>
       </c>
       <c r="R117" t="n">
-        <v>6958152</v>
+        <v>6958071</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14436,16 +14476,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134961959</t>
+          <t>https://artportalen.se/Sighting/134959721</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134962672</v>
+        <v>134960866</v>
       </c>
       <c r="B118" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14470,21 +14510,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>507106</v>
+        <v>507090</v>
       </c>
       <c r="R118" t="n">
-        <v>6958171</v>
+        <v>6958137</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14542,16 +14578,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134962672</t>
+          <t>https://artportalen.se/Sighting/134960866</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134965265</v>
+        <v>134961959</v>
       </c>
       <c r="B119" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14587,10 +14623,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>507059</v>
+        <v>507101</v>
       </c>
       <c r="R119" t="n">
-        <v>6958435</v>
+        <v>6958152</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14648,16 +14684,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965265</t>
+          <t>https://artportalen.se/Sighting/134961959</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134965893</v>
+        <v>134962672</v>
       </c>
       <c r="B120" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14684,7 +14720,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14693,10 +14729,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>507091</v>
+        <v>507106</v>
       </c>
       <c r="R120" t="n">
-        <v>6958333</v>
+        <v>6958171</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14754,16 +14790,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134965893</t>
+          <t>https://artportalen.se/Sighting/134962672</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134966517</v>
+        <v>134965265</v>
       </c>
       <c r="B121" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14790,7 +14826,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14799,10 +14835,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>507096</v>
+        <v>507059</v>
       </c>
       <c r="R121" t="n">
-        <v>6958124</v>
+        <v>6958435</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14860,16 +14896,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134966517</t>
+          <t>https://artportalen.se/Sighting/134965265</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134968005</v>
+        <v>134965893</v>
       </c>
       <c r="B122" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14896,7 +14932,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14905,10 +14941,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>507082</v>
+        <v>507091</v>
       </c>
       <c r="R122" t="n">
-        <v>6958354</v>
+        <v>6958333</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14966,16 +15002,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968005</t>
+          <t>https://artportalen.se/Sighting/134965893</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134968422</v>
+        <v>134966517</v>
       </c>
       <c r="B123" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15002,7 +15038,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -15011,10 +15047,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>507097</v>
+        <v>507096</v>
       </c>
       <c r="R123" t="n">
-        <v>6958307</v>
+        <v>6958124</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15072,16 +15108,16 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134968422</t>
+          <t>https://artportalen.se/Sighting/134966517</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134970031</v>
+        <v>134968005</v>
       </c>
       <c r="B124" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15108,7 +15144,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -15117,10 +15153,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>507099</v>
+        <v>507082</v>
       </c>
       <c r="R124" t="n">
-        <v>6958231</v>
+        <v>6958354</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -15178,16 +15214,16 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134970031</t>
+          <t>https://artportalen.se/Sighting/134968005</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134970241</v>
+        <v>134968422</v>
       </c>
       <c r="B125" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15214,7 +15250,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -15223,10 +15259,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>507017</v>
+        <v>507097</v>
       </c>
       <c r="R125" t="n">
-        <v>6958430</v>
+        <v>6958307</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15284,16 +15320,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134970241</t>
+          <t>https://artportalen.se/Sighting/134968422</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134971309</v>
+        <v>134970031</v>
       </c>
       <c r="B126" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15320,19 +15356,19 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Björnåsen, Jmt</t>
+          <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>507068</v>
+        <v>507099</v>
       </c>
       <c r="R126" t="n">
-        <v>6958037</v>
+        <v>6958231</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15390,51 +15426,55 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134971309</t>
+          <t>https://artportalen.se/Sighting/134970031</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134960018</v>
+        <v>134970241</v>
       </c>
       <c r="B127" t="n">
-        <v>106324</v>
+        <v>99242</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Björnsjöänget, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>507040</v>
+        <v>507017</v>
       </c>
       <c r="R127" t="n">
-        <v>6958405</v>
+        <v>6958430</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15492,51 +15532,55 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134960018</t>
+          <t>https://artportalen.se/Sighting/134970241</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134964821</v>
+        <v>134971309</v>
       </c>
       <c r="B128" t="n">
-        <v>98060</v>
+        <v>99242</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Björnsjöänget, Jmt</t>
+          <t>Björnåsen, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>507084</v>
+        <v>507068</v>
       </c>
       <c r="R128" t="n">
-        <v>6958378</v>
+        <v>6958037</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15594,16 +15638,16 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134964821</t>
+          <t>https://artportalen.se/Sighting/134971309</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134965892</v>
+        <v>134960018</v>
       </c>
       <c r="B129" t="n">
-        <v>103762</v>
+        <v>106379</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15611,21 +15655,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222002</v>
+        <v>221144</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15635,10 +15679,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>507106</v>
+        <v>507040</v>
       </c>
       <c r="R129" t="n">
-        <v>6958112</v>
+        <v>6958405</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15695,6 +15739,210 @@
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960018</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>134964821</v>
+      </c>
+      <c r="B130" t="n">
+        <v>98104</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Björnsjöänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>507084</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6958378</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964821</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>134965892</v>
+      </c>
+      <c r="B131" t="n">
+        <v>103813</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Björnsjöänget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>507106</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6958112</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Via Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134965892</t>
         </is>
@@ -15830,6 +16078,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
